--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -518,8 +518,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 2026-10-10
-小程序：2.0 已过审上线、2.1.1 出包未提审｜iPhone：1.2(26)｜各版本变化见后面分表</t>
+          <t>全量功能清单 · 总览｜截至 2026-10-11
+小程序：2.0 已过审上线、2.1.1 出包未提审（10-11 毛玻璃一轮已落码、未出包）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3450,6 +3450,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>2.1.0（10-08 出包 668.7KB）→ 2.1.1（10-09 出包，审计修复那一轮随包走）→ 10-10 第一屏三块改版（预览包 749.7KB，预览码 10-10 21:10 出）
+→ 10-11 毛玻璃一轮（**已落码、未出包**：四处玻璃＋两处盒子高＋列表撤那位小人）
 两号都未提审；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
 iPhone 同期：1.2(26) 当前</t>
         </is>
@@ -3697,7 +3698,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>左块人物入口 308 见方（点一下进拍照、连点两下换人物）＋右两枚计数 382×148</t>
+          <t>左块人物入口 308 见方（点一下进拍照）＋右两枚计数 382×148</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3719,17 +3720,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>两枚计数来自接口</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-10)</t>
+          <t>换人＝点右后方那枚剪影</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>改版(10-10 深夜)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+          <t>另一张缩成淡灰剪影落在主人物右后（高约一半），点它换位并记住本机</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3739,69 +3740,581 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+          <t>撤掉「连点两下」：那一下会让每次开门先被 300ms 定时器延住</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>三块面色随壁纸派生</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-10)</t>
+          <t>框外那一行＝Tips ＋ 返回</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>改版(10-10 深夜)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+          <t>左边轮播 Tips（原「选择记录模式」），右边「返回」（原「点空白处收起」）</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>未核</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+          <t>「返回」与笔记列表右上角那枚是同一支字典键，每页右上角一致</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>面板里上白边＝下白边</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>改版(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>撤掉卡里上面那一档 auto 边距，省出来的高度搬给三枚标签（43.2 → 64）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>两档 auto 会把富余对半分，上白边永远比下白边多半份</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>三枚标签按键面扩大</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>每枚吃满那一行 64rpx 高、左右各 22rpx 内缩（量到 108×63）</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>他原话「三个Tab很难点，把按键区域扩大」</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>圆钮固定橙、空着不给起拖</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>改版(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>圆始终 --cp-extract 橙；输入框空着时 touchstart 直接挡住，不再靠洗成灰表达</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>链接与文字两档同一处理；话仍然要说（那枚气泡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>所有输入报错＝输入框上方那枚气泡</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>改版(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>sayErr → hintLine → .hint-bubble（带阴影长条、3.6s 自己走、权限那一类整枚可点）</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>原来散在六处的 showToast 与框外那一行全部并进这一条；成功那声与语言切换失败没并</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>文字档也有粘贴钮、两档字同一行高</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>壳＋textarea＋粘贴钮；贴进来接在后面不顶掉；框给自己 28rpx 上内边距与链接档对齐</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>textarea 是原生组件装不下子节点，所以多包一层壳</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>列表</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>右上角那枚＝返回第一屏</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>改版(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>笔记列表与笔记卡片两枚 tab 共用同一枚，点下去 switchTab 回新建那一屏</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>「点一下展开」整件取消；「我的」那一屏右上仍是 MIND 数字（他没点到第三页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>列表</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>框外那一位：已撤（只在首页留）</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>撤除(10-11)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>站长原话「左上角的人，透明底侵入主图，列表左上角的人都去掉，维持只有首页有」；markup、样式、data 三头撤净，utils/person.js 本身留给首页</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>反向钉：列表页 markup/样式/data 里再出现 .ix-person／personSrc 就红（`验-第一屏三块`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>纯色底改半透明毛玻璃（白纱 α=.30）</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-11)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>app.wxss 一组 --glass-* 令牌：veil .30／blur(23px) saturate(1.8)／hairline .55／井底 .20／白条 .38；只在铺了形象图那一态（.container.has-bg）生效</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>α=.30 是站长在校准条上点的那一档，全站唯一出口由 `验-玻璃令牌齐不齐` 钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>面板外框与内框合成一张玻璃面</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>改版(10-11)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>外框＝白纱＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>列表</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>改版(10-11)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>改版(10-11)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>弹窗</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>三枚居中弹窗改成半透明</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-11)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度待量</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>详情</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>笔记详情浮窗保持实心</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>不做(10-11)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>`.float-sheet` 里一条玻璃声明都没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>卡片</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>大图右下那枚改叫「删除分享图」</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>改值(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>两枚计数来自接口</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>三块面色随壁纸派生</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>无障碍</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>三块各有读屏名字</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>新增(10-10)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>role=button + aria-label，念「记下来」／「12笔记」／「12卡片」，词全复用屏上字典键</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>未核</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>渲染层实测读得到（真跑尺子那条 attribute('aria-label')）</t>
         </is>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -519,7 +519,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>全量功能清单 · 总览｜截至 2026-10-11
-小程序：2.0 已过审上线、2.1.1 出包未提审（10-11 毛玻璃一轮已落码、未出包）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
+小程序：2.0 已过审上线、2.1.1 出包未提审、2.1.2 出预览包（10-11 毛玻璃一轮随这一版走，未提审）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
         </is>
       </c>
     </row>
@@ -3450,8 +3450,8 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>2.1.0（10-08 出包 668.7KB）→ 2.1.1（10-09 出包，审计修复那一轮随包走）→ 10-10 第一屏三块改版（预览包 749.7KB，预览码 10-10 21:10 出）
-→ 10-11 毛玻璃一轮（**已落码、未出包**：四处玻璃＋两处盒子高＋列表撤那位小人）
-两号都未提审；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
+→ **2.1.2**（10-11 毛玻璃一轮：四处玻璃＋两处盒子高＋列表撤那位小人；抬号后 09:03 `cli preview` 出预览包 753.9KB／772,008 B）
+2.1.1 与 2.1.2 都未提审；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
 iPhone 同期：1.2(26) 当前</t>
         </is>
       </c>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -3435,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>app.wxss 一组 --glass-* 令牌：veil .30／blur(23px) saturate(1.8)／hairline .55／井底 .20／白条 .38；只在铺了形象图那一态（.container.has-bg）生效</t>
+          <t>app.wxss 一组 --glass-* 令牌：veil .30／blur(23px) saturate(1.8)／hairline .55／井底 .20（白条 .38 那一档 10-11 09:2x 起没人吃，见下面「第一屏三块」那一行）；只在铺了形象图那一态（.container.has-bg）生效</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -4035,22 +4035,22 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>面板外框与内框合成一张玻璃面</t>
+          <t>第一屏那三块的玻璃已撤，退回实心面</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>撤掉(10-11 真机回电)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>外框＝白纱＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
+          <t>站长原话「漫画人物边缘外部是透明底，没说连衣服也透明了，ICON 也是」＋R1 后半句「按钮ICON不变」；四张插画自己就是大半透明（ic-person 实心像素只占 0.7%），底下换成 .30 白纱就直接透出照片，实测毛衣 rgb(165,133,123) vs 效果图 rgb(241,238,227)</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4060,19 +4060,19 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
+          <t>撤的是我这一轮加的，三块回到 10-10 那版实心面；要恢复这一格只欠「把四张插画压平」那一个决定</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>列表</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
+          <t>面板外框与内框合成一张玻璃面</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
+          <t>外框＝白纱＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -4092,19 +4092,19 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
+          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>列表</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
+          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -4124,29 +4124,29 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
+          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>三枚居中弹窗改成半透明</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-11)</t>
+          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>改版(10-11)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
+          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -4156,29 +4156,29 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度待量</t>
+          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>详情</t>
+          <t>弹窗</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>笔记详情浮窗保持实心</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>不做(10-11)</t>
+          <t>三枚居中弹窗改成半透明</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-11)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
+          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4188,29 +4188,29 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>`.float-sheet` 里一条玻璃声明都没有</t>
+          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>卡片</t>
+          <t>详情</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>大图右下那枚改叫「删除分享图」</t>
+          <t>笔记详情浮窗保持实心</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>改值(10-10 深夜)</t>
+          <t>不做(10-11)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
+          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
+          <t>`.float-sheet` 里一条玻璃声明都没有</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>卡片</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>两枚计数来自接口</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-10)</t>
+          <t>大图右下那枚改叫「删除分享图」</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>改值(10-10 深夜)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>三块面色随壁纸派生</t>
+          <t>两枚计数来自接口</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4274,47 +4274,79 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>未核</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>三块面色随壁纸派生</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>无障碍</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>三块各有读屏名字</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>新增(10-10)</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>role=button + aria-label，念「记下来」／「12笔记」／「12卡片」，词全复用屏上字典键</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>未核</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>渲染层实测读得到（真跑尺子那条 attribute('aria-label')）</t>
         </is>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -519,7 +519,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>全量功能清单 · 总览｜截至 2026-10-11
-小程序：2.0 已过审上线、2.1.1 出包未提审、2.1.2 出预览包（10-11 毛玻璃一轮随这一版走，未提审）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
+小程序：2.0 已过审上线、2.1.1 出包未提审、10-11 毛玻璃一轮走到 2.1.5 预览包（未提审、未上现网）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3450,8 +3450,11 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>2.1.0（10-08 出包 668.7KB）→ 2.1.1（10-09 出包，审计修复那一轮随包走）→ 10-10 第一屏三块改版（预览包 749.7KB，预览码 10-10 21:10 出）
-→ **2.1.2**（10-11 毛玻璃一轮：四处玻璃＋两处盒子高＋列表撤那位小人；抬号后 09:03 `cli preview` 出预览包 753.9KB／772,008 B）
-2.1.1 与 2.1.2 都未提审；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
+→ 2.1.2（10-11 毛玻璃一轮：四处玻璃＋两处盒子高＋列表撤那位小人；09:03 预览包 753.9KB／772,008 B）
+→ 2.1.3（他真机第一趟回电：我撤了首页三块玻璃＝错处置，并把「过深」拆成两笔账；09:46 预览包 753.5KB／771,589 B）
+→ **2.1.4**（他三句顶回后按效果图落回玻璃＋把四张插画压平成实心；10:54 预览包 753.9KB／772,008 B，与 2.1.2 逐字节相等）
+→ **2.1.5**（他再来三句：白底再毛玻璃 R14／两屏背景图上下跳 R15／默认图换第一张 R16；12:03 预览包 917.6KB／939,606 B，涨的 167,598 B 几乎全是那张 1280×1280 默认形象图）
+2.1.1～2.1.5 都未提审、未上现网；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
 iPhone 同期：1.2(26) 当前</t>
         </is>
       </c>
@@ -4018,7 +4021,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>app.wxss 一组 --glass-* 令牌：veil .30／blur(23px) saturate(1.8)／hairline .55／井底 .20（白条 .38 那一档 10-11 09:2x 起没人吃，见下面「第一屏三块」那一行）；只在铺了形象图那一态（.container.has-bg）生效</t>
+          <t>app.wxss 一组 --glass-* 令牌：veil .30／blur(23px) saturate(1.8)／hairline .55／井底 .20／白条 .38；只在铺了形象图那一态（.container.has-bg）生效</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -4028,7 +4031,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>α=.30 是站长在校准条上点的那一档，全站唯一出口由 `验-玻璃令牌齐不齐` 钉</t>
+          <t>α=.30 是站长在校准条上点的那一档，全站唯一出口由 `验-玻璃令牌齐不齐` 钉；每一枚值与效果图对得上由 `对照-效果图与落码.py` 钉</t>
         </is>
       </c>
     </row>
@@ -4040,17 +4043,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>第一屏那三块的玻璃已撤，退回实心面</t>
+          <t>第一屏那三块＝白底再毛玻璃（白纱 .30 叠在白底 .70 上）</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>撤掉(10-11 真机回电)</t>
+          <t>改版(10-11 R14)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>站长原话「漫画人物边缘外部是透明底，没说连衣服也透明了，ICON 也是」＋R1 后半句「按钮ICON不变」；四张插画自己就是大半透明（ic-person 实心像素只占 0.7%），底下换成 .30 白纱就直接透出照片，实测毛衣 rgb(165,133,123) vs 效果图 rgb(241,238,227)</t>
+          <t>站长原话「首页三个块磨玻璃的背景图换成白底再毛玻璃，否则现在如果背景深色的话，毛玻璃就会很暗，13，12等数字完全看不清」。两层白都挂在同一枚元素的 background 上（简写里 &lt;color&gt; 只许在末层 ⇒ 两层都写成渐变），不另叠定位层；他拍的 .30 一个字没抬，抬的是它下面那层 .70，合成白 .79。两枚白条不吃这一层（它们在块里面，本来就跟着变浅）</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4060,29 +4063,29 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>撤的是我这一轮加的，三块回到 10-10 那版实心面；要恢复这一格只欠「把四张插画压平」那一个决定</t>
+          <t>白底 .70 不是挑的手感：压在**纯黑**照片上面板对字墨 #352E1D 的对比要 ≥ 他 10-10 拍的那版实心面（#C9C1AE 配同一支墨＝7.51），退一档 .60 只剩 6.76 就掉在基准下面。量法＝`探-黑底穿不穿.js`（临时铺一张纯黑进 assets、跑完删）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>列表／我的</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>面板外框与内框合成一张玻璃面</t>
+          <t>头部那张形象图两屏同一个落点（切 tab 不再上下跳）</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>改版(10-11 R15)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>外框＝白纱＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
+          <t>站长原话「我第二，第三切换时候背景图为什么会上下跳到，下面面板高度不变，为什么背景图会跳动，你是否有其他代码影响」。根因：bandGeom 那句 top = -(按宽铺满的高 − 盒子高)×0.15 里带着盒子高，而 R12 那趟给两页各写了一个（列表 740／「我的」646）⇒ 实测顶边差 13.5rpx ≈ 7 视口px。修法：锚点收成全站一枚 poster.HEAD_IMG_H(740)，两页各自带高只管版式、不再递给 bandGeom</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -4092,29 +4095,29 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
+          <t>这是他第二次为同一件事打回（10-01 抓过「同一个人在这页大特写、在那页半身」，当时靠两页同一条 bandGeom 修平）。尺子：探-头部图两页对位.js（改前红 13.5、改后 0.0）＋验-玻璃令牌齐不齐 新增三条与两把反向刀（10→12 把）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>列表</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
+          <t>默认形象图换成站长给的那张</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>改版(10-11 R16)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
+          <t>站长原话「默认图换成第一个图」。assets/home-bg-portrait.jpg 整张换成 1280×1280／314,793 B（原 1116×1920／147,351 B）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -4124,29 +4127,29 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
+          <t>两个连带后果：包涨约 167KB（仍在 2MB 内）；首页那屏是全屏 aspectFill，方图横向裁掉近一半（可见宽 ≈51.8%），两条带子（750×740）几乎不裁。旧那张在 git 里可还原</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+          <t>四张插画压平成实心（穿图的根因）</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>改版(10-11 真机回电后)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
+          <t>站长原话「漫画人物边缘外部是透明底，没说连衣服也透明了，ICON 也是」＋R1 后半句「按钮ICON不变」：那四张 PNG 自己实心像素只占 0.7%～10.4%，底下一半透照片就从画里穿过来。用 docs/工具/烘-插画压平.py 在**调色板模型里**改每枚索引的 alpha 与 RGB，像素索引与原件逐张比对完全相同、轮廓外仍透明、四张字节数与原件逐字相等</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -4156,29 +4159,29 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
+          <t>尺子：量-插画压没压.py 读 alpha 直方图（半透档&gt;0 就红）＋验-第一屏三块-真跑 第 7.5 段钉块面两层与两态</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>三枚居中弹窗改成半透明</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-11)</t>
+          <t>面板外框与内框合成一张玻璃面</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>改版(10-11)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
+          <t>外框＝白纱＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4188,29 +4191,29 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
+          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>详情</t>
+          <t>列表</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>笔记详情浮窗保持实心</t>
+          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>不做(10-11)</t>
+          <t>改版(10-11)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
+          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -4220,29 +4223,29 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>`.float-sheet` 里一条玻璃声明都没有</t>
+          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>卡片</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>大图右下那枚改叫「删除分享图」</t>
+          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>改值(10-10 深夜)</t>
+          <t>改版(10-11)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
+          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4252,29 +4255,29 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
+          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>弹窗</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>两枚计数来自接口</t>
+          <t>三枚居中弹窗改成半透明</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>新增(10-10)</t>
+          <t>新增(10-11)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4284,69 +4287,165 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>详情</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>三块面色随壁纸派生</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-10)</t>
+          <t>笔记详情浮窗保持实心</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>不做(10-11)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>未核</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+          <t>`.float-sheet` 里一条玻璃声明都没有</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>卡片</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>大图右下那枚改叫「删除分享图」</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>改值(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>两枚计数来自接口</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>三块面色随壁纸派生</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>无障碍</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>三块各有读屏名字</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>新增(10-10)</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>role=button + aria-label，念「记下来」／「12笔记」／「12卡片」，词全复用屏上字典键</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>未核</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>渲染层实测读得到（真跑尺子那条 attribute('aria-label')）</t>
         </is>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -519,7 +519,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>全量功能清单 · 总览｜截至 2026-10-11
-小程序：2.0 已过审上线、2.1.1 出包未提审、10-11 毛玻璃一轮走到 2.1.5 预览包（未提审、未上现网）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
+小程序：2.0 已过审上线、2.1.1 出包未提审、10-11 毛玻璃一轮走到 2.1.6 体验版（2.1.7 号已抬、包未出；都没提审、未上现网）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3454,7 +3454,9 @@
 → 2.1.3（他真机第一趟回电：我撤了首页三块玻璃＝错处置，并把「过深」拆成两笔账；09:46 预览包 753.5KB／771,589 B）
 → **2.1.4**（他三句顶回后按效果图落回玻璃＋把四张插画压平成实心；10:54 预览包 753.9KB／772,008 B，与 2.1.2 逐字节相等）
 → **2.1.5**（他再来三句：白底再毛玻璃 R14／两屏背景图上下跳 R15／默认图换第一张 R16；12:03 预览包 917.6KB／939,606 B，涨的 167,598 B 几乎全是那张 1280×1280 默认形象图）
-2.1.1～2.1.5 都未提审、未上现网；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
+→ **2.1.6**（R17 第二屏补「调亮度／换背景」那一行；12:4x `cli upload` 提交体验版 918.0KB／940,012 B，后台「选为体验版」那一下还等他点）
+→ **2.1.7**（R14 纠正：那三块改成「白 .50 单层＋糊」，撤掉我叠错的合成白 .79；包未出——出包与跑尺子属长流程，按他 12:5x 那条新规矩要先申请）
+2.1.1～2.1.7 都没提审、没上现网；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
 iPhone 同期：1.2(26) 当前</t>
         </is>
       </c>
@@ -4043,17 +4045,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>第一屏那三块＝白底再毛玻璃（白纱 .30 叠在白底 .70 上）</t>
+          <t>第一屏那三块＝白底毛玻璃（底色固定成白、半透 .50 单层＋糊）</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>改版(10-11 R14)</t>
+          <t>改版(10-11 R14，12:5x 纠正后)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>站长原话「首页三个块磨玻璃的背景图换成白底再毛玻璃，否则现在如果背景深色的话，毛玻璃就会很暗，13，12等数字完全看不清」。两层白都挂在同一枚元素的 background 上（简写里 &lt;color&gt; 只许在末层 ⇒ 两层都写成渐变），不另叠定位层；他拍的 .30 一个字没抬，抬的是它下面那层 .70，合成白 .79。两枚白条不吃这一层（它们在块里面，本来就跟着变浅）</t>
+          <t>站长原话「首页三个块磨玻璃的背景图换成白底再毛玻璃，否则现在如果背景深色的话，毛玻璃就会很暗，13，12等数字完全看不清」＋12:5x 纠正句「不是加厚白色，是把原来根据背景风格自动切换的底色，换成白色，然后按照半透明毛玻璃进行处理……假如100%白色，半透明50%，也变成毛玻璃」。这三块的面从此固定吃 --glass-plate（白 .50 一层）＋ --glass-bf，不再吃 palette.entryBlocks() 那套随壁纸派生的有色底；他拍的 .30 全站那支没动。两条白条照旧</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4063,7 +4065,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>白底 .70 不是挑的手感：压在**纯黑**照片上面板对字墨 #352E1D 的对比要 ≥ 他 10-10 拍的那版实心面（#C9C1AE 配同一支墨＝7.51），退一档 .60 只剩 6.76 就掉在基准下面。量法＝`探-黑底穿不穿.js`（临时铺一张纯黑进 assets、跑完删）</t>
+          <t>我 11:0x 做成「白纱 .30 叠白 .70」＝合成白 .79，真机上等于半块实心卡纸、没有玻璃味，被他 12:2x 扫出来打回（「怎么又把毛玻璃效果去掉了」）。判据两头钉住：铺图态底色必须是白 .50、background-image 里白色渐变层数必须 &lt;2；对照-效果图与落码.py 那两行同时看图上与码里</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4129,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>两个连带后果：包涨约 167KB（仍在 2MB 内）；首页那屏是全屏 aspectFill，方图横向裁掉近一半（可见宽 ≈51.8%），两条带子（750×740）几乎不裁。旧那张在 git 里可还原</t>
+          <t>两个连带后果：包实测涨 167,598 B（772,008→939,606，仍在 2MB 主包上限内）；首页那屏是全屏 aspectFill，方图横向裁掉近一半（可见宽 ≈51.8%），两条带子（750×740）几乎不裁。旧那张在 git 里可还原。⚠ 这一换还抓出我自己拍的一道旧门槛：`验-首页背景图` 里那条「默认图 &lt;150KB」当天就红（他没下过这条），已改成钉真正有主的那条线＝主包 2MB 上限的八成（现 1.36MB＝上限的 67.9%）</t>
         </is>
       </c>
     </row>
@@ -4139,17 +4141,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>四张插画压平成实心（穿图的根因）</t>
+          <t>「调亮度／换背景」那一行两屏都在（第二屏＝带拍摄面板那一屏）</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>改版(10-11 真机回电后)</t>
+          <t>改版(10-11 R17)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>站长原话「漫画人物边缘外部是透明底，没说连衣服也透明了，ICON 也是」＋R1 后半句「按钮ICON不变」：那四张 PNG 自己实心像素只占 0.7%～10.4%，底下一半透照片就从画里穿过来。用 docs/工具/烘-插画压平.py 在**调色板模型里**改每枚索引的 alpha 与 RGB，像素索引与原件逐张比对完全相同、轮廓外仍透明、四张字节数与原件逐字相等</t>
+          <t>站长原话「调亮度，换背景，再第二屏也需要，第二屏就是带拍摄面板那个。补完，就提交官网体验版」。撤掉 create.wxss 那条 `.container.entry-dock .home-swap{display:none}`（10-08 定的「只在收起态存在」），这一行在展开态照旧画、且顶边与收起态同一个数</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -4159,29 +4161,29 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>尺子：量-插画压没压.py 读 alpha 直方图（半透档&gt;0 就红）＋验-第一屏三块-真跑 第 7.5 段钉块面两层与两态</t>
+          <t>撤它不欠几何账：展开态那一组是 fixed 沉底、不吃流内 margin，所以不会把面板顶高（判据新钉一条「行的底边不压到面板顶」）。四把尺子跟着翻：验-统一录入条／验-录入面板沉底（静态两条从「不渲染」翻成「不许再藏」）＋验-录入面板沉底-真跑／验-首页背景图-真跑。我自己写坏过一条：跨语言拿 zh 的顶边当基准比 en 的六个态 ⇒ 六态整批假红（en 顶边 59.0、zh 63.5，差的是标题行那一句的高度），改成每门语言现取基准</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>面板外框与内框合成一张玻璃面</t>
+          <t>四张插画压平成实心（穿图的根因）</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>改版(10-11 真机回电后)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>外框＝白纱＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
+          <t>站长原话「漫画人物边缘外部是透明底，没说连衣服也透明了，ICON 也是」＋R1 后半句「按钮ICON不变」：那四张 PNG 自己实心像素只占 0.7%～10.4%，底下一半透照片就从画里穿过来。用 docs/工具/烘-插画压平.py 在**调色板模型里**改每枚索引的 alpha 与 RGB，像素索引与原件逐张比对完全相同、轮廓外仍透明、四张字节数与原件逐字相等</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4191,19 +4193,19 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
+          <t>尺子：量-插画压没压.py 读 alpha 直方图（半透档&gt;0 就红）＋验-第一屏三块-真跑 第 7.5 段钉块面两层与两态</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>列表</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
+          <t>面板外框与内框合成一张玻璃面</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -4213,7 +4215,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
+          <t>外框＝白纱＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -4223,19 +4225,19 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
+          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>列表</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -4245,7 +4247,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
+          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4255,29 +4257,29 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
+          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>三枚居中弹窗改成半透明</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-11)</t>
+          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>改版(10-11)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
+          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4287,29 +4289,29 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
+          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>详情</t>
+          <t>弹窗</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>笔记详情浮窗保持实心</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>不做(10-11)</t>
+          <t>三枚居中弹窗改成半透明</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-11)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
+          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4319,29 +4321,29 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>`.float-sheet` 里一条玻璃声明都没有</t>
+          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>卡片</t>
+          <t>详情</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>大图右下那枚改叫「删除分享图」</t>
+          <t>笔记详情浮窗保持实心</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>改值(10-10 深夜)</t>
+          <t>不做(10-11)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
+          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4351,29 +4353,29 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
+          <t>`.float-sheet` 里一条玻璃声明都没有</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>卡片</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>两枚计数来自接口</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-10)</t>
+          <t>大图右下那枚改叫「删除分享图」</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>改值(10-10 深夜)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4383,19 +4385,19 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>三块面色随壁纸派生</t>
+          <t>两枚计数来自接口</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4405,47 +4407,79 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>未核</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>三块面色随壁纸派生</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>无障碍</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>三块各有读屏名字</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>新增(10-10)</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>role=button + aria-label，念「记下来」／「12笔记」／「12卡片」，词全复用屏上字典键</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>未核</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>渲染层实测读得到（真跑尺子那条 attribute('aria-label')）</t>
         </is>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>改版(10-11，13:0x 抬到 .50)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>外框＝白纱＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
+          <t>外框＝白 .50 一层（`--glass-plate`；站长 13:0x 原话「改第二屏面板毛玻璃（三个功能），30变50，与首页一致」，照片／链接／文字三个功能共用这一整面）＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边（他没指，未动）；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -519,7 +519,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>全量功能清单 · 总览｜截至 2026-10-11
-小程序：2.0 已过审上线、2.1.1 出包未提审、10-11 毛玻璃一轮走到 2.1.6 体验版（2.1.7 号已抬、包未出；都没提审、未上现网）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
+小程序：2.0 已过审上线、2.1.1 出包未提审、10-11 毛玻璃一轮走到 2.1.6 体验版（2.1.7／2.1.8 号已抬、两版包都没出；都没提审、未上现网）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3455,8 +3455,9 @@
 → **2.1.4**（他三句顶回后按效果图落回玻璃＋把四张插画压平成实心；10:54 预览包 753.9KB／772,008 B，与 2.1.2 逐字节相等）
 → **2.1.5**（他再来三句：白底再毛玻璃 R14／两屏背景图上下跳 R15／默认图换第一张 R16；12:03 预览包 917.6KB／939,606 B，涨的 167,598 B 几乎全是那张 1280×1280 默认形象图）
 → **2.1.6**（R17 第二屏补「调亮度／换背景」那一行；12:4x `cli upload` 提交体验版 918.0KB／940,012 B，后台「选为体验版」那一下还等他点）
-→ **2.1.7**（R14 纠正：那三块改成「白 .50 单层＋糊」，撤掉我叠错的合成白 .79；包未出——出包与跑尺子属长流程，按他 12:5x 那条新规矩要先申请）
-2.1.1～2.1.7 都没提审、没上现网；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
+→ **2.1.7**（R14 纠正：那三块改成「白 .50 单层＋糊」，撤掉我叠错的合成白 .79；随后 R18 把第二屏那张录入面板也换成 .50。包未出——出包与跑尺子属长流程，按他 12:5x 那条新规矩要先申请）
+→ **2.1.8**（13:2x 四条一起：R19 剪影两态同高／R20 第二屏 Tips 补小圆点／R21 两枚按钮英文改准／R22 抠掉压平压出来的那圈白边。同样**包未出**）
+2.1.1～2.1.8 都没提审、没上现网；2.1.7 与 2.1.8 连预览包都没打过⇒他手上现在没有任何一版能看到这四条；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
 iPhone 同期：1.2(26) 当前</t>
         </is>
       </c>
@@ -4200,22 +4201,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>面板外框与内框合成一张玻璃面</t>
+          <t>压平压出来的那圈白边抠掉（α≤64 那档整枚抠）</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>改版(10-11，13:0x 抬到 .50)</t>
+          <t>改版(10-11 R22)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>外框＝白 .50 一层（`--glass-plate`；站长 13:0x 原话「改第二屏面板毛玻璃（三个功能），30变50，与首页一致」，照片／链接／文字三个功能共用这一整面）＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边（他没指，未动）；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
+          <t>站长原话「首屏，笔记和卡片上面的图片透明底消除不干净，有明显的白边，不美观」。根因在我 09:5x 那一刀：原件轮廓外有一圈 (254,254,254)@α≈5 的柔光（实测 99% 落在贴边 1~2 环），「凡 α&gt;0 就拉满 α」把它变成实心白＝他看到的白边。现加 FAINT_MAX=64：α≤64 那档索引整枚抠掉（连同 10-10 优化进包留下的几像素调色板杂色），α&gt;64 才合成到白；四张重烘进包，字节数与上一版完全相同（P 模式压的是索引图，索引没动⇒压缩流一致，这本身就是「没重画一个像素」的旁证）</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -4225,29 +4226,29 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
+          <t>实测最外环「实心近白」占比 67.1／70.4／82.2／75.6% → 8.6／8.5／20.5／16.6%。尺子加第二条（最外 1px 环近白实心&gt;30% 就红，门槛放在两档实测中间）并反向验过：拿上一版喂进去四条全红、退出码 1。目视自证 docs/design/10-11毛玻璃/实测/白边-边缘放大对比.png（4× 最近邻、贴在真 .50 玻璃面上）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>列表</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
+          <t>右后方那枚剪影两态同高（换人不矮一截）</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>改版(10-11 R19)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
+          <t>站长原话「切换男孩后，右侧女孩高度太低，要与之前右侧男孩高度一致，大人和小人之间距离不要太多，大人和小人的高度差不要太大，他们是男女情侣」。剪影从按宽定（widthFix＋91）改成按高定（heightFix＋132rpx）⇒ 两态同高，宽各自按源件比例倒算（男 91／女 109.7）。132 这个数取的就是他说的「之前右侧男孩」那一档</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4257,29 +4258,29 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
+          <t>高差比值现两态是 0.499（女在前）／0.414（男在前）：男那张源件本就比女高 54，他钉了绝对高度之后男主人那一态必然掉到「一半」以下。要再收小只能抬到 144（⇒0.544／0.450），代价是热区要跟着抬到 ≥130×164、往左多吃 19rpx 主人物的「开门」面——这一格列在需求清单 §10.7 等他拍，我没自己抬。「距离不要太多」自动满足：取景窗 308、主人物 220，两态都是重叠不是留空。两把尺子跟着换口径（旧的两条从 width 倒推高，按高定之后那行不存在），带宽下界 .45→.40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+          <t>第二屏框外那行 Tips 前面补上小圆点</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>改版(10-11 R20)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
+          <t>站长原话「第二屏的 Tips 前面少了小圆点，要与第一屏一致」。`.out` 第一个子加 `.out-dot`，几何五条逐字抄第一屏的 `.tips-dot`（14×14／下 10／右 12／圆），色仍从 tipDotStyle（palette.TIP_DOT）递进来，样式表里不出现第二支黄</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4289,29 +4290,29 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
+          <t>连带一条：`.out` 原来那道 `gap: 20rpx` 分的是「字与返回」，留着它点与字就成 12＋20＝32、与第一屏的 12 对不上 ⇒ 挪到 `.out-r{margin-left:20rpx}`（真跑 H4「框外两枚不打架」照旧成立）。`验-统一录入条` 新增三条钉住（挂着／几何逐字相同／`.out` 不许再有 gap），227→230</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>三枚居中弹窗改成半透明</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-11)</t>
+          <t>「调亮度」「换背景」两枚按钮的英文改准</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>改值(10-11 R21)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
+          <t>站长原话「调亮度，换背景的英文不准确」。homeBgSwap：Change photo → **Background**；bgDimLabel：Dim photo → **Brightness**。旧值那支与档名 modePhoto: 'Photo'（拍照那一档）撞词，而这两枚动的都是背景形象图、不是用户照片；`Dim` 还额外承诺了「只会变暗」，那一排其实是三档可调</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4321,29 +4322,29 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
+          <t>中文侧「换背景」「调亮度」他没指，一字未动。`验-中英文缺口` 61/61；`验-背景亮度圆点` 钉的是「屏上文案==字典现读值」，换值不改判据（43/43）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>详情</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>笔记详情浮窗保持实心</t>
+          <t>面板外框与内框合成一张玻璃面</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>不做(10-11)</t>
+          <t>改版(10-11，13:0x 抬到 .50)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
+          <t>外框＝白 .50 一层（`--glass-plate`；站长 13:0x 原话「改第二屏面板毛玻璃（三个功能），30变50，与首页一致」，照片／链接／文字三个功能共用这一整面）＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边（他没指，未动）；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4353,29 +4354,29 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>`.float-sheet` 里一条玻璃声明都没有</t>
+          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>卡片</t>
+          <t>列表</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>大图右下那枚改叫「删除分享图」</t>
+          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>改值(10-10 深夜)</t>
+          <t>改版(10-11)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
+          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4385,29 +4386,29 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
+          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>两枚计数来自接口</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-10)</t>
+          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>改版(10-11)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4417,69 +4418,197 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>弹窗</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>三块面色随壁纸派生</t>
+          <t>三枚居中弹窗改成半透明</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>新增(10-10)</t>
+          <t>新增(10-11)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>未核</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>详情</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>笔记详情浮窗保持实心</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>不做(10-11)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>`.float-sheet` 里一条玻璃声明都没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>卡片</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>大图右下那枚改叫「删除分享图」</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>改值(10-10 深夜)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>两枚计数来自接口</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>三块面色随壁纸派生</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
           <t>无障碍</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>三块各有读屏名字</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>新增(10-10)</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>role=button + aria-label，念「记下来」／「12笔记」／「12卡片」，词全复用屏上字典键</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>未核</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>渲染层实测读得到（真跑尺子那条 attribute('aria-label')）</t>
         </is>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -3435,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3456,7 +3456,7 @@
 → **2.1.5**（他再来三句：白底再毛玻璃 R14／两屏背景图上下跳 R15／默认图换第一张 R16；12:03 预览包 917.6KB／939,606 B，涨的 167,598 B 几乎全是那张 1280×1280 默认形象图）
 → **2.1.6**（R17 第二屏补「调亮度／换背景」那一行；12:4x `cli upload` 提交体验版 918.0KB／940,012 B，后台「选为体验版」那一下还等他点）
 → **2.1.7**（R14 纠正：那三块改成「白 .50 单层＋糊」，撤掉我叠错的合成白 .79；随后 R18 把第二屏那张录入面板也换成 .50。包未出——出包与跑尺子属长流程，按他 12:5x 那条新规矩要先申请）
-→ **2.1.8**（13:2x 四条一起：R19 剪影两态同高／R20 第二屏 Tips 补小圆点／R21 两枚按钮英文改准／R22 抠掉压平压出来的那圈白边。同样**包未出**）
+→ **2.1.8**（13:2x 四条一起：R19 剪影两态同高／R20 第二屏 Tips 补小圆点／R21 两枚按钮英文改准／R22 抠掉压平压出来的那圈白边；13:5x 再加 R23「原文翻译」那枚的小字注释。同样**包未出**——「同号不叠第二层」那条规矩说的是出过包的号，这一版一次没出过，所以不再抬号）
 2.1.1～2.1.8 都没提审、没上现网；2.1.7 与 2.1.8 连预览包都没打过⇒他手上现在没有任何一版能看到这四条；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
 iPhone 同期：1.2(26) 当前</t>
         </is>
@@ -4270,17 +4270,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>第二屏框外那行 Tips 前面补上小圆点</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>改版(10-11 R20)</t>
+          <t>「原文翻译」那枚开关补一句小字注释</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-11 R23)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>站长原话「第二屏的 Tips 前面少了小圆点，要与第一屏一致」。`.out` 第一个子加 `.out-dot`，几何五条逐字抄第一屏的 `.tips-dot`（14×14／下 10／右 12／圆），色仍从 tipDotStyle（palette.TIP_DOT）递进来，样式表里不出现第二支黄</t>
+          <t>站长原话「原文翻译，后面加小字注释，如，开启后可自动把英文译成中文，描述你帮我优化」＋他点丙案：中文「不管哪种语言，摘要都写成中文」／英文 Summary in Chinese。与开关同一行、两态都在、比名字退一档（--fs-micro ＋ --face-ph）</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>连带一条：`.out` 原来那道 `gap: 20rpx` 分的是「字与返回」，留着它点与字就成 12＋20＝32、与第一屏的 12 对不上 ⇒ 挪到 `.out-r{margin-left:20rpx}`（真跑 H4「框外两枚不打架」照旧成立）。`验-统一录入条` 新增三条钉住（挂着／几何逐字相同／`.out` 不许再有 gap），227→230</t>
+          <t>**他草稿那句没照抄**，两处与代码事实不符：这一枚只切换提示词里「输出语言」那一段（backend/app/services/llm.py 的 _LANG_KEEP／_LANG_ZH）⇒ 改的是标题／摘要／要点／标签用什么语言写，**原文一个字不动**；而且吃的不是只有英文（日文法文同一枚）。英文省掉「不管哪种语言」是容器决定的：Translate original 那 18 个字母按 24rpx 已吃 216rpx，加上就折行。尺子五条新增（227→236）逐条反向验过；行宽中英各算 ≤ 卡内 586（zh 444／en 474），**渲染层没量**</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>首页</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>「调亮度」「换背景」两枚按钮的英文改准</t>
+          <t>第二屏框外那行 Tips 前面补上小圆点</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>改值(10-11 R21)</t>
+          <t>改版(10-11 R20)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>站长原话「调亮度，换背景的英文不准确」。homeBgSwap：Change photo → **Background**；bgDimLabel：Dim photo → **Brightness**。旧值那支与档名 modePhoto: 'Photo'（拍照那一档）撞词，而这两枚动的都是背景形象图、不是用户照片；`Dim` 还额外承诺了「只会变暗」，那一排其实是三档可调</t>
+          <t>站长原话「第二屏的 Tips 前面少了小圆点，要与第一屏一致」。`.out` 第一个子加 `.out-dot`，几何五条逐字抄第一屏的 `.tips-dot`（14×14／下 10／右 12／圆），色仍从 tipDotStyle（palette.TIP_DOT）递进来，样式表里不出现第二支黄</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4322,29 +4322,29 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>中文侧「换背景」「调亮度」他没指，一字未动。`验-中英文缺口` 61/61；`验-背景亮度圆点` 钉的是「屏上文案==字典现读值」，换值不改判据（43/43）</t>
+          <t>连带一条：`.out` 原来那道 `gap: 20rpx` 分的是「字与返回」，留着它点与字就成 12＋20＝32、与第一屏的 12 对不上 ⇒ 挪到 `.out-r{margin-left:20rpx}`（真跑 H4「框外两枚不打架」照旧成立）。`验-统一录入条` 新增三条钉住（挂着／几何逐字相同／`.out` 不许再有 gap），227→230</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>首页</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>面板外框与内框合成一张玻璃面</t>
+          <t>「调亮度」「换背景」两枚按钮的英文改准</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>改版(10-11，13:0x 抬到 .50)</t>
+          <t>改值(10-11 R21)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>外框＝白 .50 一层（`--glass-plate`；站长 13:0x 原话「改第二屏面板毛玻璃（三个功能），30变50，与首页一致」，照片／链接／文字三个功能共用这一整面）＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边（他没指，未动）；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
+          <t>站长原话「调亮度，换背景的英文不准确」。homeBgSwap：Change photo → **Background**；bgDimLabel：Dim photo → **Brightness**。旧值那支与档名 modePhoto: 'Photo'（拍照那一档）撞词，而这两枚动的都是背景形象图、不是用户照片；`Dim` 还额外承诺了「只会变暗」，那一排其实是三档可调</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -4354,29 +4354,29 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
+          <t>中文侧「换背景」「调亮度」他没指，一字未动。`验-中英文缺口` 61/61；`验-背景亮度圆点` 钉的是「屏上文案==字典现读值」，换值不改判据（43/43）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>列表</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
+          <t>面板外框与内框合成一张玻璃面</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>改版(10-11)</t>
+          <t>改版(10-11，13:0x 抬到 .50)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
+          <t>外框＝白 .50 一层（`--glass-plate`；站长 13:0x 原话「改第二屏面板毛玻璃（三个功能），30变50，与首页一致」，照片／链接／文字三个功能共用这一整面）＋模糊；内框底色与描边转透明，控件直接落在玻璃上；井（输入框／右滑条／两枚小圆）＝.20 白＋.55 白边（他没指，未动）；快门橙圆、两枚小圆里的图形、粘贴图形、三枚标签字一行没碰</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4386,19 +4386,19 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
+          <t>`.mini-c` 这一枚类名 10-11 修过一次静默不生效（写成 `.mini .c` 命中零节点）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>列表</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+          <t>卡顶两行字压在玻璃上，往下渐退到实心</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
+          <t>白纱与实心是同一张背景渐变的四个色标（0／158／198／238），中间那档吃本套 bg-card@.62；正文第一行起读数与改之前一致</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4418,29 +4418,29 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
+          <t>158 那一档改由尺子实测两行底边核，不再拿 96＋62 手算</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>三枚居中弹窗改成半透明</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-11)</t>
+          <t>名片那一行压在玻璃上，背景图往下垫 144</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>改版(10-11)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
+          <t>盒子 542→646、卡往上盖 40→144；压暗延段挂在 .head-scrim::after（跟着「调亮度」那枚 opacity 一起沉）</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -4450,29 +4450,29 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
+          <t>他抓过的「中间镂空」这一格由 `验-我的页改版-真跑` 量图底对行底</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>详情</t>
+          <t>弹窗</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>笔记详情浮窗保持实心</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>不做(10-11)</t>
+          <t>三枚居中弹窗改成半透明</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-11)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
+          <t>名片信息／私密密码／我的邮箱各挂 glass-dialog；笔记卡片页那第四处不做——该页根本不铺形象图，模糊没有对象</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4482,29 +4482,29 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>`.float-sheet` 里一条玻璃声明都没有</t>
+          <t>依据与反向钉都在 `验-名片弹窗两页同源`；白纱压暗遮罩后的对比度 10-11 已量（拍甲后六档 5.49／5.17／6.16 全过 AA 4.5）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>卡片</t>
+          <t>详情</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>大图右下那枚改叫「删除分享图」</t>
+          <t>笔记详情浮窗保持实心</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>改值(10-10 深夜)</t>
+          <t>不做(10-11)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
+          <t>站长原话「笔记详情页不用毛玻璃，因为笔记内文字较多要清晰，避免背景干扰」；选卡片模板那一屏与它共用一张皮，他拍「甲」＝同样不做</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -4514,29 +4514,29 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
+          <t>`.float-sheet` 里一条玻璃声明都没有</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>录入</t>
+          <t>卡片</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>两枚计数来自接口</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-10)</t>
+          <t>大图右下那枚改叫「删除分享图」</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>改值(10-10 深夜)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
+          <t>cardDrop：删除 → 删除分享图（英文 Delete card 不动）</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -4546,19 +4546,19 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
+          <t>它是页面里的按钮，不受 showModal 那 4 字上限管</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>录入</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>三块面色随壁纸派生</t>
+          <t>两枚计数来自接口</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -4568,47 +4568,79 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+          <t>getQuota().used 与 getMyCards().cards.length，各包各的 try，读不到画 0</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>未核</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+          <t>口径＝全量；列表页那些数是筛后的，两处不等是正常</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>三块面色随壁纸派生</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-10)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>palette.entryBlocks() 发六枚 --eb-*，样式表里一个色相都不写死</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>只钉得住「字压面 ≥4.5」；「面压照片」没有门槛也没有尺子（规格 §6.2.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
           <t>无障碍</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>三块各有读屏名字</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>新增(10-10)</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>role=button + aria-label，念「记下来」／「12笔记」／「12卡片」，词全复用屏上字典键</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>未核</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>渲染层实测读得到（真跑尺子那条 attribute('aria-label')）</t>
         </is>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>高差比值现两态是 0.499（女在前）／0.414（男在前）：男那张源件本就比女高 54，他钉了绝对高度之后男主人那一态必然掉到「一半」以下。要再收小只能抬到 144（⇒0.544／0.450），代价是热区要跟着抬到 ≥130×164、往左多吃 19rpx 主人物的「开门」面——这一格列在需求清单 §10.7 等他拍，我没自己抬。「距离不要太多」自动满足：取景窗 308、主人物 220，两态都是重叠不是留空。两把尺子跟着换口径（旧的两条从 width 倒推高，按高定之后那行不存在），带宽下界 .45→.40</t>
+          <t>高差比值现两态是 0.499（女在前）／0.414（男在前）：男那张源件本就比女高 54，他钉了绝对高度之后男主人那一态必然掉到「一半」以下。要再收小只能抬到 144（⇒0.544／0.450），代价是热区要跟着抬到 ≥130×164、往左多吃 19rpx 主人物的「开门」面——这一格 **10-11 13:5x 他拍甲「就这样」：132 定死，乙案作废**。「距离不要太多」自动满足：取景窗 308、主人物 220，两态都是重叠不是留空。两把尺子跟着换口径（旧的两条从 width 倒推高，按高定之后那行不存在），带宽下界 .45→.40</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -519,7 +519,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>全量功能清单 · 总览｜截至 2026-10-11
-小程序：2.0 已过审上线、2.1.1 出包未提审、10-11 毛玻璃一轮走到 2.1.6 体验版（2.1.7／2.1.8 号已抬、两版包都没出；都没提审、未上现网）｜iPhone：1.2(26)｜各版本变化见后面分表</t>
+小程序：2.0.1 在线上跑着；2.1.8 已上传并于 10-11 15:22:11 提审（审核中，919.8 KB／941,914 B）；体验版指向哪一版还等他在后台点（12:4x 那份是 2.1.6／940,012 B，2.1.7 一次没出过包）｜iPhone：1.2(27)｜各版本变化见后面分表</t>
         </is>
       </c>
     </row>
@@ -3456,9 +3456,10 @@
 → **2.1.5**（他再来三句：白底再毛玻璃 R14／两屏背景图上下跳 R15／默认图换第一张 R16；12:03 预览包 917.6KB／939,606 B，涨的 167,598 B 几乎全是那张 1280×1280 默认形象图）
 → **2.1.6**（R17 第二屏补「调亮度／换背景」那一行；12:4x `cli upload` 提交体验版 918.0KB／940,012 B，后台「选为体验版」那一下还等他点）
 → **2.1.7**（R14 纠正：那三块改成「白 .50 单层＋糊」，撤掉我叠错的合成白 .79；随后 R18 把第二屏那张录入面板也换成 .50。包未出——出包与跑尺子属长流程，按他 12:5x 那条新规矩要先申请）
-→ **2.1.8**（13:2x 四条一起：R19 剪影两态同高／R20 第二屏 Tips 补小圆点／R21 两枚按钮英文改准／R22 抠掉压平压出来的那圈白边；13:5x 再加 R23「原文翻译」那枚的小字注释。同样**包未出**——「同号不叠第二层」那条规矩说的是出过包的号，这一版一次没出过，所以不再抬号）
-2.1.1～2.1.8 都没提审、没上现网；2.1.7 与 2.1.8 连预览包都没打过⇒他手上现在没有任何一版能看到这四条；现网探针 profile 28/28（10-08 那一趟，后端这一半 10-09 的改动尚未部署）
-iPhone 同期：1.2(26) 当前</t>
+→ **2.1.8**（13:2x 四条一起：R19 剪影两态同高／R20 第二屏 Tips 补小圆点／R21 两枚按钮英文改准／R22 抠掉压平压出来的那圈白边；13:5x 再加 R23「原文翻译」那枚的小字注释。号不叠第二层——那条规矩说的是出过包的号，13:5x 时这一版一次没出过所以不再抬号；**15:2x 真出包时按同号覆盖上架 919.8 KB／941,914 B**，随即 15:22:11 提审）
+包的状态：2.1.8＝**审核中**（15:22:11 提交，同号覆盖 941,914 B）；2.1.7 一次没出过包；12:4x 那份 2.1.6（940,012 B）后台「选为体验版」那一下还等他点⇒**他手机上现在跑哪一版取决于体验版指向，R19～R23 这四条只在 2.1.8 那份包里**
+后端现网：已至第二十二次部署（10-10 08:29，systemd ActiveEnterTimestamp 实测对上）；10-11 逐文件 md5 比出 8 个内容不同 + 2 个现网根本没有（report_ledger／report_retention）⇒第二十三次部署欠账，等 2.1.8 审核结果再一起上。已提审的包不依赖举报接口（前端 grep「举报」零命中）
+iPhone 同期：1.2(27) 当前（扫码进来那一屏只读页已落地）</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.9" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.0" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.2" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -505,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -518,8 +519,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 2026-10-11
-小程序：2.0.1 在线上跑着；2.1.8 已上传并于 10-11 15:22:11 提审（审核中，919.8 KB／941,914 B）；体验版指向哪一版还等他在后台点（12:4x 那份是 2.1.6／940,012 B，2.1.7 一次没出过包）｜iPhone：1.2(27)｜各版本变化见后面分表</t>
+          <t>全量功能清单 · 总览｜截至 2026-10-15（**已封版**：功能不再增减，只做质量迭代）
+小程序：线上 **2.2.0**（后台截图 10-15 20:23，发布 14:35:41）／审核中 **2.2.1**（提交 15:15:02）／开发版本 **2.2.3** 带体验版标（19:22:41，676,290 B）｜iPhone：1.2(27)｜各版本变化见后面分表</t>
         </is>
       </c>
     </row>
@@ -1125,49 +1126,49 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>二维码</t>
+          <t>转存去重</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>真码印上卡片</t>
+          <t>现状：不设「不能转自己的」这种特例——自己那篇照样能再存一份（快照就是那份内容）</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>二维码位系统性留白</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>iPhone 未实现码位</t>
+          <t>⚠ 这一行 10-12 写过「BUG 待修：未判 author==self」，那句是错的：`tests/test_share_snapshot.py` 的 `test_转存自己分享的也走同一条路` 把现状钉成刻意决策，且站长没提过这条；要改属待拍</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>图片备份</t>
+          <t>分享</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>云备份</t>
+          <t>二维码</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2.0 全链：提炼/存图两链并行，存图失败不挡主流程</t>
+          <t>真码印上卡片</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>无（原图只留本机）</t>
+          <t>二维码位系统性留白</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>iPhone 未实现码位</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1180,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>删除清理</t>
+          <t>云备份</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>删笔记/注销回体带 file_ids 清云端对象；本机待删队列</t>
+          <t>2.0 全链：提炼/存图两链并行，存图失败不挡主流程</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>无（原图只留本机）</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1206,12 +1207,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>存储配额</t>
+          <t>删除清理</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>storage-quota 接口＋&gt;90% 提示（免费 5GB 全站合计）</t>
+          <t>删笔记/注销回体带 file_ids 清云端对象；本机待删队列</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1228,27 +1229,27 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>账户</t>
+          <t>图片备份</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>登录</t>
+          <t>存储配额</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>微信 openid→JWT</t>
+          <t>storage-quota 接口＋&gt;90% 提示（免费 5GB 全站合计）</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>无账户，本地优先</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>根本差异；iPhone 数据不出设备</t>
+          <t>小程序独有</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1261,22 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>换设备</t>
+          <t>登录</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>微信跟随，笔记自动在</t>
+          <t>微信 openid→JWT</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>备份导出/导入文件搬（冲突预览）；iCloud 仅预留未上线</t>
+          <t>无账户，本地优先</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>机制不同：账号跟随 vs 文件搬运</t>
+          <t>根本差异；iPhone 数据不出设备</t>
         </is>
       </c>
     </row>
@@ -1287,49 +1288,49 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>名片上云</t>
+          <t>换设备</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2.1 user_profiles：四格形象图/名称一句话/亮度档/模板选套，登录即对齐</t>
+          <t>微信跟随，笔记自动在</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>无（对应物只在本机）</t>
+          <t>备份导出/导入文件搬（冲突预览）；iCloud 仅预留未上线</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2.1.1 出包未提审</t>
+          <t>机制不同：账号跟随 vs 文件搬运</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>账户</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>名片上云</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>外观点色块直接生效；四套莫兰迪＋壁纸</t>
+          <t>2.1 user_profiles：四格形象图/名称一句话/亮度档/模板选套，登录即对齐（2.1.8 已上线）</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>背景照片＋亮度/罩层各三档</t>
+          <t>无（对应物只在本机）</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>iPhone 可用自己照片当背景；小程序是色板体系</t>
+          <t>2.1.8 随线上包发布</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1342,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>界面字体</t>
+          <t>外观</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>三档字体开关（安卓命中率差）</t>
+          <t>五档彩色毛玻璃「心情」：墨／象牙／天青／樱落／雨雾（2.2 起，`utils/palette.js` 的 `MOODS` 一份出口），外加壁纸与那套莫兰迪色板</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>背景照片＋亮度/罩层各三档</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>小程序是「一档翻整套色」，iPhone 可用自己照片当背景</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1369,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>换心情</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>中文</t>
+          <t>首页那枚云朵（`create.wxml` 的 `onCycleMood` → `app.cycleGlassMood()`）一档一档轮，只有壁纸真变时才 PUT</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>中英双语切换</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>iPhone 双语</t>
+          <t>小程序独有</t>
         </is>
       </c>
     </row>
@@ -1395,22 +1396,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>数据管理</t>
+          <t>界面字体</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>无导出入口</t>
+          <t>三档字体开关（安卓命中率差）</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>导出/导入/清空</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>iPhone 独有</t>
+          <t>小程序独有</t>
         </is>
       </c>
     </row>
@@ -1422,74 +1423,128 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>关于页</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>关于内联＋版本号</t>
+          <t>中英双语：首屏右上角那枚角标切，服务端记 `language`（`PUT /api/user/language`）</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>关于页逐条对齐（1.2）</t>
+          <t>中英双语切换</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>内容对齐，形态不同</t>
+          <t>两端都能切；小程序这枚的画法 2.2 改过（撤下划线撤加粗，前面一枚小黄点）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>引导</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>三步指引</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>录入面板三步指引</t>
+          <t>无导出入口</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>无引导页</t>
+          <t>导出/导入/清空</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>iPhone 独有</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>关于页</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>关于内联＋版本号</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>关于页逐条对齐（1.2）</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>内容对齐，形态不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>引导</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>三步指引</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>录入面板三步指引</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>无引导页</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>小程序独有</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
           <t>商业化</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>内购</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>无（xpay 在旧分支未捞）</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>StoreKit 2：买断 ¥69.99＋月订 ¥19.99，先看后买＋恢复购买</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>iPhone 独有</t>
         </is>
@@ -3435,7 +3490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3457,8 +3512,8 @@
 → **2.1.6**（R17 第二屏补「调亮度／换背景」那一行；12:4x `cli upload` 提交体验版 918.0KB／940,012 B，后台「选为体验版」那一下还等他点）
 → **2.1.7**（R14 纠正：那三块改成「白 .50 单层＋糊」，撤掉我叠错的合成白 .79；随后 R18 把第二屏那张录入面板也换成 .50。包未出——出包与跑尺子属长流程，按他 12:5x 那条新规矩要先申请）
 → **2.1.8**（13:2x 四条一起：R19 剪影两态同高／R20 第二屏 Tips 补小圆点／R21 两枚按钮英文改准／R22 抠掉压平压出来的那圈白边；13:5x 再加 R23「原文翻译」那枚的小字注释。号不叠第二层——那条规矩说的是出过包的号，13:5x 时这一版一次没出过所以不再抬号；**15:2x 真出包时按同号覆盖上架 919.8 KB／941,914 B**，随即 15:22:11 提审）
-包的状态：2.1.8＝**审核中**（15:22:11 提交，同号覆盖 941,914 B）；2.1.7 一次没出过包；12:4x 那份 2.1.6（940,012 B）后台「选为体验版」那一下还等他点⇒**他手机上现在跑哪一版取决于体验版指向，R19～R23 这四条只在 2.1.8 那份包里**
-后端现网：已至第二十二次部署（10-10 08:29，systemd ActiveEnterTimestamp 实测对上）；10-11 逐文件 md5 比出 8 个内容不同 + 2 个现网根本没有（report_ledger／report_retention）⇒第二十三次部署欠账，等 2.1.8 审核结果再一起上。已提审的包不依赖举报接口（前端 grep「举报」零命中）
+包的状态：**2.1.8 已上线**（后台实据 10-12 11:00:17）；2.1.9 于 10-12 11:21:32 提审、16:0x 按授权撤回（审核台空着）；2.1.7 一次没出过包
+后端现网：已至**第二十四次部署**（10-12 14:19 私密笔记不登记卡片那道闸，探针 46/46＋51/51＋57/57）；P0-a 运营图后台第二十三次部署已上（探针 9/9，inert）；现网后端＝HEAD 全一致
 iPhone 同期：1.2(27) 当前（扫码进来那一屏只读页已落地）</t>
         </is>
       </c>
@@ -3523,7 +3578,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2.1.1 未提审</t>
+          <t>2.1.8 已上线</t>
         </is>
       </c>
     </row>
@@ -4644,6 +4699,650 @@
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>渲染层实测读得到（真跑尺子那条 attribute('aria-label')）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>私密笔记</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>解锁判据搬出页面</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>迭代(10-12)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>解锁逻辑从页面级抽到公共层；C1–C5 落码＋私密笔记不登记卡片（815 passed）</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>服务端那道闸 10-12 14:19 上现网（第二十四次部署，探针 46/46）；界面五条仍在本地、没出包</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>私密笔记</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>列表响应没有 is_private</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>约束(10-12)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>本机那份字段是猜的，列表 API 实际不返回 is_private</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>判据只能走分类名「私密」，不能靠响应字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>运营后台</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>P0-a 资产管理上线</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-12)</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>管默认背景图＋笔记模板、可上传、全量更新；第二十三次部署上现网（探针 9/9，inert）</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>运营图域名只能 api.agentsbin.cn⇒云开发桶判死；等他：/ops 浏览器实测 + 点发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>拍照只能一张</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>约束(10-12)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>快门排只在零张渲染＋➕ 漏 data-source 发出枚举外值；一行已修</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>相册多选＋拍照</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>他要的连拍缺的只有取景那半，单批 40MB 与 OCR 压缩档位是丙方案的开工前置</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>版本</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2.1.9 提审后撤回</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>事件(10-12)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>11:21:32 提审（944,290 B）→ 16:0x 按授权撤回；审核台现在空着；重提＝重排 1–7 天</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>只剩甲/乙：原样重提 vs 出 2.1.10 带 C1–C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>背景图上文字颜色随深浅自动切换</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>已完成(10-12)，随 2.2.0 上线</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>三个页面有文字压在形象图上：① 列表页（标题/统计数字/搜索栏）② 我的页（关于·设置标签/脑力值）③ 首页（标题/中EN/调亮度·换背景/Tips/三块核心件标签）；canvas 32×32 采样均亮度，&gt;160 判浅色 → .bg-light 翻墨字；localStorage 按路径缓存；导航条同步翻 frontColor</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>**这一行 10-15 重核过两处过期话**：①「已落码未出包」不对了——随 2.2.0 出包并 10-15 14:35:41 上线；②「罩子换浅色提亮」与「applyNavForBand 第二参数」都已整条撤掉（罩层只留压暗那一支；导航条那一枚改成 `palette.js` 的 `navFor()` 按心情档发面与字，10-15 删净）——细节见 2.2 分表</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>自己转存自己的笔记去重</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>待拍（不是待开发的 BUG）</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>现状：`POST /api/notes/from-share` 不判作者本人，自己扫自己那枚码会在自己库里再存一份；这一条被 `tests/test_share_snapshot.py::test_转存自己分享的也走同一条路` 钉成**刻意决策**（原文理由：不设「不能转自己的」这种特例，它就是公开页上那一份内容）</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 10-12 这一行写的是「BUG 待修：转存链路未判 author==self」——那句是**我这边造的**：全仓 grep 没找到站长提过它，而 tests 里反向钉着现状（同 10-15 监督记录第三节那条纪律：全称判断必须含 tests/）。要不要加闸门、提示什么、存量已重复的那几篇怎么办，三条都得他先拍</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2.2.0（10-14 21:27 那份包，10-15 01:12:02 提审、**14:35:41 已上线**）→ 2.2.1（在台上，10-15 15:15:02 提交）→ 2.2.2／2.2.3（各一枚预览码；2.2.3 又 `cli upload` 成开发版本并带体验版标，19:22:41，676,290 B）
+界面主线：五档彩色毛玻璃＋首页「换心情」；顶上那一条通栏反向坡；导航条改跟心情走；面板投影五档同一支；Tips 改后台下发；语言角标改画法；列表与「我的」两屏不再跟随调亮度
+后台那一侧：`/ops` 分「数据／配置」两屏（六张卡＋逐日表）、第三屏「卡片模板」管理栏、与图麦克的换票口（第二十七、二十八次部署已上现网）
+**10-15 深夜站长宣布封版**：功能不再增减，往后只做质量迭代（判据、缺陷、口径、一致性）
+包的状态：线上 2.2.0／审核中 2.2.1／开发版本 2.2.3（三个数取自他 10-15 20:23 那张后台截图，本表不再引 10-12 那句「2.1.8 已上线」——那格到 10-15 已作废）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一级功能点</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>二级功能点</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>本版本状态</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>小程序端</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>iPhone同期</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>两者差异</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>五档彩色毛玻璃＋首页「换心情」</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-14)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>五档＝墨／象牙／天青／樱落／雨雾，各发玻璃本色 `m.glass` 与那条 `band`（`utils/palette.js` 的 `MOODS`，一份出口，`app.wxss` 那五块 `.mood-*` 与它逐字镜像、由 `验-五档彩色玻璃` 钉等值）；首页那枚云朵 `catchtap="onCycleMood"` → `app.cycleGlassMood()` 一档一档轮，只有壁纸真变时才 PUT</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 是那套背景照片体系，没有「一档翻整套色」这枚开关</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>外观</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>面板投影五档同一支算法</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>迭代(10-15)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>`--sh-lift`／`--sh-drop` 六份（`app.wxss` 的 page 兜底＋五块 `.mood-*`）**逐字相同**：`…rgba(18, 20, 26, 0.16)`；墨档那枚 α .42 的特例撤了。他 10-15 真机原话「墨档的阴影过黑，与其他色的阴影不一致。你的算法不一样吗？」——是我不一样。复测：五档压暗各 13.2 格（同一趟可比），改前墨 25.5／彩色 9.8 那 2.6 倍差就是他读出来的「不一致」</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>全站一枚</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>要抬只能六份一起抬成同一个数；单独抬任何一档，`验-五档彩色玻璃`＋`验-玻璃令牌齐不齐` 各红一把（反向刀两把）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>导航条</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>顶上那一条改跟心情走</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>改版(10-15)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>唯一出口 `palette.js` 的 `navFor(key)`：面＝该档玻璃本色，字＝按皮的相对亮度在微信只认的 `#ffffff`／`#000000` 里挑（实读：墨 0.14→白字，其余四档 .65~.70→黑字）；`app.js` 的 `applyTheme` 不再吃 `theme.page`，改调 `applyNav()`；`applyNavForBand` 连同那两枚写死的 `#f2efe9`／`#181a20` 整个删掉</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>状态栏明暗在 App 层定</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>他 10-15 那句「有些是黑底，有些是白底」的根因就是同一条栏有两套真相</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>首屏</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>顶部那一行与那条亮带</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>迭代(10-14→10-15)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>`.ai-line`：`box-shadow: var(--sh-drop)`＋`background: var(--stage-strip)`（`.94→.80@55%→.16`）＋高度压回一行字高；容器顶内缩收到 0（`create.wxss` 的 `.container { padding-top: 0 }`）——导航条翻深色之后，app.wxss 那 `padding: 2rpx …` 顶部一档在导航条底下露成正好 2rpx 的亮带（他真机「为什么顶部有条线，要去掉」；量到 3 设备像素÷1.488＝2rpx）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>未跟</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>笔记页与「我的」页 10-04 就各自收过同一条线，这一屏当时没轮到</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>引导</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Tips 改为后台下发</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-15)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>读 `/api/mp/config` 的 `tips`（`utils/mpAssets.js`，缓存键 `MP_TEXT_KEY_tips`），首屏 `tipsFor(lang)` 远端优先、**包内六句兜底仍在**（`utils/i18n.js` zh／en 各六句），八秒一句；现网那一栏 10-15 18:2x 起是七句新文案（用户侧要下一次冷启才轮到）</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>改文案不发版；他 10-15 那句「帮我把Tips重新整理，并且填上去」已生效（口验到 `/api/mp/config` 回 7/7）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>语言角标改画法</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>改值(10-15)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>撤常驻下划线、撤加粗，前面加一枚小黄点（`#F6C445`，`palette.js` 的 `TIP_DOT` 由 JS 递进样式、不写在 wxss 里）；屏上只写**待切换**那一门（中文态显示 EN、英文态显示「中」）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>双语切换</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>他 10-15 14:0x 原话「中 EN 的下划线去掉，不要加粗，前面加小黄点就行」</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>性能</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>两屏不再跟随「调亮度」</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>迭代(10-15)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>列表页那两个 vtab 与「我的」那两个 seg 改吃 `app.bgSkinLocked()`（＝原图档，不再跟随首页那枚）；按上下两段各自翻色的判定（`utils/imgBrightness.js` 的 `applyTone`）三页都还在——撤的是「跟随」，不是「分段判深浅」</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>他 10-15 09:2x 那四句里的第二句；首页那一屏仍跟随，因为那枚开关就在首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>运营后台</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>「数据」那一栏</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-15)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>`GET /api/admin/stats/overview?days=N`（`services/admin_stats.py`：零新列、零迁移、零埋点、对外文本一行没改）；`/ops` 六张卡＋逐日表，窗口 7／14／30 可切，每个数后面跟一句口径。三条最容易说谎的：预置不计新增、邀请两个数一起回不替判等、日期按 UTC 分桶不擅自换算</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>17:42 第二次上现网时是一列插两行小标题，被他打回「数据分析和配置要分开，你怎么没按你的设计稿来做」；18:04 按方向图重做成两屏（结构也是拍板内容）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>运营后台</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>「卡片模板」那一栏</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-15)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>`GET/PUT /api/admin/poster/templates`（读 60/分、写 30/分）：改中英文名、排序、最低包版本、上架／下架；先全部校验后一次性落笔。**三处刻意为之**：配方只读（P2 没拍开）、`group_key` 只读（那两个分组名出处在客户端）、撞车只报错不自动归档在位那一版</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>P1 原清单里那条「上传后台预览缩略图」没做：表里没那列、画面由客户端手工解释器画，要做得单独拍</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>运营后台</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>一次登录管两个后台（换票）</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>半成品(10-15)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>图麦克拿我们签的那枚票来 `POST /api/admin/verify-token`，凭另一把暗号 `X-Exchange`＝`ADMIN_EXCHANGE_SECRET`（两边 `.env` 同一把：我们这侧 20:58、对面那台 22:44 配的）；三道判据（签名／`scope`／`atk` 指纹）收进 `core/admin_access.py::_decode_admin_ticket()` 一份实现；回体只有 `sub/scope/exp`，签名权不外借；暗号留空＝该口 503</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>**只完成我们这半**：对面还没有来验票的代码，登录仍是两次；`/ops` 顶栏那枚「图麦克」灰着，旁边用一行字写明为什么灰（不许做成「看着能点」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>版本</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2.2 号段与封版</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>事件(10-13～10-15)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>一份包一个号：2.2.0（10-14 21:27 构建，10-15 01:12 提审、14:35 上线，中间 14:16 同号覆盖传过一次）→ 2.2.1（台上）→ 2.2.2、2.2.3 各一枚预览码；`utils/appInfo.js` 的 `VERSION` 与出包那一趟的 `-v` 必须同一个数（这一条踩过三次）</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>「同一号不许叠第二层」是他 10-15 14:2x 拍的；下一份包要从 **2.2.4** 起</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -519,8 +519,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 2026-10-15（**已封版**：功能不再增减，只做质量迭代）
-小程序：线上 **2.2.0**（后台截图 10-15 20:23，发布 14:35:41）／审核中 **2.2.1**（提交 15:15:02）／开发版本 **2.2.3** 带体验版标（19:22:41，676,290 B）｜iPhone：1.2(27)｜各版本变化见后面分表</t>
+          <t>全量功能清单 · 总览｜截至 2026-10-16（**已封版**：功能不再增减，只做质量迭代）
+小程序：线上 **2.2.0**（后台截图 10-15 20:23，发布 14:35:41）／审核中 **2.2.1**（提交 15:15:02，这一格今天没重读）／本地 **2.2.4**、**2.2.5** 各一枚预览码（10-16，未上传未提审）｜iPhone：**1.2(33)**（10-16 一天六批 28→33 复刻 2.2）｜各版本变化见后面分表</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>折叠搜索行（1.2）</t>
+          <t>折叠搜索行；**1.2(29) 把那一排十处照正本对齐**（展开即起键盘、常驻那枚「搜索」、三个收条口、条外空白收条、定高 30pt、放大镜 @.55、字号 14）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>入口形态不同，功能等价</t>
+          <t>入口形态已同；⚠ 那枚「搜索」那边 10-03 就有、这边 10-05 砍早了，**这一批是纠错不是跟新版**</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>排序＋原文翻译（1.9.25）</t>
+          <t>排序＋原文翻译（1.9.25）；10-16 那一枚开关搬到「返回」同一行、三档都在、默认改开</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>无翻译</t>
+          <t>排序有；「原文翻译」开关 **1.2(33) 画上并真落库**——端上 `Translation` 框架整份译成中文，只写「摘要」那一栏</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>翻译小程序独有</t>
+          <t>两边都有、但**不是同一件事**：小程序那一步是云端提炼（把原文压成中文摘要、出要点），iPhone 是端上整份翻译、不压缩不出要点，且要设备装了那一对语言模型才译得动</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>背景照片＋亮度/罩层各三档</t>
+          <t>背景照片＋亮度/罩层各三档；**五档色源这边还没立**（R3），且全仓 0 处模糊材质</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>小程序是「一档翻整套色」，iPhone 可用自己照片当背景</t>
+          <t>小程序是「一档翻整套色」，iPhone 可用自己照片当背景；⚠ 玻璃那层 iOS 只给系统材质档位（ultraThin/thin/regular/thick/chromic），模糊半径与饱和倍数不由我们填＝L1，**逐像素同做不到**</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无——那一行只有两截（调亮度／换背景），第三截没画（R4）</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>小程序独有；他 10-14 那句「白底也要换背景，这是核心功能」那一半 iPhone 已在 1.2(31) 补回，「换心情」这一截仍等他点头（心情落本机还是跟账号走）</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>中英双语切换</t>
+          <t>中英双语：「我的」里一行 → `LanguageView` 三档（跟随系统／English／简体）</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>两端都能切；小程序这枚的画法 2.2 改过（撤下划线撤加粗，前面一枚小黄点）</t>
+          <t>两端都能切；小程序这枚的画法 2.2 改过（撤下划线撤加粗，前面一枚小黄点）。iPhone 那枚角标没跟（R8）：**加角标就成两个口**，撞他自己那条「一个功能只留一个入口」，除非同时撤「我的」那一行</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,8 @@
 → **2.1.8**（13:2x 四条一起：R19 剪影两态同高／R20 第二屏 Tips 补小圆点／R21 两枚按钮英文改准／R22 抠掉压平压出来的那圈白边；13:5x 再加 R23「原文翻译」那枚的小字注释。号不叠第二层——那条规矩说的是出过包的号，13:5x 时这一版一次没出过所以不再抬号；**15:2x 真出包时按同号覆盖上架 919.8 KB／941,914 B**，随即 15:22:11 提审）
 包的状态：**2.1.8 已上线**（后台实据 10-12 11:00:17）；2.1.9 于 10-12 11:21:32 提审、16:0x 按授权撤回（审核台空着）；2.1.7 一次没出过包
 后端现网：已至**第二十四次部署**（10-12 14:19 私密笔记不登记卡片那道闸，探针 46/46＋51/51＋57/57）；P0-a 运营图后台第二十三次部署已上（探针 9/9，inert）；现网后端＝HEAD 全一致
-iPhone 同期：1.2(27) 当前（扫码进来那一屏只读页已落地）</t>
+iPhone 同期：这一窗口走到 **1.2(27)**（10-09 00:43 那一份＝扫码进来那一屏只读页落地）；此后整七天没抬号，10-16 一天六批走到 1.2(33)，见下一张表
+⚠ 这一张表里那些「未核」＝**当时没核**，不是「现在还没做」：10-16 那份 `TumarkNote/ios/复刻清单-小程序2.2-20261016.md` 照 2.2 正本现读答了一部分（右上角那枚＝已跟、那行两截＝入口已补、通栏 Tips＝位置与前缀已对、玻璃＝全仓 0 处），逐条答案在 2.2 分表末尾「iPhone 复刻」那一块</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4954,11 +4955,13 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2.2.0（10-14 21:27 那份包，10-15 01:12:02 提审、**14:35:41 已上线**）→ 2.2.1（在台上，10-15 15:15:02 提交）→ 2.2.2／2.2.3（各一枚预览码；2.2.3 又 `cli upload` 成开发版本并带体验版标，19:22:41，676,290 B）
-界面主线：五档彩色毛玻璃＋首页「换心情」；顶上那一条通栏反向坡；导航条改跟心情走；面板投影五档同一支；Tips 改后台下发；语言角标改画法；列表与「我的」两屏不再跟随调亮度
-后台那一侧：`/ops` 分「数据／配置」两屏（六张卡＋逐日表）、第三屏「卡片模板」管理栏、与图麦克的换票口（第二十七、二十八次部署已上现网）
+          <t>2.2.0（10-14 21:27 那份包，10-15 01:12:02 提审、**14:35:41 已上线**）→ 2.2.1（在台上，10-15 15:15:02 提交）→ 2.2.2／2.2.3（各一枚预览码；2.2.3 又 `cli upload` 成开发版本并带体验版标，19:22:41，676,290 B）→ **2.2.4／2.2.5 各一枚预览码（10-16，没 `cli upload`、没提审）**
+界面主线：五档彩色毛玻璃＋首页「换心情」；顶上那一条通栏反向坡；导航条改跟心情走；面板投影五档同一支；Tips 改后台下发；语言角标改画法；列表与「我的」两屏不再跟随调亮度；10-16 那一刀＝「原文翻译」开关搬到「返回」同一行、三档全局、默认改开，照片那一排第三枚改「粘贴」
+后台那一侧：`/ops` 分「数据／配置」两屏（**10-16 六张卡 → 八张**：加 A4 分类未分类占比＋A9 图片备份健康度，落码未部署）、第三屏「卡片模板」管理栏＋浏览器里跑客户端那份解释器画预览（第三十二次部署已上）、与图麦克的换票口（**10-16 结案：对面四步全上线，现网真点 14 条全过 ⇒ 一次口令进两个后台成立**）
+后端现网：已至**第三十三次部署**（10-16 上午＝四路审计第二批那五条）；四路审计第一批六条 10-16 落码**未部署**（35a2431）
 **10-15 深夜站长宣布封版**：功能不再增减，往后只做质量迭代（判据、缺陷、口径、一致性）
-包的状态：线上 2.2.0／审核中 2.2.1／开发版本 2.2.3（三个数取自他 10-15 20:23 那张后台截图，本表不再引 10-12 那句「2.1.8 已上线」——那格到 10-15 已作废）</t>
+包的状态：线上 2.2.0／审核中 2.2.1／开发版本 2.2.3（这三格取自他 10-15 20:23 那张后台截图，**10-16 没有重读后台**，本地那两个新号只到预览码为止）
+iPhone 同期：**1.2(27) → 1.2(33)**——那边 10-16 02:34～17:53 一天六批复刻这一张表的正本（28 返回＋按下回执真源／29 搜索那一排十处／30 按下回执余下五档／31 白底补回「换背景」入口＋那行的字·墨·图形／32 界面用例补落定等待·屏上零改动／33「原文翻译」开关画上并真落库）；**六批全部只有模拟器断言**，真机只做到编译通过、手点与目视那一笔仍欠</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5020,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无（R3 五档色源还没立；且这边 0 处模糊材质）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>iPhone 是那套背景照片体系，没有「一档翻整套色」这枚开关</t>
+          <t>iPhone 是那套背景照片体系，没有「一档翻整套色」这枚开关。⚠ 就算立了色源，那层玻璃也**只能近似**：iOS 给的是系统材质档位，模糊半径与饱和倍数不由我们填（L1），要他判「近似算不算复刻到位」</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5084,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>状态栏明暗在 App 层定</t>
+          <t>只有一处 `systemChrome` 决定状态栏明暗，**导航条底色没设过**（各页只写 `navigationTitle`）</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>他 10-15 那句「有些是黑底，有些是白底」的根因就是同一条栏有两套真相</t>
+          <t>他 10-15 那句「有些是黑底，有些是白底」的根因就是同一条栏有两套真相。iPhone 那一条跟着心情走（R7）还没做——**这条不是平台限制**：两边都只认黑／白两档字，等价可复刻</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5116,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>未跟</t>
+          <t>未跟（R5：新建页那一行 8 秒轮播的**位置与前缀已对**，差的是那层玻璃与「通栏」两角）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -5145,12 +5148,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无（R11：六句写死在 `AppCopy.swift`，没有任何远程口）</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>改文案不发版；他 10-15 那句「帮我把Tips重新整理，并且填上去」已生效（口验到 `/api/mp/config` 回 7/7）</t>
+          <t>改文案不发版；他 10-15 那句「帮我把Tips重新整理，并且填上去」已生效（口验到 `/api/mp/config` 回 7/7）。iPhone 那一条**能做**（接口在现网、回体形状已核）——要拍的只是「这个配置口要不要公开」，不是 iOS 限制</t>
         </is>
       </c>
     </row>
@@ -5177,12 +5180,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>双语切换</t>
+          <t>双语切换（「我的」里一行 → `LanguageView` 三档：跟随系统／English／简体）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>他 10-15 14:0x 原话「中 EN 的下划线去掉，不要加粗，前面加小黄点就行」</t>
+          <t>他 10-15 14:0x 原话「中 EN 的下划线去掉，不要加粗，前面加小黄点就行」。iPhone 那枚角标没跟（R8）：**这边「我的→语言」那一行也是入口**，加角标就成两个口，除非同时撤那一行——那是替他砍功能，等他点头</t>
         </is>
       </c>
     </row>
@@ -5209,12 +5212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>不适用（罩层仍画在笔记／新建／「我的」三处头图带＝R10 没跟）</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>他 10-15 09:2x 那四句里的第二句；首页那一屏仍跟随，因为那枚开关就在首页</t>
+          <t>他 10-15 09:2x 那四句里的第二句；首页那一屏仍跟随，因为那枚开关就在首页。⚠ iPhone 这一条**不许单独做**：那边撤罩层的同时把字色改成按像素翻极性（R9），只撤罩层不接翻转＝屏上读不动，两条必须同批</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5234,13 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>新增(10-15)</t>
+          <t>新增(10-15)→迭代(10-16)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>`GET /api/admin/stats/overview?days=N`（`services/admin_stats.py`：零新列、零迁移、零埋点、对外文本一行没改）；`/ops` 六张卡＋逐日表，窗口 7／14／30 可切，每个数后面跟一句口径。三条最容易说谎的：预置不计新增、邀请两个数一起回不替判等、日期按 UTC 分桶不擅自换算</t>
+          <t>`GET /api/admin/stats/overview?days=N`（`services/admin_stats.py`：零新列、零迁移、零埋点、对外文本一行没改）；`/ops` 六张卡＋逐日表，窗口 7／14／30 可切，每个数后面跟一句口径。三条最容易说谎的：预置不计新增、邀请两个数一起回不替判等、日期按 UTC 分桶不擅自换算。
+**10-16 六张 → 八张**（他问「你的工作是做后台，下一步是什么」，我点名 A4＋A9，他回一个「动」）：A4 分类健康度（只出四个计数＋一格槽位数，**一个分类名都不列**——分类名是用户写的字）、A9 图片备份健康度（`not_failed()` 复用模型那一枚判据、不写第二份 `or_`；NULL 状态并进「已上传」，`file_size` 为 NULL 单独出一格「体积不知道」，所以屏上明写「这个数是下界，不是精确占用」）；零新列、零迁移。**这一批落码未部署**</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5246,7 +5250,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>17:42 第二次上现网时是一列插两行小标题，被他打回「数据分析和配置要分开，你怎么没按你的设计稿来做」；18:04 按方向图重做成两屏（结构也是拍板内容）</t>
+          <t>17:42 第二次上现网时是一列插两行小标题，被他打回「数据分析和配置要分开，你怎么没按你的设计稿来做」；18:04 按方向图重做成两屏（结构也是拍板内容）。八张那两枚是浏览器真点自证的（本地起 uvicorn＋headless Chrome，读数取自一台一次性空库，不是推断）</t>
         </is>
       </c>
     </row>
@@ -5263,12 +5267,13 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>新增(10-15)</t>
+          <t>新增(10-15)→迭代(10-16)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>`GET/PUT /api/admin/poster/templates`（读 60/分、写 30/分）：改中英文名、排序、最低包版本、上架／下架；先全部校验后一次性落笔。**三处刻意为之**：配方只读（P2 没拍开）、`group_key` 只读（那两个分组名出处在客户端）、撞车只报错不自动归档在位那一版</t>
+          <t>`GET/PUT /api/admin/poster/templates`（读 60/分、写 30/分）：改中英文名、排序、最低包版本、上架／下架；先全部校验后一次性落笔。**三处刻意为之**：配方只读（P2 没拍开）、`group_key` 只读（那两个分组名出处在客户端）、撞车只报错不自动归档在位那一版。
+**10-16 第三十二次部署加了预览**：他一句「卡片模版要增加预览功能」，走的是「浏览器里跑客户端那一份 `poster.js` 解释器现画」，不是上传缩略图——那张图不会跟着配方变（`GET /api/admin/poster/engine` 把源码当数据吐出去，md5 钉住副本）</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5278,7 +5283,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>P1 原清单里那条「上传后台预览缩略图」没做：表里没那列、画面由客户端手工解释器画，要做得单独拍</t>
+          <t>P1 原清单里那条「上传后台预览缩略图」被换成丙案；表里没那列，画面由客户端那份解释器画</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5300,13 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>半成品(10-15)</t>
+          <t>已完成(10-16)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>图麦克拿我们签的那枚票来 `POST /api/admin/verify-token`，凭另一把暗号 `X-Exchange`＝`ADMIN_EXCHANGE_SECRET`（两边 `.env` 同一把：我们这侧 20:58、对面那台 22:44 配的）；三道判据（签名／`scope`／`atk` 指纹）收进 `core/admin_access.py::_decode_admin_ticket()` 一份实现；回体只有 `sub/scope/exp`，签名权不外借；暗号留空＝该口 503</t>
+          <t>图麦克拿我们签的那枚票来 `POST /api/admin/verify-token`，凭另一把暗号 `X-Exchange`＝`ADMIN_EXCHANGE_SECRET`（两边 `.env` 同一把：我们这侧 20:58、对面那台 22:44 配的）；三道判据（签名／`scope`／`atk` 指纹）收进 `core/admin_access.py::_decode_admin_ticket()` 一份实现；回体只有 `sub/scope/exp`，签名权不外借；暗号留空＝该口 503。
+**10-16 结案**：他一句「继续啊，全部做好才跟我说验收」放行对面那条工作区，四步（暗号／换票口／那一页登录改道／登出清两把）代码全落并已部署（容器重建两次），现网真点 14 条全过（两个方向各钉一条），现网探针并进来 45 条全过</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -5310,7 +5316,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>**只完成我们这半**：对面还没有来验票的代码，登录仍是两次；`/ops` 顶栏那枚「图麦克」灰着，旁边用一行字写明为什么灰（不许做成「看着能点」）</t>
+          <t>**不再是「只完成我们这半」**：10-15 那格写的「对面还没来验过票、登录仍是两次」到 10-16 作废；`/ops` 顶栏那枚「图麦克」已经不是灰的</t>
         </is>
       </c>
     </row>
@@ -5327,22 +5333,342 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>事件(10-13～10-15)</t>
+          <t>事件(10-13～10-16)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>一份包一个号：2.2.0（10-14 21:27 构建，10-15 01:12 提审、14:35 上线，中间 14:16 同号覆盖传过一次）→ 2.2.1（台上）→ 2.2.2、2.2.3 各一枚预览码；`utils/appInfo.js` 的 `VERSION` 与出包那一趟的 `-v` 必须同一个数（这一条踩过三次）</t>
+          <t>一份包一个号：2.2.0（10-14 21:27 构建，10-15 01:12 提审、14:35 上线，中间 14:16 同号覆盖传过一次）→ 2.2.1（台上）→ 2.2.2、2.2.3 各一枚预览码 → **2.2.4（10-16 14:38 预览码 679,397 B）→ 2.2.5（10-16 18:13 预览码）**；`utils/appInfo.js` 的 `VERSION` 现读 **2.2.5**，与出包那一趟的 `-v` 必须同一个数（这一条踩过三次）。两个新号**都没 `cli upload`、没提审、没推远端**</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>iPhone 同期 **1.2(27)→1.2(33)**：10-16 一天六批，一批占一个构建号（同样不叠第二层）；`ios/project.yml` 的 `CURRENT_PROJECT_VERSION` 现读 **33**，`MARKETING_VERSION` 仍是 1.2</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>「同一号不许叠第二层」是他 10-15 14:2x 拍的；两边这条一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>「原文翻译」开关上移、三档全局、默认改开</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>迭代(10-16)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>他三刀落在同一句里（§8.279）：① 开关从卡里搬进**框外那一行**、与「返回」同一行（`.out` 的 `justify-content` 由 `flex-end` 换成 `space-between`）；② 撤掉 `active === 'write' &amp;&amp; panelOpen` 那道闸⇒ 链接／照片／文字三档都在；③ 默认由关改**开**（`writeTranslate: true`），提炼完那一趟也复位回开。这一位现在三处都送进提炼请求（链接、照片、文字）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 同期把同一枚开关**从无到有**做了出来（1.2(33)，见下面「iPhone 复刻」那一块）</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>效果不是同一件事：那边这一位改的是**云端提炼**的输出语言（把原文压成中文摘要）；这边没有提炼那一步，走端上系统翻译、整份译、不压缩不出要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>第二屏那一层皮三刀＋照片那排第三枚改「粘贴」</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>迭代(10-16)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>① 输入框改纯白实心、右滑那条改与**底栏那一档本色**同色（新立一枚 `--glass-chrome-dock`，权威出处是 `palette.moodChromeOf(心情).bg`，五档镜像只是影子）；② 墨档那条黑边换成发光；③ 照片那一排第三枚改叫「粘贴」——剪贴板里**只读得到文字**（`wx.getClipboardData` 对 PNG 两个回调六秒一个都不回，实测），所以像链接的串跳「链接」档并填进框、其余文字跳「文字」档接在已打的字后面，三条出口各一句不静默</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>未跟（这一屏的皮三刀那边还没对上）</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>⚠ ①那一刀的根因值得留一句：`.container.has-bg .field/.sld` 两条覆盖一直压住基条，**「改了基条屏上不动」不是没改、是被盖住**——整队删掉而不是再抬权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 复刻</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>右上角那枚＝「返回」（R1）</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>跟版(1.2(28))</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>10-10 深夜那一刀：笔记列表与笔记卡片两枚 tab 共用同一枚「返回」，点下去回新建那一屏</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>1.2(28)（10-16 02:34）撤掉 `listWide`／`toggleWide`／`wideHeadHeight`／`foldButton` 整件，新增 `home-back`＋`goFirstScreen()`；旧的界面用例改写成返回语义，另补三条源码守卫（含「不许复活」的负向钉）；同批立了 `PressFeedback` 真源</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>同形。字色两边同一个 `.72`（正本 `.ix-back` 吃 `--text-secondary`，这边取 `inkSecondary`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 复刻</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>按下回执成档（R2）</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>跟版(1.2(28)→(30))</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>十档透明度（`.vtab` .7／`.ix-back` .6／`.xrow` .66／`.pad` .9／`.srch-go` .66／`.ds-more` .55／`.swap-half` .66／`.mini` .82／`.shutcol` .86／`.th-add` .82）＋全站 `.card:active` `scale(0.988)`</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>1.2(30) 屏上**九档挂齐**（一支正本规则钉一档、每档真被消费），另用一把跨进程取证证明 `.buttonStyle` 确实进了 `PhotosPicker` 内部那颗按钮（那两枚落点不是假挂）</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>没跟的两档各有各的原因：`.pad` 在这边**没有落点**（R14——这边一行只有一个热区，挂上去就是一支没人用的死档）、`.lang-corner` 无此枚（R8）；`scale(.988)` 与 `.menu-item.share-row` 换底色那一族仍欠（L6：哪些元素算「那张卡」要他圈一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 复刻</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>搜索那一排十处（R12）</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>跟版(1.2(29))</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>展开即起键盘（`focus="{{searchOpen}}"`）＋常驻那枚「搜索」＋三个收条口（点行／点分类／点卡片格都收条但留词）＋条外空白＝收条＋清词＋重拉＋定高 30pt、内缩 11pt</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>1.2(29)（06:49）十处一次对齐——头一版清单只有七处，量它的时候又抓出三处：收起那一枚的 label 上写了 `maxWidth: .infinity`，把热区摊成 408pt、图形从右沿挪到屏幕正中；放大镜没接 `.glyph-search{opacity:.55}`；输入框写 13.5 而正本吃 `--fs-body`＝14pt。并撤掉这边多出来那枚「取消」（实测它在一整份 `UITests` 里 0 处引用）</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>**不是跟新版，是纠错**：`.srch-go` 那边 `git log -S` 只有一把 `a8fb0f8`（10-03），而这边是 10-05 A-3 那一批把「搜索笔记」整枚删掉的——当时砍早了</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 复刻</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>白底那一态补回「换背景」入口（R16）＋那行的字·墨·图形（R15）</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>跟版(1.2(31))</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>他 10-14 原话「白底也要换背景，这是核心功能」⇒ 条件从行挪到只有「调亮度」那一枚；10-15 再来一句「调亮度的icon 改为太阳icon」＋「字体小一档，不要加粗」</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1.2(31)（13:26）撤掉整行的 `photoOn` 闸，只有「调亮度」那一枚带自己的条件；②字（10.5pt／400／字距 0.5）、③极性（改走 `inkColor(alpha:fallback:)`，没铺图吃浅墨 .72、铺图吃纸白）、④形状（圆点连外圈整件撤掉、换成同档一支太阳）都跟了；①a 横向也量平——热区左沿实测 `minX`＝7.0＝正本 `left: 14rpx`＝7pt；713/0（654 单元＋59 界面）、反向验证二十六跑全对</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>三处实话：① 用的是 SF Symbol `sun.max`，**不是那边那支 Lucide 1.6 描边的同一张路径**（判据钉的是「画太阳这件事」，不是那条 SVG）；② 「按照片自己那块矩形翻极性」没做（R9，这边没有任何取像素的口子），所以判的是「铺没铺图」不是「那块底亮不亮」；③ 竖向那一格没做（要的是「字的下沿离录入条顶 8pt」那句关系，不是 255pt 那个字面量），它和 R5／R6 抢的是同一格。顺带抓到一条两边英文串早就分岔：这边一直钉着 10-11 被打回的旧值 `Dim photo`／`Change photo`，正本现读是 `Brightness`／`Background`——**钉字面的判据把旧值钉成了正确值，判据自己发现不了，只有回去现读正本才抓得出来**</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 复刻</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>「原文翻译」开关画上并真落库（R17）</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>跟版(1.2(33))</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>10-16 那一刀三条：开关搬进「返回」同一行、三档都在、默认改开（见上一行）；效果走**云端提炼**那一步的输出语言</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>1.2(33)（17:53）位置／三档都在／存完那一篇回开三条照正本；效果那一半走端上——`NaturalLanguage` 认这一段是哪种语言，不是中文就交给 `Translation` 框架整理成简体中文，**只写进「摘要」那一栏**，「原文内容」一个字不动；一支新层（协议＋桩）＋三处落库口子各加一个默认 nil 的位置参数，旧用例一个字没改就继续绿；新判据 19 条＋1 条界面用例，673 单元＋60 界面全绿、反向验证十把全对</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>**他 10-16 否掉了我第一版报的「做不到」**（「翻译开关是必须的，小程序一早就有了，你这个必须加上」）。但两边不是同一件事：那边压成中文摘要、这边整份翻译不压缩。两处没跟：那一行右半的「返回」没画（这边收起已有两枚入口，第三枚撞「一个功能只留一个入口」）、送进引擎的只有前 2000 字。⚠ 这台模拟器**每一对语言都回 `unsupported`**（`canRequestDownloads=false`），「真翻出来是什么样」在这台证明不了，只能在真机等一次验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 复刻</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>界面用例补落定等待（屏上零改动）</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>跟版(1.2(32))</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>「同一号不许叠第二层」是他 10-15 14:2x 拍的；下一份包要从 **2.2.4** 起</t>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>1.2(32)（14:15）那一族「启动后第一下就点／读」的落点补上落定等待（22 处，只增不删），713/0（654＋59）</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>修的是判据本身、不改屏；这一批**做不了反向验证**，那句实话写在交付文档里</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 复刻</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>还没跟的那一摞</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>欠账(10-16)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>五档心情色源／通栏 `.ai-line` 那层玻璃／第一屏三块／语言角标／按像素翻极性／撤两屏罩层／Tips 远程口／取图那一态三枚圈／行首那张图垫</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>R3 五档色源、R4 换心情、R5 通栏那枚的皮、R6 第一屏三块、R8 语言角标、R9 按像素、R10 撤罩层、R11 Tips 下发、R13 三枚圈、R14 行首图垫——**一条没动**</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>四条等他点头（R4 心情落本机还是跟账号走／R6 值不值得动首页那棵树／R8 撤不撤「我的」那一行／R13、R14 会动他拍过的形状）；一条是平台口径要他判：L1 iOS 只给系统材质档位，「近似算不算复刻到位」——不算的话 R3 的玻璃、R5 的皮、R6 的 `.blk-face`、底栏那颗胶囊都只能停在实心面</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 复刻</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>真机那一格</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>欠账(10-16)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>这一路每一批都出一张预览码给他扫，10-11 那轮就是靠真机回电改回来的（R14 纠正、R22 白边都是他手机上读出来的）</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>六批**全部只有模拟器断言**，目视与设备手点一条没有；10-16 18:0x 真机编译第二跑 `** BUILD SUCCEEDED **`（第一跑红在账号与描述文件，不是代码）</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 这一格现在是空的，不许写成已验收：build 15–19 欠的那笔＋「真翻出来的那一份」只能到设备上验</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.0" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.1" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.3 做减法" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,8 +520,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 2026-10-16（**已封版**：功能不再增减，只做质量迭代）
-小程序：线上 **2.2.0**（后台截图 10-15 20:23，发布 14:35:41）／审核中 **2.2.1**（提交 15:15:02，这一格今天没重读）／本地 **2.2.4**、**2.2.5** 各一枚预览码（10-16，未上传未提审）｜iPhone：**1.2(33)**（10-16 一天六批 28→33 复刻 2.2）｜各版本变化见后面分表</t>
+          <t>全量功能清单 · 总览｜截至 **2026-10-18 10:0x**
+小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第二十六次部署**（10-18 02:58，定向一个文件）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
         </is>
       </c>
     </row>
@@ -726,7 +727,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>轻盈化：点＋分类名，铺形象图底，骨架屏</t>
+          <t>**2.3.0 起两张列表并成一张**（笔记列表与卡片列表合一，「不需要跳转」那一轮）：一篇一张卡＋右侧那枚配图封面；封面吃服务端现算的那栏 `cover_file_id`（删掉封面那张会自动换下一张），私密篇一律不画封面</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -736,7 +737,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>视觉结构两套（差异清单 1.x：圆角接缝、半透明、滚动模型）</t>
+          <t>小程序这一趟是**做减法**（撤掉第二个入口）；iPhone 那边这一轮没重读，不替它下结论</t>
         </is>
       </c>
     </row>
@@ -780,7 +781,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>分类行文字下划线式；私密格自动备、有笔记删不掉</t>
+          <t>分类行文字下划线式；私密格自动备、有笔记删不掉；**10-17 起改成面板内管理**（`a2f0141`：＋新增／✕删带二次确认／长按拖动／点空白自动保存／四类默认／名称跟着界面语言自动翻译），⚠ **后端那一半（`5f0b801`）到 10-18 10:0x 仍未上现网**（服务器 alembic 头 `e3a7c91b4f26`，那批要 `b4e8a1c7d205`）</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -790,7 +791,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>样式不同；小程序有私密格保护规则</t>
+          <t>样式不同；小程序有私密格保护规则；**「名称自动翻译」这一件在现网还差服务端那两栏**（切语言不出译名、删除问话不报篇数）</t>
         </is>
       </c>
     </row>
@@ -861,7 +862,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>详情页/详情窗</t>
+          <t>独立一屏 `pages/write`：标题／摘要／要点／标签／分类五栏（**没有「原文」那一栏**，原文只在详情看）；**2.3.7 起这一屏多出「配图」一排**——每张一个 ✕，确认之后逐张删；没图整栏不画；⚠ 他没提「加图」，所以这一屏**没有加图的口**（选图仍只在录入那一屏）；点图也不看大图</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -871,7 +872,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>iPhone 编辑成页更完整；小程序以窗为主</t>
+          <t>文字那几栏 iPhone 多一栏「原文」；**配图能否逐张删是小程序这一侧 2.3.7 新加的**——iPhone 那侧 10-18 10:0x 现读：`ShotImportModel.remove(id)` 只在**导入前**能撤某一张，`DetailView.swift:303` 对已建好的笔记只 `urls(for:).count` 数张数，没有逐张删的口</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1213,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>删笔记/注销回体带 file_ids 清云端对象；本机待删队列</t>
+          <t>删笔记/注销回体带 file_ids 清云端对象；本机待删队列；**2.3.7 起多了「删一张」**：先记待删再发 `DELETE /api/notes/{id}/assets/{数字 id}`，回体就是剩下的那批，没成把预留撤回去（云上那个对象只有客户端删得动）</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1553,6 +1554,521 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2.3.0 ~ 2.3.7（10-17 15:59 ~ 10-18 03:0x）
+**站长 10-15 那句「封版」在这一窗口由他本人松了两次**：10-17「不需要跳转」（分类与列表合一）与 10-18「编辑时，图片要展示，然后支持删除图片」——都是新能力，不是质量迭代。
+包的去向（三档分清）：工具实据＝**2.3.6 与 2.3.7 已传开发版本**（01:55 696,717 B／03:0x 699,157 B，`cli upload` 回 `✔ upload`）；他口述＝**已提审**（02:00 一句「我已经提交审批」、10:0x 一句「我提审了」，都不是 agent 点的）；agent 不知道＝2.3.6 那一单现在撤了还是在台上、体验版挂哪一份、线上号动没动（10-18 两次去读后台都是登录态没了）。
+⚠ 2.3.1~2.3.5 这一路只出过预览码，**真机扫到问题的只有他自己那两次**（编辑页报错、页面错位）；iPhone 那侧这一窗口 agent 没读号（列里写的「未重读」＝10-16 的 1.2(33) 那份现状），只有「配图能否逐张删」与「编辑页字段」这两格是 10-18 10:0x 现读 `TumarkNote/ios` 得来的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一级功能点</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>二级功能点</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>本版本状态</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>小程序端</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>iPhone同期</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>两者差异</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>列表合一</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.3.0)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>笔记列表与卡片列表并成一张（一篇一张卡＋右侧那枚配图封面）；封面由服务端现算一栏 `cover_file_id`，删掉封面那张自动换下一张；私密篇一律不画封面（`ca610f7`／`1848649`，同日第三十四次部署）</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>小程序主动撤掉第二个入口（做减法）；iPhone 这一窗口没读，不替它下结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>卡距与卡影</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.3.1)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>照他那张参考原件收薄：卡距抬到 28rpx、卡影换薄那一枚（10-17「阴影太厚、几乎连起来」，`5eef64e`）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>视觉档，小程序这侧的数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>列表打不开</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>修复(2.3.1)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>`formatDate` 一直没进 `date.js` 的出口 ⇒ 列表那一趟当场挂（真机报 `Load failed`），补进出口（`b8a25b1`）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>搜索那一态</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.3.3)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>拆成两枚＋两处输入框换淡皮（10-17 夜两句：「点笔记返回后搜索框清不掉」与「搜索框太深，改成邮箱那种淡框深字」，`dc77466`）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>1.2(29) 那批已把那一排十处照正本对齐</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>入口形态已同（这一格是 10-16 的读数，未重读）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>详情窗配图</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.3.3)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>详情窗补配图那一排＋卡片那一格撤白垫＋一枚「分享笔记」＋开窗不再钉死模板（`205c2a9`）</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>详情窗抬头</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.3.4)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>撤两列分栏与那排小方格，换通栏固定高大图＋数字＋圆点横杠＋标签弱化（`0a9399f`）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>看大图退回来跌回列表</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>修复(2.3.5)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>`wx.previewImage` 开在新页面里，关掉＝切回这一屏 ⇒ 平台补发一次 `onShow`，而那一趟里有一句 `_closeFloats()` 把窗自己收了；改成出去前记一格「为看大图才出去的」、只放过那一趟（`62623ad`，他 10-17 23:1x 一句「那条 BUG 没修」）</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>平台行为（原生层回来补发 onShow），不是我们写的跳转</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>两句话术</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.3.5)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>「分享笔记」→「分享」；「分享卡片：…」→「分享到：…」</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>分类改面板内管理</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.3.x 10-17)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>前端那一半 `a2f0141`：＋新增／✕删（带二次确认）／长按拖动／点空白自动保存／四类默认／名称跟着界面语言自动翻译（规则只在 `utils/catText.js` 一份）。⚠ 后端那一半 `5f0b801`（迁移 `b4e8a1c7d205`）**到 10-18 10:0x 仍未上现网**——现读服务器 `alembic current` = `e3a7c91b4f26 (head)`</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>**「名称自动翻译」这一件在现网还差服务端那两栏**：症状＝切语言不出译名、删除问话不报篇数、新用户默认四格看不见</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>图片设置那一层</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.3.6)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>层名从「卡片上的信息」改成「图片设置」；卡里两枚芯片按他念的次序＝上「背景」下「头像」；首页那枚「换背景」就地拉起这一层、不再跳设置（`a5521c6`，他 10-18 凌晨两句）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>界面</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>遮罩不压暗＋报错气泡</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.3.6)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>`.ci-mask` 从 `rgba(20,20,28,.55)` 换成不涂色＋`--glass-bf` 毛玻璃；报错气泡换白底／深灰字／不加粗＋阴影浮起＋抖一抖（`2fd49c3`。这一刀翻掉他 10-11 逐条裁定那版的 §6.4，所以那三枚字面色连 `.container.has-bg` 那条暗纱覆盖一起撤，撤完两态同一个值）</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>编辑页一进门弹「加载失败」</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>修复(2.3.7)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>`write.js` 的 `normTags` 是给「两头同一把尺」写的，可它只折非数组那一支，库里那个**数组**原样交给 `.split` ⇒ `TypeError` 被 catch 接住成「加载失败」；抛点在建基线那一行、**排在 setData 之后**，所以症状是他那两张图的样子：五栏字都铺出来了、却弹一句报错（`2742ea0`，10-18 02:0x 他真机抓到）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>未重读</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>编辑这一屏的配图</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.3.7)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>分类那一栏后面多出「配图」一排：方格定宽又定高＋每枚右上角一只 ✕；确认后才删；没图整栏不画；**他没提「加图」，所以这一屏没有加图的口**（选图仍只在录入那一屏），点图也不看大图。二次确认复用删一篇那两句（`confirmDelete`／`cannotRestore`），**i18n 零新键**（`9104aeb`）</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>10-18 10:0x 现读：`ShotImportModel.remove(id)` 只在**导入前**能撤某一张；`DetailView.swift:303` 对已建好的笔记只 `urls(for:).count` 数张数</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>**「笔记建好之后逐张删配图」这一件是小程序这一侧 2.3.7 新加的，iPhone 那侧没有这个口**（现读，不是推测）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>图片备份</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>删一张</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.3.7)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>后端 `DELETE /api/notes/{note_id}/assets/{asset_id}`（**路径带的是那一行的数字 id 不是 fileID**： `cloud://…` 里全是斜杠，塞进路径段会被多切两截＝路由层通用 404，第一版就是这么错的）。归属：不是这篇／不是这个号一律 404 不回 403；私密篇没解锁 403。回的是**剩下的那批**，界面拿它直接刷那一排。**10-18 02:58 第二十六次部署已上现网**（定向一个文件，传前核过「服务器那份与本地改动前那份 md5 一字不差」；探针 49/49）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>不适用（那侧图片不出设备）</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>小程序独有；次序是同一条：先记待删再发请求，没成撤回去</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -521,7 +521,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>全量功能清单 · 总览｜截至 **2026-10-18 10:0x**
-小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第二十六次部署**（10-18 02:58，定向一个文件）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
+小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第三十六次部署**（10-18 02:58，定向一个文件）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>后端 `DELETE /api/notes/{note_id}/assets/{asset_id}`（**路径带的是那一行的数字 id 不是 fileID**： `cloud://…` 里全是斜杠，塞进路径段会被多切两截＝路由层通用 404，第一版就是这么错的）。归属：不是这篇／不是这个号一律 404 不回 403；私密篇没解锁 403。回的是**剩下的那批**，界面拿它直接刷那一排。**10-18 02:58 第二十六次部署已上现网**（定向一个文件，传前核过「服务器那份与本地改动前那份 md5 一字不差」；探针 49/49）</t>
+          <t>后端 `DELETE /api/notes/{note_id}/assets/{asset_id}`（**路径带的是那一行的数字 id 不是 fileID**： `cloud://…` 里全是斜杠，塞进路径段会被多切两截＝路由层通用 404，第一版就是这么错的）。归属：不是这篇／不是这个号一律 404 不回 403；私密篇没解锁 403。回的是**剩下的那批**，界面拿它直接刷那一排。**10-18 02:58 第三十六次部署已上现网**（定向一个文件，传前核过「服务器那份与本地改动前那份 md5 一字不差」；探针 49/49）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -857,22 +857,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>编辑</t>
+          <t>新用户默认那一篇</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>独立一屏 `pages/write`：标题／摘要／要点／标签／分类五栏（**没有「原文」那一栏**，原文只在详情看）；**2.3.7 起这一屏多出「配图」一排**——每张一个 ✕，确认之后逐张删；没图整栏不画；⚠ 他没提「加图」，所以这一屏**没有加图的口**（选图仍只在录入那一屏）；点图也不看大图</t>
+          <t>**服务端在建号那一次**存进一篇产品说明：种子是 `backend/seed/preset_note.json`（标题「你收藏过的 200 条，为什么一条都找不到？」、标签「产品说明」、五条要点＋716 字正文，正文不走模型、不烧提炼额度）；来源栏念「自带」；能编辑、能分享、能设私密，但**删不掉**（站长 10-14「默认的不能删除」）；删了也不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效：到 10-18 10:0x 库里 6 行，六个新账号名下各正好一篇</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>编辑页全字段（标题/摘要/要点/标签/原文）</t>
+          <t>有，但不是同一件事：`DemoData.swift` 是**六条演示笔记**，`NoteStore` 起手 `seedIfEmpty` 灌进第一份本地库，固定 UUID、吃灌库那一刻的界面语言（切语言不改用户已有数据）——那是给用户看的样例，不是产品说明</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>文字那几栏 iPhone 多一栏「原文」；**配图能否逐张删是小程序这一侧 2.3.7 新加的**——iPhone 那侧 10-18 10:0x 现读：`ShotImportModel.remove(id)` 只在**导入前**能撤某一张，`DetailView.swift:303` 对已建好的笔记只 `urls(for:).count` 数张数，没有逐张删的口</t>
+          <t>小程序灌**一条真说明**（服务端建、跟账号走、删不掉）；iPhone 灌**六条样例**（本机建、能删）。⚠ 配套那条「首启自动出的一张卡片」在现网**没有读数**：10-18 10:0x 查 `note_cards`，这六个新账号名下 0 行（客户端那条链是设计成「让位就不出声」的，服务器侧看不到）⇒ 这一半不许报成已生效</t>
         </is>
       </c>
     </row>
@@ -884,49 +884,49 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>排序与翻译</t>
+          <t>编辑</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>排序＋原文翻译（1.9.25）；10-16 那一枚开关搬到「返回」同一行、三档都在、默认改开</t>
+          <t>独立一屏 `pages/write`：标题／摘要／要点／标签／分类五栏（**没有「原文」那一栏**，原文只在详情看）；**2.3.7 起这一屏多出「配图」一排**——每张一个 ✕，确认之后逐张删；没图整栏不画；⚠ 他没提「加图」，所以这一屏**没有加图的口**（选图仍只在录入那一屏）；点图也不看大图</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>排序有；「原文翻译」开关 **1.2(33) 画上并真落库**——端上 `Translation` 框架整份译成中文，只写「摘要」那一栏</t>
+          <t>编辑页全字段（标题/摘要/要点/标签/原文）</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>两边都有、但**不是同一件事**：小程序那一步是云端提炼（把原文压成中文摘要、出要点），iPhone 是端上整份翻译、不压缩不出要点，且要设备装了那一对语言模型才译得动</t>
+          <t>文字那几栏 iPhone 多一栏「原文」；**配图能否逐张删是小程序这一侧 2.3.7 新加的**——iPhone 那侧 10-18 10:0x 现读：`ShotImportModel.remove(id)` 只在**导入前**能撤某一张，`DetailView.swift:303` 对已建好的笔记只 `urls(for:).count` 数张数，没有逐张删的口</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>卡片模板</t>
+          <t>笔记管理</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>模板来源</t>
+          <t>排序与翻译</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>包内十套兜底＋服务端配方下发（2.0 已开闸，十套 live）</t>
+          <t>排序＋原文翻译（1.9.25）；10-16 那一枚开关搬到「返回」同一行、三档都在、默认改开</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>4 免费＋6 订阅；远程模板包（签名验证）</t>
+          <t>排序有；「原文翻译」开关 **1.2(33) 画上并真落库**——端上 `Translation` 框架整份译成中文，只写「摘要」那一栏</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>商业模式不同：小程序全免费、iPhone 六套要订阅</t>
+          <t>两边都有、但**不是同一件事**：小程序那一步是云端提炼（把原文压成中文摘要、出要点），iPhone 是端上整份翻译、不压缩不出要点，且要设备装了那一对语言模型才译得动</t>
         </is>
       </c>
     </row>
@@ -938,22 +938,22 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>挑选交互</t>
+          <t>模板来源</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>十枚圆点＋左右滑</t>
+          <t>包内十套兜底＋服务端配方下发（2.0 已开闸，十套 live）</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>缩略图条</t>
+          <t>4 免费＋6 订阅；远程模板包（签名验证）</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>交互不同</t>
+          <t>商业模式不同：小程序全免费、iPhone 六套要订阅</t>
         </is>
       </c>
     </row>
@@ -965,22 +965,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>预览</t>
+          <t>挑选交互</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>页内浮层窗</t>
+          <t>十枚圆点＋左右滑</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>全屏 sheet</t>
+          <t>缩略图条</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>形态不同</t>
+          <t>交互不同</t>
         </is>
       </c>
     </row>
@@ -992,22 +992,22 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>生成与保存</t>
+          <t>预览</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>存到相册；2.0.1 起生成即上云留档（note_cards）</t>
+          <t>页内浮层窗</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>渲染＋保存相册（仅新增写入权限）＋本机台账 PNG</t>
+          <t>全屏 sheet</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>小程序云端留档换机还在，iPhone 台账只在本机</t>
+          <t>形态不同</t>
         </is>
       </c>
     </row>
@@ -1019,22 +1019,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>形象图上卡</t>
+          <t>生成与保存</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>人像彩色整幅（1.2.0）等玩法</t>
+          <t>存到相册；2.0.1 起生成即上云留档（note_cards）</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>渲染＋保存相册（仅新增写入权限）＋本机台账 PNG</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>小程序云端留档换机还在，iPhone 台账只在本机</t>
         </is>
       </c>
     </row>
@@ -1046,49 +1046,49 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>模板更新</t>
+          <t>形象图上卡</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>配方下发即生效，不发版</t>
+          <t>人像彩色整幅（1.2.0）等玩法</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>模板更新红点提示</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>各自机制</t>
+          <t>小程序独有</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>分享</t>
+          <t>卡片模板</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>渠道</t>
+          <t>模板更新</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>通栏「微信好友/朋友圈/公众号」＋微信图片分享面板</t>
+          <t>配方下发即生效，不发版</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>UIActivityViewController 系统面板</t>
+          <t>模板更新红点提示</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>小程序走微信场景，iPhone 走系统面板（可到任意 App）</t>
+          <t>各自机制</t>
         </is>
       </c>
     </row>
@@ -1100,22 +1100,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>活码与撤回</t>
+          <t>渠道</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>一篇一张码、公开/不公开开关、撤回</t>
+          <t>通栏「微信好友/朋友圈/公众号」＋微信图片分享面板</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>无链接分享</t>
+          <t>UIActivityViewController 系统面板</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>小程序走微信场景，iPhone 走系统面板（可到任意 App）</t>
         </is>
       </c>
     </row>
@@ -1127,22 +1127,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>转存去重</t>
+          <t>活码与撤回</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>现状：不设「不能转自己的」这种特例——自己那篇照样能再存一份（快照就是那份内容）</t>
+          <t>一篇一张码、公开/不公开开关、撤回</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无链接分享</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>⚠ 这一行 10-12 写过「BUG 待修：未判 author==self」，那句是错的：`tests/test_share_snapshot.py` 的 `test_转存自己分享的也走同一条路` 把现状钉成刻意决策，且站长没提过这条；要改属待拍</t>
+          <t>小程序独有</t>
         </is>
       </c>
     </row>
@@ -1154,49 +1154,49 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>二维码</t>
+          <t>转存去重</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>真码印上卡片</t>
+          <t>现状：不设「不能转自己的」这种特例——自己那篇照样能再存一份（快照就是那份内容）</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>二维码位系统性留白</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>iPhone 未实现码位</t>
+          <t>⚠ 这一行 10-12 写过「BUG 待修：未判 author==self」，那句是错的：`tests/test_share_snapshot.py` 的 `test_转存自己分享的也走同一条路` 把现状钉成刻意决策，且站长没提过这条；要改属待拍</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>图片备份</t>
+          <t>分享</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>云备份</t>
+          <t>二维码</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2.0 全链：提炼/存图两链并行，存图失败不挡主流程</t>
+          <t>真码印上卡片</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>无（原图只留本机）</t>
+          <t>二维码位系统性留白</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>iPhone 未实现码位</t>
         </is>
       </c>
     </row>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>删除清理</t>
+          <t>云备份</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>删笔记/注销回体带 file_ids 清云端对象；本机待删队列；**2.3.7 起多了「删一张」**：先记待删再发 `DELETE /api/notes/{id}/assets/{数字 id}`，回体就是剩下的那批，没成把预留撤回去（云上那个对象只有客户端删得动）</t>
+          <t>2.0 全链：提炼/存图两链并行，存图失败不挡主流程</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>无（原图只留本机）</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>存储配额</t>
+          <t>删除清理</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>storage-quota 接口＋&gt;90% 提示（免费 5GB 全站合计）</t>
+          <t>删笔记/注销回体带 file_ids 清云端对象；本机待删队列；**2.3.7 起多了「删一张」**：先记待删再发 `DELETE /api/notes/{id}/assets/{数字 id}`，回体就是剩下的那批，没成把预留撤回去（云上那个对象只有客户端删得动）</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1257,27 +1257,27 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>账户</t>
+          <t>图片备份</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>登录</t>
+          <t>存储配额</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>微信 openid→JWT</t>
+          <t>storage-quota 接口＋&gt;90% 提示（免费 5GB 全站合计）</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>无账户，本地优先</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>根本差异；iPhone 数据不出设备</t>
+          <t>小程序独有</t>
         </is>
       </c>
     </row>
@@ -1289,22 +1289,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>换设备</t>
+          <t>登录</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>微信跟随，笔记自动在</t>
+          <t>微信 openid→JWT</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>备份导出/导入文件搬（冲突预览）；iCloud 仅预留未上线</t>
+          <t>无账户，本地优先</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>机制不同：账号跟随 vs 文件搬运</t>
+          <t>根本差异；iPhone 数据不出设备</t>
         </is>
       </c>
     </row>
@@ -1316,49 +1316,49 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>名片上云</t>
+          <t>换设备</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2.1 user_profiles：四格形象图/名称一句话/亮度档/模板选套，登录即对齐（2.1.8 已上线）</t>
+          <t>微信跟随，笔记自动在</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>无（对应物只在本机）</t>
+          <t>备份导出/导入文件搬（冲突预览）；iCloud 仅预留未上线</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2.1.8 随线上包发布</t>
+          <t>机制不同：账号跟随 vs 文件搬运</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>账户</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>外观</t>
+          <t>名片上云</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>五档彩色毛玻璃「心情」：墨／象牙／天青／樱落／雨雾（2.2 起，`utils/palette.js` 的 `MOODS` 一份出口），外加壁纸与那套莫兰迪色板</t>
+          <t>2.1 user_profiles：四格形象图/名称一句话/亮度档/模板选套，登录即对齐（2.1.8 已上线）</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>背景照片＋亮度/罩层各三档；**五档色源这边还没立**（R3），且全仓 0 处模糊材质</t>
+          <t>无（对应物只在本机）</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>小程序是「一档翻整套色」，iPhone 可用自己照片当背景；⚠ 玻璃那层 iOS 只给系统材质档位（ultraThin/thin/regular/thick/chromic），模糊半径与饱和倍数不由我们填＝L1，**逐像素同做不到**</t>
+          <t>2.1.8 随线上包发布</t>
         </is>
       </c>
     </row>
@@ -1370,22 +1370,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>换心情</t>
+          <t>外观</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>首页那枚云朵（`create.wxml` 的 `onCycleMood` → `app.cycleGlassMood()`）一档一档轮，只有壁纸真变时才 PUT</t>
+          <t>五档彩色毛玻璃「心情」：墨／象牙／天青／樱落／雨雾（2.2 起，`utils/palette.js` 的 `MOODS` 一份出口），外加壁纸与那套莫兰迪色板</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>无——那一行只有两截（调亮度／换背景），第三截没画（R4）</t>
+          <t>背景照片＋亮度/罩层各三档；**五档色源这边还没立**（R3），且全仓 0 处模糊材质</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>小程序独有；他 10-14 那句「白底也要换背景，这是核心功能」那一半 iPhone 已在 1.2(31) 补回，「换心情」这一截仍等他点头（心情落本机还是跟账号走）</t>
+          <t>小程序是「一档翻整套色」，iPhone 可用自己照片当背景；⚠ 玻璃那层 iOS 只给系统材质档位（ultraThin/thin/regular/thick/chromic），模糊半径与饱和倍数不由我们填＝L1，**逐像素同做不到**</t>
         </is>
       </c>
     </row>
@@ -1397,22 +1397,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>界面字体</t>
+          <t>换心情</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>三档字体开关（安卓命中率差）</t>
+          <t>首页那枚云朵（`create.wxml` 的 `onCycleMood` → `app.cycleGlassMood()`）一档一档轮，只有壁纸真变时才 PUT</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无——那一行只有两截（调亮度／换背景），第三截没画（R4）</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>小程序独有；他 10-14 那句「白底也要换背景，这是核心功能」那一半 iPhone 已在 1.2(31) 补回，「换心情」这一截仍等他点头（心情落本机还是跟账号走）</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>界面字体</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>中英双语：首屏右上角那枚角标切，服务端记 `language`（`PUT /api/user/language`）</t>
+          <t>三档字体开关（安卓命中率差）</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>中英双语：「我的」里一行 → `LanguageView` 三档（跟随系统／English／简体）</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>两端都能切；小程序这枚的画法 2.2 改过（撤下划线撤加粗，前面一枚小黄点）。iPhone 那枚角标没跟（R8）：**加角标就成两个口**，撞他自己那条「一个功能只留一个入口」，除非同时撤「我的」那一行</t>
+          <t>小程序独有</t>
         </is>
       </c>
     </row>
@@ -1451,22 +1451,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>数据管理</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>无导出入口</t>
+          <t>中英双语：首屏右上角那枚角标切，服务端记 `language`（`PUT /api/user/language`）</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>导出/导入/清空</t>
+          <t>中英双语：「我的」里一行 → `LanguageView` 三档（跟随系统／English／简体）</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>iPhone 独有</t>
+          <t>两端都能切；小程序这枚的画法 2.2 改过（撤下划线撤加粗，前面一枚小黄点）。iPhone 那枚角标没跟（R8）：**加角标就成两个口**，撞他自己那条「一个功能只留一个入口」，除非同时撤「我的」那一行</t>
         </is>
       </c>
     </row>
@@ -1478,74 +1478,101 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>关于页</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>关于内联＋版本号</t>
+          <t>无导出入口</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>关于页逐条对齐（1.2）</t>
+          <t>导出/导入/清空</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>内容对齐，形态不同</t>
+          <t>iPhone 独有</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>引导</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>三步指引</t>
+          <t>关于页</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>录入面板三步指引</t>
+          <t>关于内联＋版本号</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>无引导页</t>
+          <t>关于页逐条对齐（1.2）</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>小程序独有</t>
+          <t>内容对齐，形态不同</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>引导</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>三步指引</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>录入面板三步指引</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>无引导页</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>小程序独有</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>商业化</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>内购</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>无（xpay 在旧分支未捞）</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>StoreKit 2：买断 ¥69.99＋月订 ¥19.99，先看后买＋恢复购买</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>iPhone 独有</t>
         </is>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -520,8 +520,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 **2026-10-18 10:0x**
-小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第三十六次部署**（10-18 02:58，定向一个文件）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
+          <t>全量功能清单 · 总览｜截至 **2026-10-18 11:5x**（这一趟只刷新服务器那几格；小程序后台与 iPhone 那侧没重读）
+小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第三十七次部署**（10-18 11:2x，定向八份文件＝四个后端＋四份预览引擎镜像副本；探针 22/22；11:3x 接着按他「老账户也补」给 70 个老号各补了那一篇预置笔记）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>**服务端在建号那一次**存进一篇产品说明：种子是 `backend/seed/preset_note.json`（标题「你收藏过的 200 条，为什么一条都找不到？」、标签「产品说明」、五条要点＋716 字正文，正文不走模型、不烧提炼额度）；来源栏念「自带」；能编辑、能分享、能设私密，但**删不掉**（站长 10-14「默认的不能删除」）；删了也不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效：到 10-18 10:0x 库里 6 行，六个新账号名下各正好一篇</t>
+          <t>**服务端在建号那一次**存进一篇产品说明；**10-18 起这份文案归后台管**（`/ops` 里「默认笔记」那一栏五个字段可编辑——改它既不用发版也不用部署；生效值存在库里那一行，库里没有或形状不合格才落回 `backend/seed/preset_note.json`）；当前那份是标题「你收藏过的 200 条，为什么一条都找不到？」、标签「产品说明」、五条要点＋716 字正文，正文不走模型、不烧提炼额度；来源栏念「自带」；能编辑、能分享、能设私密，但**删不掉**（站长 10-14「默认的不能删除」）；新号删了也不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效；**10-18 11:3x 站长拍「老账户也补」：70 个老号一次性各补一篇**（走同一只生产函数、幂等重跑新增 0），库里 `source_type='preset'` 由 6 行 → **76 行**，76 个号名下各正好一篇</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>小程序灌**一条真说明**（服务端建、跟账号走、删不掉）；iPhone 灌**六条样例**（本机建、能删）。⚠ 配套那条「首启自动出的一张卡片」在现网**没有读数**：10-18 10:0x 查 `note_cards`，这六个新账号名下 0 行（客户端那条链是设计成「让位就不出声」的，服务器侧看不到）⇒ 这一半不许报成已生效</t>
+          <t>小程序灌**一条真说明**（服务端建、跟账号走、删不掉、文案后台可改）；iPhone 灌**六条样例**（本机建、能删）。⚠ 配套那条「首启自动出的一张卡片」在现网**没有读数**：10-18 11:5x 查 `note_cards`，这 76 篇预置笔记名下 **0 行**（同一天对照：站长名下另外 24 篇有 19 张卡，说明表本身在写）——客户端那条链是设计成「让位就不出声」的，服务器侧看不到；补种那 70 篇更不可能出卡，它不经过登录、回体里没有 `seeded_note_id` ⇒ 这一半不许报成已生效</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
           <t>2.2.0（10-14 21:27 那份包，10-15 01:12:02 提审、**14:35:41 已上线**）→ 2.2.1（在台上，10-15 15:15:02 提交）→ 2.2.2／2.2.3（各一枚预览码；2.2.3 又 `cli upload` 成开发版本并带体验版标，19:22:41，676,290 B）→ **2.2.4／2.2.5 各一枚预览码（10-16，没 `cli upload`、没提审）**
 界面主线：五档彩色毛玻璃＋首页「换心情」；顶上那一条通栏反向坡；导航条改跟心情走；面板投影五档同一支；Tips 改后台下发；语言角标改画法；列表与「我的」两屏不再跟随调亮度；10-16 那一刀＝「原文翻译」开关搬到「返回」同一行、三档全局、默认改开，照片那一排第三枚改「粘贴」
 后台那一侧：`/ops` 分「数据／配置」两屏（**10-16 六张卡 → 八张**：加 A4 分类未分类占比＋A9 图片备份健康度，落码未部署）、第三屏「卡片模板」管理栏＋浏览器里跑客户端那份解释器画预览（第三十二次部署已上）、与图麦克的换票口（**10-16 结案：对面四步全上线，现网真点 14 条全过 ⇒ 一次口令进两个后台成立**）
-后端现网：已至**第三十三次部署**（10-16 上午＝四路审计第二批那五条）；四路审计第一批六条 10-16 落码**未部署**（35a2431）
+后端现网：截至 10-16 当晚是**第三十三次部署**（10-16 上午＝四路审计第二批那五条；往后的三趟见本表最上面那一行与 §8.30x）；四路审计第一批六条 10-16 落码**当时**未部署（35a2431，后端那三条 10-17 随第三十四次上了）
 **10-15 深夜站长宣布封版**：功能不再增减，往后只做质量迭代（判据、缺陷、口径、一致性）
 包的状态：线上 2.2.0／审核中 2.2.1／开发版本 2.2.3（这三格取自他 10-15 20:23 那张后台截图，**10-16 没有重读后台**，本地那两个新号只到预览码为止）
 iPhone 同期：**1.2(27) → 1.2(33)**——那边 10-16 02:34～17:53 一天六批复刻这一张表的正本（28 返回＋按下回执真源／29 搜索那一排十处／30 按下回执余下五档／31 白底补回「换背景」入口＋那行的字·墨·图形／32 界面用例补落定等待·屏上零改动／33「原文翻译」开关画上并真落库）；**六批全部只有模拟器断言**，真机只做到编译通过、手点与目视那一笔仍欠</t>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -520,8 +520,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 **2026-10-18 11:5x**（这一趟只刷新服务器那几格；小程序后台与 iPhone 那侧没重读）
-小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第三十七次部署**（10-18 11:2x，定向八份文件＝四个后端＋四份预览引擎镜像副本；探针 22/22；11:3x 接着按他「老账户也补」给 70 个老号各补了那一篇预置笔记）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
+          <t>全量功能清单 · 总览｜截至 **2026-10-18 13:1x**（12:4x～13:1x 只刷新服务器那几格；小程序后台与 iPhone 那侧没重读）
+小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第三十八次部署**（10-18 12:4x，定向九份文件＝七个后端＋两份预览引擎镜像；现网探针 23/23；紧接着经真口把存量刷成他后台那份：`refreshed: 76 / closed_shares: 4`；11:3x 那一趟「老账户也补」给 70 个老号各补一篇，库里 preset 6 → 76 行）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜⚠ **13:1x 那一刀（这一篇也能带一张配图）落码未部署、未出包**（它带一条新迁移，挂在现网还没有的 `b4e8a1c7d205` 之后）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>新用户默认那一篇</t>
+          <t>新用户默认那一篇（10-18 起叫「帮助文档」）</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>**服务端在建号那一次**存进一篇产品说明；**10-18 起这份文案归后台管**（`/ops` 里「默认笔记」那一栏五个字段可编辑——改它既不用发版也不用部署；生效值存在库里那一行，库里没有或形状不合格才落回 `backend/seed/preset_note.json`）；当前那份是标题「你收藏过的 200 条，为什么一条都找不到？」、标签「产品说明」、五条要点＋716 字正文，正文不走模型、不烧提炼额度；来源栏念「自带」；能编辑、能分享、能设私密，但**删不掉**（站长 10-14「默认的不能删除」）；新号删了也不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效；**10-18 11:3x 站长拍「老账户也补」：70 个老号一次性各补一篇**（走同一只生产函数、幂等重跑新增 0），库里 `source_type='preset'` 由 6 行 → **76 行**，76 个号名下各正好一篇</t>
+          <t>**服务端在建号那一次**存进一篇产品说明；**10-18 起这篇归后台管**（`/ops` 里那一栏五个字段可编辑——改它既不用发版也不用部署；生效值存在库里那一行，库里没有或形状不合格才落回 `backend/seed/preset_note.json`；具体文案以库里为准，站长 10-18 已在后台改过，这里不再抄旧串）；正文不走模型、不烧提炼额度；来源栏念「自带」；**四条规矩 10-18 换过一版**（站长原话「变成『帮助文档』，不能编辑（按钮置灰），不能分享，允许删除」）：**不能编辑、不能分享、不能出卡片图**（三处都在服务端闸，编辑那道只在真动到内容六栏时才拦，改分类/置顶照样放行）、**能删除**（10-14 那条「默认的不能删除」已撤）；删了不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。**后台点一次发布＝新旧用户全量刷新**：`resync_all` 把库里 `source_type='preset'` 那些篇逐字覆盖成后台那份（顺手关掉这一类名下还开着的分享码）；10-18 12:4x 经真口跑过一趟，读数 `refreshed: 76 / closed_shares: 4`。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效；**10-18 11:3x 站长拍「老账户也补」：70 个老号一次性各补一篇**（走同一只生产函数、幂等重跑新增 0），库里 `source_type='preset'` 由 6 行 → **76 行**，76 个号名下各正好一篇；**这一篇还能带一张配图（站长 10-18「默认笔记，后台也应该支持上传图片」）——落码未部署、未出包**：后台多一格图片栏 `preset_note_image`，走运营图下发链（存我们服务器、`/api/mp/a/{token}` 匿名发字节），客户端拿同一条 https 串画列表右侧那枚封面＋详情那一排＋喂 `previewImage`；一张，不是多张</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>小程序灌**一条真说明**（服务端建、跟账号走、删不掉、文案后台可改）；iPhone 灌**六条样例**（本机建、能删）。⚠ 配套那条「首启自动出的一张卡片」在现网**没有读数**：10-18 11:5x 查 `note_cards`，这 76 篇预置笔记名下 **0 行**（同一天对照：站长名下另外 24 篇有 19 张卡，说明表本身在写）——客户端那条链是设计成「让位就不出声」的，服务器侧看不到；补种那 70 篇更不可能出卡，它不经过登录、回体里没有 `seeded_note_id` ⇒ 这一半不许报成已生效</t>
+          <t>小程序灌**一条真说明**（服务端建、跟账号走、**10-18 起删得掉**、文案与那张配图都后台可改、但不能编辑不能分享）；iPhone 灌**六条样例**（本机建、能删）。⚠ 配套那条「首启自动出的一张卡片」在现网**没有读数**：10-18 11:5x 查 `note_cards`，这 76 篇预置笔记名下 **0 行**（同一天对照：站长名下另外 24 篇有 19 张卡，说明表本身在写）——客户端那条链是设计成「让位就不出声」的，服务器侧看不到；补种那 70 篇更不可能出卡，它不经过登录、回体里没有 `seeded_note_id` ⇒ 这一半不许报成已生效</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1606,8 +1606,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2.3.0 ~ 2.3.7（10-17 15:59 ~ 10-18 03:0x）
-**站长 10-15 那句「封版」在这一窗口由他本人松了两次**：10-17「不需要跳转」（分类与列表合一）与 10-18「编辑时，图片要展示，然后支持删除图片」——都是新能力，不是质量迭代。
+          <t>2.3.0 ~ 2.3.7 那七刀 ＋ 10-18 白天那四件（10-17 15:59 ~ 10-18 13:1x）
+**站长 10-15 那句「封版」在这一窗口由他本人松了三次**：10-17「不需要跳转」（分类与列表合一）、10-18「编辑时，图片要展示，然后支持删除图片」、10-18「官方预置变成帮助文档＋后台更新要全量刷新＋默认笔记也要能上传图片」——都是新能力，不是质量迭代。
 包的去向（三档分清）：工具实据＝**2.3.6 与 2.3.7 已传开发版本**（01:55 696,717 B／03:0x 699,157 B，`cli upload` 回 `✔ upload`）；他口述＝**已提审**（02:00 一句「我已经提交审批」、10:0x 一句「我提审了」，都不是 agent 点的）；agent 不知道＝2.3.6 那一单现在撤了还是在台上、体验版挂哪一份、线上号动没动（10-18 两次去读后台都是登录态没了）。
 ⚠ 2.3.1~2.3.5 这一路只出过预览码，**真机扫到问题的只有他自己那两次**（编辑页报错、页面错位）；iPhone 那侧这一窗口 agent 没读号（列里写的「未重读」＝10-16 的 1.2(33) 那份现状），只有「配图能否逐张删」与「编辑页字段」这两格是 10-18 10:0x 现读 `TumarkNote/ios` 得来的。</t>
         </is>
@@ -2090,6 +2090,134 @@
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>小程序独有；次序是同一条：先记待删再发请求，没成撤回去</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>帮助文档</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>这一类四条新规矩</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-18 12:4x 服务端已上现网／客户端未出包)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>站长 10-18 原话「官方预置，变成『帮助文档』，然后这类笔记，不能编辑（按钮置灰），不能分享，允许删除。然后后台更新后，要新旧用户全量刷新。」⇒ 叫法改「帮助文档」；编辑／分享／出卡片三处**服务端闸 400**（编辑那道只在真动到内容六栏时才拦，改分类、置顶照样放行——这条是他没提但我按「不能编辑」的字面收窄过一次又改回来的）；**删除放开**（翻掉 10-14 那条「默认的不能删除」，那道闸已撤净）；删了不复活。客户端那半（两页的钮置灰、与私密并列、提示行只在 `wx:elif`）**在同一份改动里但没进包**</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>不适用（那侧没有这一类笔记）</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>小程序独有；闸在服务端不是界面上 disabled——界面上灰了也不许当成安全边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>帮助文档</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>后台点一次发布＝新旧全量刷新</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-18 12:4x 已上现网)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>发布口顺手调 `resync_all(db)`：把库里 `source_type='preset'` 那些篇**逐字覆盖成后台那份**（六栏全覆盖，`original_content` 跟着正文走），并关掉这一类名下还开着的分享码；回体带 `refreshed`／`closed_shares` 两枚读数。10-18 12:4x 经真口（`PUT /api/admin/preset-note` 原样再发一次）跑过一趟＝**76 / 4**。⚠ 这一条推翻了 §8.305／8.306 那句「生效面只往前、不回头」</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>他上午那句「我在后台更新了帮助文档，并点了发布，为什么不立即生效」根因就在这儿：旧口径只往前生效，存量一篇不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>界面</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>详情窗正文认换行</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>修复(10-18 落码，未出包)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>他问「我在后台看到是有回行的，为什么笔记详情页原文都是一段文字」。数据先排除：76 篇正文各含 10 个 `\n`、现网 0 篇被改过 ⇒ 换行一直在库里也在接口里。坏在渲染层：详情窗摘要与原文那两枚是 `&lt;view&gt;`（＝div，默认 `white-space: normal` 把 `\n` 折成空格），而旁边 `.original-text` 用的是 `&lt;text&gt;`（微信组件，认 `\n`）⇒ 同一屏两种画法。改一处 `index.wxss` 给 `.ds-para` 补 `white-space: pre-wrap`。探针真开模拟器、同一枚元素 A/B 喂串比高：改前 23.8／23.8（比值 1.00＝折成一段），改后 **214.2／23.8（9.00）**；`&lt;text&gt;` 那一格作正控 179.6／14（12.83）</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>这条改的是 CSS，**现网那个包不含** ⇒ 屏上要等下一个包；不许报成已生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>帮助文档</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>这一篇也能带一张配图</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-18 13:1x 落码，未部署未出包)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>站长 10-18「默认笔记，后台也应该支持上传图片」＋拍板「笔记里＋列表封面都用它」「一张」。**走已经上线的运营图下发链**（新 kind `preset_note_image`），不给这一篇另开一条通路：笔记自己那排图存在云开发桶里，而后台是浏览器、传不进那个桶（服务端至今没有写桶的凭据）。客户端只认**一条 https 串**，同一个串三处共用：列表右侧那枚封面、详情那一排、喂 `previewImage`（本机 `USER_DATA_PATH` 那个路径 previewImage 不认，10-08 记过）。`hideCover` 与私密那道判断排在取官方图之前；官方那张排在用户自己配图之后最后一格；不进 `assets` 那条链、不算用户配额。新栏配一条空值迁移 `c7d1e4a9f380`（10-15 那条「空要显式写出来」的老判据抓出来的，它红了是我漏步骤不是判据写错）</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>⚠ **未部署**：新迁移挂在 `b4e8a1c7d205`（分类名那条，现网还没有）之后 ⇒ 要上它就必然把分类那条一起带上去，两条路等站长挑</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -520,8 +520,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 **2026-10-18 13:1x**（12:4x～13:1x 只刷新服务器那几格；小程序后台与 iPhone 那侧没重读）
-小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第三十八次部署**（10-18 12:4x，定向九份文件＝七个后端＋两份预览引擎镜像；现网探针 23/23；紧接着经真口把存量刷成他后台那份：`refreshed: 76 / closed_shares: 4`；11:3x 那一趟「老账户也补」给 70 个老号各补一篇，库里 preset 6 → 76 行）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜⚠ **13:1x 那一刀（这一篇也能带一张配图）落码未部署、未出包**（它带一条新迁移，挂在现网还没有的 `b4e8a1c7d205` 之后）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
+          <t>全量功能清单 · 总览｜截至 **2026-10-18 14:0x**（14:0x 只刷新服务器那一格＝第三十九次部署（乙路）＋现网探针 31 条 0 红；小程序后台与 iPhone 那侧没重读）
+小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；**2.3.8（13:35）与 2.3.9（13:51）两份都只有预览码、没 `cli upload`**——2.3.8 那张他扫过并回电「回行正常了」（换行那一刀的真机读数），2.3.9 那张含首屏改「图片」那一枚、**还没有回电读数**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第三十九次部署**（10-18 14:0x，官方配图那一栏走**乙**＝只传代码、不跑那条新迁移；定向七份文件＝三个后端＋四份预览引擎镜像；传前／传后两边 md5 各七枚对齐、现网探针 **31 条 0 红**、两 unit 重启后 `NRestarts` 0、本机与公网 health 各 200、`alembic current` 未动）｜第三十八次（10-18 12:4x，定向九份文件＝七个后端＋两份预览引擎镜像；现网探针 23/23；紧接着经真口把存量刷成他后台那份：`refreshed: 76 / closed_shares: 4`；11:3x 那一趟「老账户也补」给 70 个老号各补一篇，库里 preset 6 → 76 行）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜⚠ **这一篇的配图：后台那一半已上现网（乙路），但探针那张没点发布 ⇒ 用户侧仍不带图，发布那一下归站长在 `/ops` 点；客户端那一半（列表封面＋详情窗那一排）未出包 ⇒ 屏上要等下一个包**｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>**服务端在建号那一次**存进一篇产品说明；**10-18 起这篇归后台管**（`/ops` 里那一栏五个字段可编辑——改它既不用发版也不用部署；生效值存在库里那一行，库里没有或形状不合格才落回 `backend/seed/preset_note.json`；具体文案以库里为准，站长 10-18 已在后台改过，这里不再抄旧串）；正文不走模型、不烧提炼额度；来源栏念「自带」；**四条规矩 10-18 换过一版**（站长原话「变成『帮助文档』，不能编辑（按钮置灰），不能分享，允许删除」）：**不能编辑、不能分享、不能出卡片图**（三处都在服务端闸，编辑那道只在真动到内容六栏时才拦，改分类/置顶照样放行）、**能删除**（10-14 那条「默认的不能删除」已撤）；删了不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。**后台点一次发布＝新旧用户全量刷新**：`resync_all` 把库里 `source_type='preset'` 那些篇逐字覆盖成后台那份（顺手关掉这一类名下还开着的分享码）；10-18 12:4x 经真口跑过一趟，读数 `refreshed: 76 / closed_shares: 4`。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效；**10-18 11:3x 站长拍「老账户也补」：70 个老号一次性各补一篇**（走同一只生产函数、幂等重跑新增 0），库里 `source_type='preset'` 由 6 行 → **76 行**，76 个号名下各正好一篇；**这一篇还能带一张配图（站长 10-18「默认笔记，后台也应该支持上传图片」）——落码未部署、未出包**：后台多一格图片栏 `preset_note_image`，走运营图下发链（存我们服务器、`/api/mp/a/{token}` 匿名发字节），客户端拿同一条 https 串画列表右侧那枚封面＋详情那一排＋喂 `previewImage`；一张，不是多张</t>
+          <t>**服务端在建号那一次**存进一篇产品说明；**10-18 起这篇归后台管**（`/ops` 里那一栏五个字段可编辑——改它既不用发版也不用部署；生效值存在库里那一行，库里没有或形状不合格才落回 `backend/seed/preset_note.json`；具体文案以库里为准，站长 10-18 已在后台改过，这里不再抄旧串）；正文不走模型、不烧提炼额度；来源栏念「自带」；**四条规矩 10-18 换过一版**（站长原话「变成『帮助文档』，不能编辑（按钮置灰），不能分享，允许删除」）：**不能编辑、不能分享、不能出卡片图**（三处都在服务端闸，编辑那道只在真动到内容六栏时才拦，改分类/置顶照样放行）、**能删除**（10-14 那条「默认的不能删除」已撤）；删了不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。**后台点一次发布＝新旧用户全量刷新**：`resync_all` 把库里 `source_type='preset'` 那些篇逐字覆盖成后台那份（顺手关掉这一类名下还开着的分享码）；10-18 12:4x 经真口跑过一趟，读数 `refreshed: 76 / closed_shares: 4`。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效；**10-18 11:3x 站长拍「老账户也补」：70 个老号一次性各补一篇**（走同一只生产函数、幂等重跑新增 0），库里 `source_type='preset'` 由 6 行 → **76 行**，76 个号名下各正好一篇；**这一篇还能带一张配图（站长 10-18「默认笔记，后台也应该支持上传图片」）——后台那一半 14:0x 已随第三十九次上现网（乙路），**没点发布 ⇒ 用户侧至今不带图；客户端那一半未出包 ⇒ 屏上要等下一个包**：后台多一格图片栏 `preset_note_image`，走运营图下发链（存我们服务器、`/api/mp/a/{token}` 匿名发字节），客户端拿同一条 https 串画列表右侧那枚封面＋详情那一排＋喂 `previewImage`；一张，不是多张</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>修复(10-18 落码，未出包)</t>
+          <t>修复(10-18 落码，**已在真机验过**＝2.3.8 预览码，线上包仍不含)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2185,39 +2185,71 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>这条改的是 CSS，**现网那个包不含** ⇒ 屏上要等下一个包；不许报成已生效</t>
+          <t>这条改的是 CSS，**线上那个包不含** ⇒ 只有扫预览码才看得到。10-18 站长扫 2.3.8 那张预览码回电「回行正常了」（在那之前他先回了一次「还是没有段落回行」，ssh 读库核过 `#69 original_content len=460／\n=27`，加上那一屏「编辑／分享」并未置灰 ⇒ 定性成他手上还是 03:0x 那个旧包，不是代码坏）；不许报成线上已生效</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>界面</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>首屏左下角那一枚计数</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>改口(10-18 13:5x 落码，未出包)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>站长 10-18 原话「把首屏左下角的『卡片』和上面的『数量』，改为图片和数量。」⇒ 那一格的名字从「卡片」改成「图片」（**键是改名不是加键**：`statCards` → `statImages`，中英两份＝图片／Images，旧键留着就是死键）；上面那个数从「出过几张卡片」换成「名下配了几张图」，**出处只有服务端那一个**：`storage-quota` 回体里的 `user_count`（判据钉死不许在客户端拿卡片清单或别的数组现数一遍）。那一排的几何与落点一个字没动，点下去仍回合一后的那一张列表；读屏那句跟着走「数字＋那一格的名字」。</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>不适用（那侧首屏没有这两枚计数）</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>小程序独有。静态尺子 `验-第一屏三块.js` **92 条全过**（含为这一改新写的那条「数只有服务端一个出处」）；**真跑那把 `验-第一屏三块-真跑.js` 判据已跟着改口、还没跑** ⇒ 这一格只算落码，不算上屏验过</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>帮助文档</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>这一篇也能带一张配图</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>新增(10-18 13:1x 落码，未部署未出包)</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-18 13:1x 落码；后端那一半 14:0x 已上现网＝第三十九次·乙路；未发布、未出包)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>站长 10-18「默认笔记，后台也应该支持上传图片」＋拍板「笔记里＋列表封面都用它」「一张」。**走已经上线的运营图下发链**（新 kind `preset_note_image`），不给这一篇另开一条通路：笔记自己那排图存在云开发桶里，而后台是浏览器、传不进那个桶（服务端至今没有写桶的凭据）。客户端只认**一条 https 串**，同一个串三处共用：列表右侧那枚封面、详情那一排、喂 `previewImage`（本机 `USER_DATA_PATH` 那个路径 previewImage 不认，10-08 记过）。`hideCover` 与私密那道判断排在取官方图之前；官方那张排在用户自己配图之后最后一格；不进 `assets` 那条链、不算用户配额。新栏配一条空值迁移 `c7d1e4a9f380`（10-15 那条「空要显式写出来」的老判据抓出来的，它红了是我漏步骤不是判据写错）</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>⚠ **未部署**：新迁移挂在 `b4e8a1c7d205`（分类名那条，现网还没有）之后 ⇒ 要上它就必然把分类那条一起带上去，两条路等站长挑</t>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>⚠ **现网跑的是乙路**：只传代码、**那条新迁移故意没跑**（它挂在 `b4e8a1c7d205` 分类名那条之后，跑它就必然把分类那条一起带上去）。不跑不坏——写口 `setting_row(create=True)` 会按需建行；实测 `alembic current` 仍 `e3a7c91b4f26`、探针 31 条 0 红、`mp_settings` 里这一行 `asset_id=None`。**没点发布**（探针那张 48×32 测试图不发给用户），所以现网用户读到的仍是 `preset_note_image: null`；发布那一下归站长在 `/ops` 点，屏上那一半等下一个包</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -521,7 +521,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>全量功能清单 · 总览｜截至 **2026-10-18 14:0x**（14:0x 只刷新服务器那一格＝第三十九次部署（乙路）＋现网探针 31 条 0 红；小程序后台与 iPhone 那侧没重读）
-小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**；**2.3.8（13:35）与 2.3.9（13:51）两份都只有预览码、没 `cli upload`**——2.3.8 那张他扫过并回电「回行正常了」（换行那一刀的真机读数），2.3.9 那张含首屏改「图片」那一枚、**还没有回电读数**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），不是 agent 点的、也不是 agent 读到的——10-18 两次去读后台都是登录态没了（「登录超时」／扫码页）｜后端现网 **第三十九次部署**（10-18 14:0x，官方配图那一栏走**乙**＝只传代码、不跑那条新迁移；定向七份文件＝三个后端＋四份预览引擎镜像；传前／传后两边 md5 各七枚对齐、现网探针 **31 条 0 红**、两 unit 重启后 `NRestarts` 0、本机与公网 health 各 200、`alembic current` 未动）｜第三十八次（10-18 12:4x，定向九份文件＝七个后端＋两份预览引擎镜像；现网探针 23/23；紧接着经真口把存量刷成他后台那份：`refreshed: 76 / closed_shares: 4`；11:3x 那一趟「老账户也补」给 70 个老号各补一篇，库里 preset 6 → 76 行）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜⚠ **这一篇的配图：后台那一半已上现网（乙路），但探针那张没点发布 ⇒ 用户侧仍不带图，发布那一下归站长在 `/ops` 点；客户端那一半（列表封面＋详情窗那一排）未出包 ⇒ 屏上要等下一个包**｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
+小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**，**14:3x 又传了 2.3.9（700,759 B＝684.3 KB，`cli upload` 退出码 0）**；2.3.8（13:35 那张预览码）没单独 upload——它的作用只是让他当场验换行，验完他回电「回行正常了」；**2.3.9 那张预览码含首屏改「图片」那一枚、那一处还没有单独回电**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），14:3x 他这句是「我自己手动提交审批」⇒ **提审归他、我没碰**；⚠ **「设为体验版」这一格我没做成**：10-18 三次去读后台（02:00／10:0x／14:3x）都是「登录超时」／扫码页，扫码只能他本人⇒ 后台现状是**开发版本里有 2.3.9、体验版仍挂着旧那一份（挂哪一份读不到）**｜后端现网 **第三十九次部署**（10-18 14:0x，官方配图那一栏走**乙**＝只传代码、不跑那条新迁移；定向七份文件＝三个后端＋四份预览引擎镜像；传前／传后两边 md5 各七枚对齐、现网探针 **31 条 0 红**、两 unit 重启后 `NRestarts` 0、本机与公网 health 各 200、`alembic current` 未动）｜第三十八次（10-18 12:4x，定向九份文件＝七个后端＋两份预览引擎镜像；现网探针 23/23；紧接着经真口把存量刷成他后台那份：`refreshed: 76 / closed_shares: 4`；11:3x 那一趟「老账户也补」给 70 个老号各补一篇，库里 preset 6 → 76 行）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜⚠ **这一篇的配图：后台那一半已上现网（乙路），但探针那张没点发布 ⇒ 用户侧仍不带图，发布那一下归站长在 `/ops` 点；客户端那一半（列表封面＋详情窗那一排）未出包 ⇒ 屏上要等下一个包**｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -520,8 +520,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 **2026-10-18 14:0x**（14:0x 只刷新服务器那一格＝第三十九次部署（乙路）＋现网探针 31 条 0 红；小程序后台与 iPhone 那侧没重读）
-小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本已传 2.3.6（10-18 01:55，696,717 B）与 2.3.7（10-18 03:0x，699,157 B）**，**14:3x 又传了 2.3.9（700,759 B＝684.3 KB，`cli upload` 退出码 0）**；2.3.8（13:35 那张预览码）没单独 upload——它的作用只是让他当场验换行，验完他回电「回行正常了」；**2.3.9 那张预览码含首屏改「图片」那一枚、那一处还没有单独回电**；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），14:3x 他这句是「我自己手动提交审批」⇒ **提审归他、我没碰**；⚠ **「设为体验版」这一格我没做成**：10-18 三次去读后台（02:00／10:0x／14:3x）都是「登录超时」／扫码页，扫码只能他本人⇒ 后台现状是**开发版本里有 2.3.9、体验版仍挂着旧那一份（挂哪一份读不到）**｜后端现网 **第三十九次部署**（10-18 14:0x，官方配图那一栏走**乙**＝只传代码、不跑那条新迁移；定向七份文件＝三个后端＋四份预览引擎镜像；传前／传后两边 md5 各七枚对齐、现网探针 **31 条 0 红**、两 unit 重启后 `NRestarts` 0、本机与公网 health 各 200、`alembic current` 未动）｜第三十八次（10-18 12:4x，定向九份文件＝七个后端＋两份预览引擎镜像；现网探针 23/23；紧接着经真口把存量刷成他后台那份：`refreshed: 76 / closed_shares: 4`；11:3x 那一趟「老账户也补」给 70 个老号各补一篇，库里 preset 6 → 76 行）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜⚠ **这一篇的配图：后台那一半已上现网（乙路），但探针那张没点发布 ⇒ 用户侧仍不带图，发布那一下归站长在 `/ops` 点；客户端那一半（列表封面＋详情窗那一排）未出包 ⇒ 屏上要等下一个包**｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
+          <t>全量功能清单 · 总览｜截至 **2026-10-19 01:0x**（01:0x 刷的还是服务器那一格＝**第四十次部署**（来源黑名单八份＋两 unit 重启）＋现网探针 66 条 0 红；小程序后台与 iPhone 那侧没重读）
+小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本一路传上来：2.3.6（10-18 01:55，696,717 B）→ 2.3.7（10-18 03:0x，699,157 B）→ 2.3.9（10-18 14:3x，700,759 B）→ 最新一枚 2.3.18（10-19 00:2x，692.9 KB／709,540 B，台账 §8.319）**；2.3.8（13:35 那张预览码）没单独 upload——它的作用只是让他当场验换行，验完他回电「回行正常了」；⚠ 号从 2.3.16 直接跳 **2.3.18**，2.3.17 只在本地草稿里停过一夜，没提交、没出包、没上传 ⇒ 别去找那一号；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），14:3x 他这句是「我自己手动提交审批」⇒ **提审归他、我没碰**；⚠ **「设为体验版」与「后台那一格现值」这两格我都没做成**：10-18 三次去读后台（02:00／10:0x／14:3x）都是「登录超时」／扫码页，扫码只能他本人；10-19 01:0x 也没重读 ⇒ 上面那串开发版本靠的是**每次 `cli upload` 的退出码与回体字节数**，不是后台截图后端现网 **第四十次部署**（10-19 00:4x，来源黑名单那八份代码＋两个 unit 重启：`wtsj-api` 1837910→1988285、`wtsj-worker` 1837908→1988284、`NRestarts` 均 0；定向八份传前逐份 diff 过服务器那份、回退点 `wtsj-20261019-004222.sqlite.gz`；**现网探针 `docs/工具/探-现网来源黑名单.py` 66 条 0 红**：命中时抓取调用次数＝0、任务判 failed、那句话原样落进任务、自动攒够 3 次那一路（1→2 放行、3 拦、跨线只打一行 WARNING、第 4 次只加行不新建）、子域各攒各的、两个计入落点之一（200 而正文 0 字）从 worker 那段实现真落了账、fail-open 那一支回 False 且大声记 ERROR——全部跑在 `.invalid` 那四枚主机上，收尾独立复读 `source_blocklist` **0 行**、notes 125／users 77 一字没动）｜**第三十九次**（10-18 14:0x，官方配图那一栏走**乙**＝只传代码、不跑那条新迁移；定向七份文件＝三个后端＋四份预览引擎镜像；传前／传后两边 md5 各七枚对齐、现网探针 31 条 0 红、两 unit 重启后 `NRestarts` 0、本机与公网 health 各 200、`alembic current` 当时未动）｜第三十八次（10-18 12:4x，定向九份文件＝七个后端＋两份预览引擎镜像；现网探针 23/23；紧接着经真口把存量刷成他后台那份：`refreshed: 76 / closed_shares: 4`；11:3x 那一趟「老账户也补」给 70 个老号各补一篇，库里 preset 6 → 76 行）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜⚠ **这一篇的配图：后台那一半已上现网、且他 10-18 14:1x 真点了发布**（10-19 01:0x 现读 `mp_settings.preset_note_image.asset_id = 4`，那张是 1186×906／294,804 B 的真图，不是探针那张 48×32）；客户端那一半（列表封面＋详情窗那一排＋卡片大图位）随 **2.3.18** 出包 ⇒ **屏上要等他扫那一枚预览码，未提审**；⚠ 卡片那一处另有一条断点：他扫新包回电「大图没出现」，那一路的根因**不是包**——现网库里下发那十套配方还是老的，要灌新种子才画得出来（归另一路，正本 §8.322，任务 #221 等他一句）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>分类行文字下划线式；私密格自动备、有笔记删不掉；**10-17 起改成面板内管理**（`a2f0141`：＋新增／✕删带二次确认／长按拖动／点空白自动保存／四类默认／名称跟着界面语言自动翻译），⚠ **后端那一半（`5f0b801`）到 10-18 10:0x 仍未上现网**（服务器 alembic 头 `e3a7c91b4f26`，那批要 `b4e8a1c7d205`）</t>
+          <t>分类行文字下划线式；私密格自动备、有笔记删不掉；**10-17 起改成面板内管理**（`a2f0141`：＋新增／✕删带二次确认／长按拖动／点空白自动保存／四类默认／名称跟着界面语言自动翻译），⚠ **后端那一半（`5f0b801`）今天算「半上」：库到位了、代码没上**——10-19 01:0x 现读服务器：alembic 头已到 `f0a3b9c6d172`、`categories` 里 `name_zh`／`name_en` 两列**在**（那表 9 行），而 `app/api/routes/categories.py` 里 `name_zh|name_en` 命中 **0**、`app/services/category_names.py` 这只文件在服务器上**不存在** ⇒ 表在库里≠这条链上线</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>样式不同；小程序有私密格保护规则；**「名称自动翻译」这一件在现网还差服务端那两栏**（切语言不出译名、删除问话不报篇数）</t>
+          <t>样式不同；小程序有私密格保护规则；**「名称自动翻译」这一件在现网差的是读那两栏的代码**（列已在库里，屏上仍不出译名）</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>**服务端在建号那一次**存进一篇产品说明；**10-18 起这篇归后台管**（`/ops` 里那一栏五个字段可编辑——改它既不用发版也不用部署；生效值存在库里那一行，库里没有或形状不合格才落回 `backend/seed/preset_note.json`；具体文案以库里为准，站长 10-18 已在后台改过，这里不再抄旧串）；正文不走模型、不烧提炼额度；来源栏念「自带」；**四条规矩 10-18 换过一版**（站长原话「变成『帮助文档』，不能编辑（按钮置灰），不能分享，允许删除」）：**不能编辑、不能分享、不能出卡片图**（三处都在服务端闸，编辑那道只在真动到内容六栏时才拦，改分类/置顶照样放行）、**能删除**（10-14 那条「默认的不能删除」已撤）；删了不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。**后台点一次发布＝新旧用户全量刷新**：`resync_all` 把库里 `source_type='preset'` 那些篇逐字覆盖成后台那份（顺手关掉这一类名下还开着的分享码）；10-18 12:4x 经真口跑过一趟，读数 `refreshed: 76 / closed_shares: 4`。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效；**10-18 11:3x 站长拍「老账户也补」：70 个老号一次性各补一篇**（走同一只生产函数、幂等重跑新增 0），库里 `source_type='preset'` 由 6 行 → **76 行**，76 个号名下各正好一篇；**这一篇还能带一张配图（站长 10-18「默认笔记，后台也应该支持上传图片」）——后台那一半 14:0x 已随第三十九次上现网（乙路），**没点发布 ⇒ 用户侧至今不带图；客户端那一半未出包 ⇒ 屏上要等下一个包**：后台多一格图片栏 `preset_note_image`，走运营图下发链（存我们服务器、`/api/mp/a/{token}` 匿名发字节），客户端拿同一条 https 串画列表右侧那枚封面＋详情那一排＋喂 `previewImage`；一张，不是多张</t>
+          <t>**服务端在建号那一次**存进一篇产品说明；**10-18 起这篇归后台管**（`/ops` 里那一栏五个字段可编辑——改它既不用发版也不用部署；生效值存在库里那一行，库里没有或形状不合格才落回 `backend/seed/preset_note.json`；具体文案以库里为准，站长 10-18 已在后台改过，这里不再抄旧串）；正文不走模型、不烧提炼额度；来源栏念「自带」；**四条规矩 10-18 换过一版**（站长原话「变成『帮助文档』，不能编辑（按钮置灰），不能分享，允许删除」）：**不能编辑、不能分享、不能出卡片图**（三处都在服务端闸，编辑那道只在真动到内容六栏时才拦，改分类/置顶照样放行）、**能删除**（10-14 那条「默认的不能删除」已撤）；删了不复活——判据挂在建号那一支，不是「名下没笔记」那种现算状态。**后台点一次发布＝新旧用户全量刷新**：`resync_all` 把库里 `source_type='preset'` 那些篇逐字覆盖成后台那份（顺手关掉这一类名下还开着的分享码）；10-18 12:4x 经真口跑过一趟，读数 `refreshed: 76 / closed_shares: 4`。10-14 落码（`cba5bda`，随 2.1.15），10-15 起现网生效；**10-18 11:3x 站长拍「老账户也补」：70 个老号一次性各补一篇**（走同一只生产函数、幂等重跑新增 0），库里 `source_type='preset'` 由 6 行 → **76 行**，76 个号名下各正好一篇；**这一篇还能带一张配图（站长 10-18「默认笔记，后台也应该支持上传图片」）——后台那一半 14:0x 已随第三十九次上现网（乙路），**发布那一下他 10-18 14:17 已经点了**（10-19 01:0x 现读 `preset_note_image.asset_id = 4`，那张 1186×906／294,804 B，不是探针那张 48×32）；客户端那一半随 **2.3.18** 出包、未提审 ⇒ 屏上要等扫那一枚预览码**：后台多一格图片栏 `preset_note_image`，走运营图下发链（存我们服务器、`/api/mp/a/{token}` 匿名发字节），客户端拿同一条 https 串画列表右侧那枚封面＋详情那一排＋喂 `previewImage`；一张，不是多张</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>前端那一半 `a2f0141`：＋新增／✕删（带二次确认）／长按拖动／点空白自动保存／四类默认／名称跟着界面语言自动翻译（规则只在 `utils/catText.js` 一份）。⚠ 后端那一半 `5f0b801`（迁移 `b4e8a1c7d205`）**到 10-18 10:0x 仍未上现网**——现读服务器 `alembic current` = `e3a7c91b4f26 (head)`</t>
+          <t>前端那一半 `a2f0141`：＋新增／✕删（带二次确认）／长按拖动／点空白自动保存／四类默认／名称跟着界面语言自动翻译（规则只在 `utils/catText.js` 一份）。⚠ 后端那一半 `5f0b801`（迁移 `b4e8a1c7d205`）今天算**半上**——10-19 01:0x 现读服务器：`alembic current` = **`f0a3b9c6d172 (head)`**（那三笔欠账 00:3x 被他一句「先跑那三笔迁移」跑掉了）、`categories` 里 `name_zh`／`name_en` 两列**在**（9 行）；但 `routes/categories.py` 里读那两列的代码命中 **0**、`services/category_names.py` 这只文件在服务器上**不存在**</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>**「名称自动翻译」这一件在现网还差服务端那两栏**：症状＝切语言不出译名、删除问话不报篇数、新用户默认四格看不见</t>
+          <t>**「名称自动翻译」这一件在现网差的是读那两栏的代码，不是那两栏**：症状仍是切语言不出译名、删除问话不报篇数、新用户默认四格看不见</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>新增(10-18 13:1x 落码；后端那一半 14:0x 已上现网＝第三十九次·乙路；未发布、未出包)</t>
+          <t>新增(10-18 13:1x 落码；后端那一半 14:0x 已上现网＝第三十九次·乙路；**已发布、已随 2.3.18 出包**)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2249,7 +2249,39 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>⚠ **现网跑的是乙路**：只传代码、**那条新迁移故意没跑**（它挂在 `b4e8a1c7d205` 分类名那条之后，跑它就必然把分类那条一起带上去）。不跑不坏——写口 `setting_row(create=True)` 会按需建行；实测 `alembic current` 仍 `e3a7c91b4f26`、探针 31 条 0 红、`mp_settings` 里这一行 `asset_id=None`。**没点发布**（探针那张 48×32 测试图不发给用户），所以现网用户读到的仍是 `preset_note_image: null`；发布那一下归站长在 `/ops` 点，屏上那一半等下一个包</t>
+          <t>⚠ 这一栏**当时走的是乙路**（只传代码、那条新迁移 `c7d1e4a9f380` 故意没跑——它挂在 `b4e8a1c7d205` 分类名那条之后，跑它就必然把分类那条一起带上去）；不跑不坏，因为写口 `setting_row(create=True)` 会按需建行，当时实测 `mp_settings` 里这一行 `asset_id=None`、后台那一格第一句念「这台后台还没登记过这一栏」。**这两句现在都过期了**：10-18 14:17 他在 `/ops` 传了真图并点发布；10-19 00:3x 那三笔欠账一起跑掉了。10-19 01:0x 现读＝`preset_note_image.asset_id = 4`（1186×906／294,804 B），探针那张 48×32 留在 `mp_assets` id=3 当留痕、从没发出去过；屏上那一半随 2.3.18 出包、未提审</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>来源黑名单</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>新增(10-18 深夜落码；10-19 00:4x 已上现网＝第四十次部署)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>站长原话「只要提取失败3次以上，自动落入黑名单，管理员可以查看到域名，可以手工增删。后端提取时，先读取是否在黑名单，如果在就返回给客户端，提醒用户」，目的他那句是省服务器资源。落成的形状（正本 `docs/规格-来源黑名单.md`）：**计数只认两型**——站点回 4xx／5xx、或 200 而正文读出 0 字；提炼失败／超时／DNS／worker 挂／单张贴图下载失败**一条都不计**（计了就把我们自己的故障算到网站头上，10-13 那次 `.env` 少三行那种一天能刷黑全网）；主机名原样、不去子域、不合并注册域；阈值 3、全局、不自动过期，出去只有管理员手工移。新表 `source_blocklist`（迁移 `f0a3b9c6d172`，10-19 00:3x 已跑）、三个管理口＋后台那一栏、闸门放在 **worker 里**（所以小程序一行代码都不用改）。</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>不适用（闸在服务端那条提取链上，那侧没有这个入口）</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>⚠ **命中时一次外网都不发**是这条唯一要证的数，判据是抓取替身的**调用次数等于 0**、不是返回的那句话：现网探针 `docs/工具/探-现网来源黑名单.py` **66 条 0 红**（10-19 01:0x，含自动攒够 3 次那一路 1→2 放行／3 拦／第 4 次只加行、子域各攒各的、两个计入落点之一从 worker 那段实现真落账、fail-open 那一支回 False 且大声记 ERROR，全跑在 `.invalid` 那四枚主机上、收尾读回 0 行）。⚠ **仍无读数的一格＝真人手机上那句 toast**（要一台手机）。⚠ 现网另有一行**未部署的一行修复**：后台那一格留空点「加入」，今天回的是 422「host不能为空」——`BlockIn` 那道 `min_length=1` 抢在 `clean_host` 之前响，把设计好的那句中文挡掉了；本地已收成只剩一份真相，等部署</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.1" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.2" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.3 做减法" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.4 一夜八句" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,8 +521,11 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 **2026-10-19 01:0x**（01:0x 刷的还是服务器那一格＝**第四十次部署**（来源黑名单八份＋两 unit 重启）＋现网探针 66 条 0 红；小程序后台与 iPhone 那侧没重读）
-小程序：线上 **2.2.0**（后台最后一格真读数＝站长 10-15 20:23 那张截图，发布 14:35:41）／审核中 **2.2.1**（10-15 15:15:02，10-18 没重读）／**开发版本一路传上来：2.3.6（10-18 01:55，696,717 B）→ 2.3.7（10-18 03:0x，699,157 B）→ 2.3.9（10-18 14:3x，700,759 B）→ 最新一枚 2.3.18（10-19 00:2x，692.9 KB／709,540 B，台账 §8.319）**；2.3.8（13:35 那张预览码）没单独 upload——它的作用只是让他当场验换行，验完他回电「回行正常了」；⚠ 号从 2.3.16 直接跳 **2.3.18**，2.3.17 只在本地草稿里停过一夜，没提交、没出包、没上传 ⇒ 别去找那一号；「已提审」两处都是**他口述**（02:00 一句、10:0x 一句），14:3x 他这句是「我自己手动提交审批」⇒ **提审归他、我没碰**；⚠ **「设为体验版」与「后台那一格现值」这两格我都没做成**：10-18 三次去读后台（02:00／10:0x／14:3x）都是「登录超时」／扫码页，扫码只能他本人；10-19 01:0x 也没重读 ⇒ 上面那串开发版本靠的是**每次 `cli upload` 的退出码与回体字节数**，不是后台截图后端现网 **第四十次部署**（10-19 00:4x，来源黑名单那八份代码＋两个 unit 重启：`wtsj-api` 1837910→1988285、`wtsj-worker` 1837908→1988284、`NRestarts` 均 0；定向八份传前逐份 diff 过服务器那份、回退点 `wtsj-20261019-004222.sqlite.gz`；**现网探针 `docs/工具/探-现网来源黑名单.py` 66 条 0 红**：命中时抓取调用次数＝0、任务判 failed、那句话原样落进任务、自动攒够 3 次那一路（1→2 放行、3 拦、跨线只打一行 WARNING、第 4 次只加行不新建）、子域各攒各的、两个计入落点之一（200 而正文 0 字）从 worker 那段实现真落了账、fail-open 那一支回 False 且大声记 ERROR——全部跑在 `.invalid` 那四枚主机上，收尾独立复读 `source_blocklist` **0 行**、notes 125／users 77 一字没动）｜**第三十九次**（10-18 14:0x，官方配图那一栏走**乙**＝只传代码、不跑那条新迁移；定向七份文件＝三个后端＋四份预览引擎镜像；传前／传后两边 md5 各七枚对齐、现网探针 31 条 0 红、两 unit 重启后 `NRestarts` 0、本机与公网 health 各 200、`alembic current` 当时未动）｜第三十八次（10-18 12:4x，定向九份文件＝七个后端＋两份预览引擎镜像；现网探针 23/23；紧接着经真口把存量刷成他后台那份：`refreshed: 76 / closed_shares: 4`；11:3x 那一趟「老账户也补」给 70 个老号各补一篇，库里 preset 6 → 76 行）｜iPhone：**1.2(33)**（10-16，这一轮没重读那侧的号）｜⚠ **这一篇的配图：后台那一半已上现网、且他 10-18 14:1x 真点了发布**（10-19 01:0x 现读 `mp_settings.preset_note_image.asset_id = 4`，那张是 1186×906／294,804 B 的真图，不是探针那张 48×32）；客户端那一半（列表封面＋详情窗那一排＋卡片大图位）随 **2.3.18** 出包 ⇒ **屏上要等他扫那一枚预览码，未提审**；⚠ 卡片那一处另有一条断点：他扫新包回电「大图没出现」，那一路的根因**不是包**——现网库里下发那十套配方还是老的，要灌新种子才画得出来（归另一路，正本 §8.322，任务 #221 等他一句）｜2.3.x 那一整窗口见后面「2.3 做减法」那张分表</t>
+          <t>全量功能清单 · 总览｜截至 **2026-10-21 01:0x**（版本号与发布位次已另立正本 **`docs/版本与发布现状.md`**——要位次读那一份，这张表只管功能对照；10-21 这趟只重读了小程序本地号与 iPhone 那一侧，服务器与后台没再进）
+小程序：线上 **2.4.0**（他 10-20 傍晚口述＋一条服务端日志佐证＝正式版 referer 档当天从 `/14/` 升到 `/15/`；后台最后一格**真截图**仍是 10-15 20:23＝那时线上 2.2.0，10-21 没进后台）／**审核中＝没有读数**（提审这一步 10-11 起定死归他本人，我不自动跑）／架上开发版本最新一枚 **2.4.8**（10-21 00:3x `cli upload -v 2.4.8`，包 **728,596 B**）；本地树 `appInfo.js:457` 现读 `VERSION = '2.4.8'`＝**与架上同号，没有「改了没出包」的欠账**；⚠ **2.4.1～2.4.8 那七号的东西一件都不在线上**（新分享封面／「懒人记录神器」那句／配图长按拖动排序·第一张＝头图／卡片圆点横拖换模板／详情窗左右滑换前后篇·遇私密自动跳过／卡片外圈只往纸白走／首屏那枚 Share 胶囊）⇒ **对外材料里的「当前版本」只能写 2.4.0**；⚠ 10-21 凌晨那句「编辑笔记又不能拖动图片排序了」就是这么结案的：**不是回归，是他手机上跑的是线上那颗 2.4.0**。
+后端现网 **第五十一次部署**（10-20 18:53＝第三轮审计那批修复：后端 26 只文件＋云函数 `extract` 重传，双 unit 重启）｜**第五十次**（10-20 15:4x＝**配图拖动排序的后端那一半**上现网：`assets.sort_order` 那一列＋迁移＋`POST /api/notes/{id}/assets/reorder`＋四处读图口改吃同一份排序键，**小程序包一个字节没动**；那条口部署前 **405**→部署后 **401「无效的 Token」**；新探针 `docs/工具/探-现网配图拖动排序.py` 23 条红 0、回归 `assets_live_probe.py` 49/49；迁移头 `alembic current` = **`a4d7e2b91c58`**（由 `f0a3b9c6d172` 升上来；升完 `assets` 91 行 `sort_order` 全是 0、28 篇头图 `cover_file_id` 逐篇未变））｜卡片模板下发：现网 **11 行 live**，10-20 另两趟是**纯数据**改动（图文卡那一圈 3 宽灰描边撤＝配方 20 步减到 19 步；网点漫画补回 `onDark` 白字），不发版；`deploy.sh` 那道闸默认关，要 `POSTER_TEMPLATES=1`｜⚠ **分类译名那一格 10-21 没重读服务器**，仍是「列在库里、读它的代码没上」＝**待核，不许写成已上线**。
+iPhone：**1.2(34)**（`TumarkNote/ios/project.yml:224-225` 10-21 现读 `MARKETING_VERSION: "1.2"`／`CURRENT_PROJECT_VERSION: "34"`，树顶 `65c312c` 10-21 00:45，无远端）；它自己那套复刻清单正本 `ios/复刻清单-小程序2.2-20261016.md`（137,562 B，10-21 00:54 还在改）的锚点停在 **2.4.6**，而小程序这头已走到 **2.4.8** ⇒ **那一列凡是「照正本对齐」的结论都按 2.4.6 读的，2.4.7／2.4.8 那两号它还没跟**；它自己那份 `ios/出包前检查.md:1075` 现读**「能提审的仍然只有 `1.2(13)`；14~26 都只出过 Debug 包」**，且那边写明这仓库根本没有 remote；⚠ **真机那一头仍欠**（第十七到二十八刀的真机清单已落盘、装机卡在「手机锁着」）⇒ **iPhone 列写「有」的，多数只到模拟器断言级，不是真机级**，引用时带上这一句。
+⚠ 两端对照口径禁令照旧：10-21 在那侧现读到的三格硬差异——**配图不能逐张删也不能拖动排序**（`Domain/ShotAttachmentStore.swift` 只有 `retain`／`urls`／`delete`／`sweepOrphans`／`discardAll` 五只口）、**没有私密分类**（`Views/NoteRowView.swift:19,25`、`Design/AppCopy.swift:166`、`Views/DetailView.swift:473` 三处都自己写明）、**没有转存这件事**（`Views/NoteRowView.swift:21,151`：列表来源栏第三档「转存人昵称」这边没有对应数据）；模板那一族是**十套写死在编译期**（`Domain/Card/CardTemplate.swift:5`），远程模板包目录 `agentsbin.cn/templates/manifest.json` 按它自己那份检查文档**还没部署** ⇒ 取不到就原地不动。小程序全免费、iPhone 六套要订阅（¥69.99 买断／¥19.99 月订）；小程序有账号与云备份、iPhone 本地优先无账户——**功能与商业口径都不许互推**；2.4.x 那一整窗口见后面「2.4 一夜八句」那张分表</t>
         </is>
       </c>
     </row>
@@ -727,7 +731,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>**2.3.0 起两张列表并成一张**（笔记列表与卡片列表合一，「不需要跳转」那一轮）：一篇一张卡＋右侧那枚配图封面；封面吃服务端现算的那栏 `cover_file_id`（删掉封面那张会自动换下一张），私密篇一律不画封面</t>
+          <t>**2.3.0 起两张列表并成一张**（笔记列表与卡片列表合一，「不需要跳转」那一轮）：一篇一张卡＋右侧那枚配图封面；封面吃服务端现算的那栏 `cover_file_id`（删掉封面那张会自动换下一张），私密篇一律不画封面；**2.4.4 起这一屏那扇详情窗（带毛玻璃那一层）能左右滑换前后篇**，到头就停、不循环；滑的落点永远取左右最近的一行**不私密**的⇒ 这一条把手上撞不响密码；左上角那句 `noteSwipeHint` 念「左右滑动看下一篇」／英文 `Swipe for the next note`（`pages/index/index.wxml:216`，10-21 现读）；⚠ 这一刀第一版落到了全屏那一页，他夜里改口「是指带毛玻璃背景的那个界面」⇒ 功能搬进这一屏，全屏那一页一行没留</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -737,7 +741,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>小程序这一趟是**做减法**（撤掉第二个入口）；iPhone 那边这一轮没重读，不替它下结论</t>
+          <t>小程序这一趟是**做减法**（撤掉第二个入口）＋加了一扇窗里的滑动把手；⚠ iPhone 那一列仍是 10-16 的读数，这一轮没重读那侧的列表交互，不替它下结论；但「滑到私密自动跳过」那一条在 iPhone **没有输入源**（那侧没有私密分类，见下面「私密锁」那一行）</t>
         </is>
       </c>
     </row>
@@ -840,12 +844,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无（**10-21 在那侧现读、三处注释自己写明「这一版没有私密分类」**：`Views/NoteRowView.swift:19,25`、`Design/AppCopy.swift:166`、`Views/DetailView.swift:473`）</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>小程序独有（服务端强制）</t>
+          <t>小程序独有，且闸在**服务端**（不解锁连正文与概要都不下发）；iPhone 那边连「私密」这个数据源都没有 ⇒ 凡挂在私密上的交互（列表不画封面、不能分享、滑动自动跳过）在它那儿都无从对齐</t>
         </is>
       </c>
     </row>
@@ -889,7 +893,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>独立一屏 `pages/write`：标题／摘要／要点／标签／分类五栏（**没有「原文」那一栏**，原文只在详情看）；**2.3.7 起这一屏多出「配图」一排**——每张一个 ✕，确认之后逐张删；没图整栏不画；⚠ 他没提「加图」，所以这一屏**没有加图的口**（选图仍只在录入那一屏）；点图也不看大图</t>
+          <t>独立一屏 `pages/write`：标题／摘要／要点／标签／分类五栏（**没有「原文」那一栏**，原文只在详情看）；**2.3.7 起这一屏多出「配图」一排**——每张一个 ✕，确认之后逐张删；没图整栏不画；⚠ 他没提「加图」，所以这一屏**没有加图的口**（选图仍只在录入那一屏）；点图也不看大图（10-21 复核：这一屏 `previewImage` 命中 0）；**2.4.1 起配图那一排能长按拖动排序**——`bindlongpress="onShotDragStart"`（`pages/write/write.wxml:89`）越过谁的中心就换到谁的位置，松手发一次 `reorderNoteAssets`（`write.js:308`），**第一张＝头图**；后端那一半 10-20 15:4x 已上现网＝第五十次部署（`assets.sort_order` 列＋`POST /api/notes/{id}/assets/reorder`＋四处读图口吃同一份排序键），**这一侧要等他扫 2.4.1 之后的那颗包才生效**</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -970,7 +974,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>十枚圆点＋左右滑</t>
+          <t>十枚圆点＋左右滑；**2.4.1 起模板名常驻出卡片那一屏顶上**、**2.4.5 起名字两侧加 `&lt; … &gt;` 两枚箭头**提醒能左右滑（加粗那一格本来就成立，屏上实测 font-weight 读到 700），箭头与名字仍是同一条文字、同一个点击把手（点它照旧换下一套，没拆成三枚）；**2.4.4 起圆点上能横着拖**——拖过一枚点的间距就换一套，走到最后一套再往前回第一套（他 10-20 那句「不要卡死」）；改选与画布解耦，画还在画时选择照样跟手；英文那句提示 2.4.8 收成 `Swipe to switch`（`i18n.js:686`，宾语不写死成 template 因为那一格就住在模板名旁边）</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -980,7 +984,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>交互不同</t>
+          <t>交互不同：这边 10-20 把「拖」与「点」两条把手并到同一屏；iPhone 那侧这一轮没重读，不替它下结论</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1028,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>存到相册；2.0.1 起生成即上云留档（note_cards）</t>
+          <t>存到相册；2.0.1 起生成即上云留档（note_cards）；导出成品那一圈**不在模板配方里**、是导出那一步给成品垫的（10-01 深夜为「微信图片面板是全黑底、卡片直边贴上去像被裁一半」加的）——2.4.5 第一版按字面改成「拿这一张卡自己的底渗一档墨」＋宽度 40→20，**被打回**（深底那一族渗完仍读成黑边）；2.4.6 定口径＝那一圈**只往纸白那边走、不描黑**</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1034,7 +1038,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>小程序云端留档换机还在，iPhone 台账只在本机</t>
+          <t>小程序云端留档换机还在，iPhone 台账只在本机；导出垫圈那一处是微信分享面板的场景，iPhone 走系统面板、没有同一问题</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1109,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>通栏「微信好友/朋友圈/公众号」＋微信图片分享面板</t>
+          <t>通栏「微信好友/朋友圈/公众号」＋微信图片分享面板；**屏上另有两枚入口干同一件事**：首屏那枚胶囊（2.4.4 立、2.4.8 整块换皮＝实心黄底＋斜 −45° 纸飞机＋墨字，144×44、圆角 13、无投影，落点搬到首屏最上面那条玻璃带 `.ai-line` 的最左；`button.rec-bar open-type="share"`，`pages/create/create.wxml:103`；皮只住一份＝`styles/rec-bar.wxss`，中文念「告诉好友」／英文 `Share`，`i18n.js:17,483`）与「我的」页那行「推荐图麦」（`pages/me/me.wxml:156`）——要不要撤「我的」那一枚仍等他一句；载荷三格（标题／落地页／封面）住 `utils/shareCard.js` 一份实现、两处消费——2.4.2 换封面那张（`assets/share-card.jpg` 123,994 B，左列「仅需10秒／拍照截图／网页转笔记」），2.4.3 把中文标题换成「图麦笔记懒人记录神器」（`i18n.js:279`；⚠ 英文那格仍是 `TumarkNote | Make every read useful`，`i18n.js:701`⇒ 这一改只落中英两档，不是 12 语）；⚠ 2.4.5 抓到的一条：那一枚在**铺了背景图那一态点不动**，根因不在按钮在层序——这一屏有一层 fixed＋z-index 1＋铺满整屏的「调亮度」罩子，按钮 z-index 停在 auto ⇒ 罩子排在它上面，**透明度为 0 也照样吃点击**；现已抬进那份「铺图时抬到罩层之上」的名单（第三次同一个形状）</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1115,7 +1119,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>小程序走微信场景，iPhone 走系统面板（可到任意 App）</t>
+          <t>小程序走微信场景，iPhone 走系统面板（可到任意 App）；⚠ 首屏那一枚黄条是 2.4.4–2.4.8 一夜追出来的，**一件都不在线上**（线上 2.4.0 屏上没有它）</t>
         </is>
       </c>
     </row>
@@ -2293,6 +2297,551 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2.4.0 ~ 2.4.8（10-19 15:0x 起 ~ 10-21 00:3x）｜**他 10-20 傍晚口述「2.4.0 已经发布」⇒ 线上＝2.4.0，而 2.4.1~2.4.8 那七号的东西一件都不在线上**
+iPhone 同期：1.2(34)（树顶 `65c312c` 10-21 00:45），它那份复刻清单的锚点只重到正本 **2.4.6** ⇒ 本表凡是「2.4.7／2.4.8」的行，那侧连对标都没开始；那边真机仍欠（装机卡在「手机锁着」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一级功能点</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>二级功能点</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>本版本状态</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>小程序端</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>iPhone同期</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>两者差异</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>位次</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>线上／架上／本地三格</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>线上 **2.4.0**（口述＋一条服务端日志佐证：正式版 referer 档当天从 `/14/` 升到 `/15/`）；架上开发版最新 **2.4.8**（10-21 00:3x `cli upload -v 2.4.8`，**728,596 B**）；本地 `appInfo.js:457` 现读 `VERSION = '2.4.8'`＝与架上同号、没有「改了没出包」的欠账；**审核中＝没有读数**（提审归他本人，10-11 起定死）</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1.2(34)（`project.yml:224-225` 现读 MARKETING 1.2／CURRENT 34）；它自己 `ios/出包前检查.md:1075` 现读「能提审的仍然只有 `1.2(13)`，14~26 都只出过 Debug 包」</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>⚠ **对外材料里的「当前版本」只能写 2.4.0**；演示前先让他看「我的→关于」那一行念的是哪一号</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>详情窗顶上常驻模板名</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.4.1)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>`5dbff99`：卡片那一屏顶上那一行中间把模板名常驻，不再被别的字挡（他原话「卡片名称，被遮挡，要提到顶上中间」）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>缩略图条那一族没有这一行 ⇒ 无从对齐</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>图片备份</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>配图长按拖动排序·第一张＝头图</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.4.1)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>`7b4806e`：`pages/write/write.wxml:89` `bindlongpress` 起拖，越过谁的中心就换到谁的位置，松手发一次 `reorderNoteAssets`（`write.js:308`）；**第一张＝头图**（列表那枚封面跟着换）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>**没有**：10-21 现读 `ios/Sources/Domain/ShotAttachmentStore.swift` 只有 `retain`／`urls`／`delete`／`sweepOrphans`／`discardAll` 五只口，既不能逐张删也没有 move／setCover</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 这一件是**两端都动、现网只到一半**的形状：后端那一半 10-20 15:4x 已上现网（第五十次部署，`assets.sort_order`＋迁移 `a4d7e2b91c58`＋`POST …/assets/reorder`），他 16:04 在自己手机上拖了一次，日志回 200、库里那篇六行序号变成 1..6 ⇒ **服务端侧已闭合，屏上那一侧要等他扫 2.4.1 之后的包**</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>新分享封面那一张图</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.4.2)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>`assets/share-card.jpg` 117,067 B → **123,994 B**（右半换成正向 iPhone 壳、屏里是列表页实拍，左列「仅需10秒／拍照截图／网页转笔记」＋「英法日韩等 16 国语言自动翻译」＋六枚圆形平台标）；⚠ 压图档从 `-q:v 2` 抬到 **`-q:v 4`**——这张图 q2/q3 都越 131,072，而越线微信**不报错、只静默退回「截当前页」**</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>不适用（那侧走系统面板，没有这张卡）</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>⚠ 这一行左列那句「16 国语言自动翻译」是**图上印的话**不是新功能：16 语那条是**站长拍的实测数**、口径见 `docs/产品需求.md` 对外文案那一节，别把这一行当成 2.4.2 新加了翻译能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>分享出去那一行的标题</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.4.3)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>`utils/i18n.js` 中文那格 `shareCardTitle` 从「图麦笔记 | 把图文提炼成有用的干货」换成**「图麦笔记懒人记录神器」**（照他写的原样，中间没加竖线；`i18n.js:279` 现读）</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>⚠ **只中英两块字典、不是 12 处**，且英文那一格没动，仍是 `TumarkNote | Make every read useful`（`i18n.js:701` 现读）⇒ 中英两张卡念两句不同的话，要不要跟着换等他一句</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>首屏那枚推荐入口</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.4.4 立／2.4.8 换皮)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2.4.4 立（他四句，后两句改的是前两句的落点与形），2.4.8 一夜又追四句：整块换皮成**实心黄底胶囊＋斜 −45° 纸飞机＋墨字**，144×44、圆角 13、无投影，落点从「英文那一行下方」搬到**首屏最上面那条玻璃带 `.ai-line` 的最左**；中文念「告诉好友」、英文 `Share`（取自本字典已有的 `shareNote`）；皮只住一份＝`styles/rec-bar.wxss`；本身是 `open-type=share`，弹微信原生分享面板</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>**没有对应物**（那侧「推荐」走系统面板，首屏那一行没有这一枚）</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>⚠ 三条留痕：① **微信给 `button` 自带一条 `.wx-btn { width:184px }`**，特异度与裸类 `.rec-bar` 同分却排在后面 ⇒ 第一版只写 width 静默不生效，屏上一颗 184px 居中胶囊压在人脸上下巴之间、源码看着全对，修法＝选择器写 `button.rec-bar`（0,1,1）；② 2.4.5 抓到它在**铺了背景图那一态点不动**，根因不在按钮在层序（那屏有一层 fixed＋z-index 1 铺满整屏的「调亮度」罩子，**透明度为 0 也照样吃点击**）；③ 面板**弹没弹我只证到「点击落得到按钮」那一层**——开发者工具里 `open-type=share` 两态都不弹面板，模拟器给不出这个读数 ⇒ 那一格只能他手机上看</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>卡片模板</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>圆点上横拖换模板</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.4.4)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>拖过一枚点的间距就换一套，走到最后一套再往前**回第一套**（他那句「不要卡死」）；顶上模板名点一下也换下一套；改选与画布**解耦**——画还在画时选择照样跟手</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>缩略图条（点选）</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>交互不同：这边把「拖」与「点」两条把手并到同一屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>笔记管理</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>详情窗左右滑换前后篇</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.4.4)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>列表那一屏那扇**带毛玻璃的详情窗**大标题能左右滑换前后篇，到头就停、不循环；左上角那句 `noteSwipeHint`「左右滑动看下一篇」／英文 `Swipe for the next note`；⚠ 第一版我落到了全屏那一页，他夜里改口「是指带毛玻璃背景的那个界面，不是全屏那个」⇒ 功能搬进这一屏，**全屏那一页一行没留**</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>**没有输入源**：那侧没有私密分类（`NoteRowView.swift:19,25`、`AppCopy.swift:166`、`DetailView.swift:473` 三处注释自己写明）</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>他随后追的那句「滑动遇到私密，自动跳过」已落成：**滑的落点永远是左右最近的一行不私密的** ⇒ 这一条把手上撞不响密码；点行进去那一趟一个字没改，想看的还是想看、照样问密码</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>卡片模板</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>模板名两侧加箭头</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>新增(2.4.5)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>「卡片模板名称（字体加粗）左右加小箭头，例如 &lt; 图文卡 &gt;，提醒用户知道可以左右滑」——加粗那一格本来就成立（屏上实测 font-weight 读到 700），这一刀只补两枚箭头；箭头与名字仍是**同一条文字、同一个点击把手**，没拆成三枚</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>卡片模板</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>导出成品那一圈的颜色</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.4.5 被打回→2.4.6)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>那道黑**不在模板配方里**、是导出那一步给成品垫的一圈（10-01 深夜为「微信图片面板是全黑底、卡片直边贴上去像被裁一半」加的）。2.4.5 第一版按字面改成「拿这一张卡自己的底渗一档墨」＋宽度 40→20 ⇒ **被打回**；2.4.6 口径＝边框**留着**、宽度还是那一半，改的是**掺的方向**：只往纸白掺（纸白占 80%，归 `MATTE_PAPER` 一个数）。包内十套逐套真算过：#fcfcfc／#fdfdfc／#fffffd／#e3e6ff／#dde0de／#ced1db／#ced0d7／#d0d0d1／#fdfcfa 这一档，明度 208~255，**没有一套是深的**</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>⚠ 为什么 2.4.5 真机上「还是有黑边」，2.4.6 量出了实据：把公式改回「往墨渗」再逐套数一遍，十套里有**五套是深的**（杂志封面 #0e1635／荧光渐变 #0e1c46／波普分格 #14151d／网点漫画 #6877e1／摘句 #4e5955）；他截图那张正是「杂志封面」——黑在**掺错了方向**，不在「加了一圈」。那次反向验证跑完已撤回。⚠ 「纸白占 80%」这一档是我定的，他没拍数</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>拖动失败那句英文的收口</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.4.6)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>屏上那一串「Method Not Allowed」**不是我们写的话**，是后端框架的兜底短语；改成只认带中文的那一份，英文一律改说本机那句「保存失败，请重试」</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 为什么是 405 不是 404：现网注册着 `DELETE …/assets/{asset_id}` 却没有那条 reorder ⇒ `reorder` 被当 `asset_id` 吃进那条路，**路径对上、方法不对**。四条对照探针量出来的：reorder 405／zzz9x 405（同形状）／`DELETE …/assets/reorder` 401（同一条路、方法对了就走到鉴权）／没注册的路径 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>卡片模板</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>图文卡描边＋网点漫画署名色</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.4.7 纯数据、不发版)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>① 图文卡那一圈 3 宽灰描边撤了（配方 20 步减到 19 步，四边无线；外圈那一档留住＝2.4.6 那个数）；② 网点漫画署名行**漏传了一个开关**——那句 slogan 走「深色底就白、浅底就灰」，它没说是深色底，于是紫底上拿到了灰、对底只有 **1.20:1（等于看不见）**；补上 `onDark` 后那句走白（2.42:1）、名字跟着变纸白，与它那三套深色兄弟同一口径</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>⚠ 两处都灌进现网了（库里 live 那两行 `c2415afcf6c7`／`0f55f945b267`），但客户端**只在开一次「我的」那一屏时才重取下发** ⇒ 不刷那一下屏上还是旧样子，那不是没生效；⚠ 那句要**纯白**（3.23:1）还差一步：得给署名那枚原语加一个单独管它颜色的参数＝改画法＝要发版，等他挑</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>录入</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>首屏那一行那句短话</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.4.8)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>他 ⑮「那句话也改下，图麦笔记：仅需10秒拍照截图网页转笔记」⇒ `i18n.js:7` `aiLine` 换成这一句；英文那格是我砍的＝`TumarkNote: any shot, noted in 10s`（他 only 给了中文）</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 改短不是顺手：那一行 `white-space: nowrap`，挤不下**不折行**、会把最右的中/EN 角标顶出屏；旧那句屏上量到 515rpx 墨迹，再加这枚 144 就超 702 的内容宽</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>卡片模板</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>英文那一句压住模板名</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>迭代(2.4.8)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>他 ⑰「英文版，左上角与中间重叠了，你要压缩左侧英文」——那一句里带答案，所以照做、没列成待拍；只有英文怎么写是我定的：`Swipe to change template` → **`Swipe to switch`**（宾语不写死成 template，因为中间那枚正在念的就是模板名）；中文「左右滑换模板」是他原话一字没动</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>⚠ 那一行三枚字全是绝对定位、挤在一条 56rpx 的带子里 ⇒ 挤不下不折行也不缩，直接压在一起；判据量的是**墨迹**不是盒子（中间那枚盒子恒等于限宽 340rpx，`left:0;right:0;max-width;margin:0 auto` 拉满再夹回来——第一版把盒子当墨迹，11 套量回来全是同一组数）。自证：静态 45 条全绿（含一条反向），真跑 43 条全绿，最窄那条缝 41.1rpx 出在 `Magazine Cover` 那一档</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>位次</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>「不能拖动图片排序了」那一问</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>⑱ 结案：**不是回归**——他手机此刻跑的是线上 2.4.0 那颗包。2.4.0 是 10-19 15:0x 传的，这一刀 21:33 才落码 ⇒ 那颗包里 `onShotDragStart` 出现零次，第一颗含它的是 2.4.1；日志对得上：16:04／16:08 那两拖成功的 referer 包号 `/0/`（开发版·预览码那一档）</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 这一条给的是一条**读法**（10-20 我自己也栽过一次）：**「抬号那一刀没带功能」≠「那一个包没带功能」**——包是 `cli upload` 那一刻的整棵工作树，2.4.0 那颗里就压着抬号之后另两刀（`65d791b` 详情窗大图按比例完整显示＋毛玻璃垫底、`d460db0` 提炼完不再跳走）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -523,7 +523,7 @@
         <is>
           <t>全量功能清单 · 总览｜截至 **2026-10-21 01:0x**（版本号与发布位次已另立正本 **`docs/版本与发布现状.md`**——要位次读那一份，这张表只管功能对照；10-21 这趟只重读了小程序本地号与 iPhone 那一侧，服务器与后台没再进）
 小程序：线上 **2.4.0**（他 10-20 傍晚口述＋一条服务端日志佐证＝正式版 referer 档当天从 `/14/` 升到 `/15/`；后台最后一格**真截图**仍是 10-15 20:23＝那时线上 2.2.0，10-21 没进后台）／**审核中＝没有读数**（提审这一步 10-11 起定死归他本人，我不自动跑）／架上开发版本最新一枚 **2.4.8**（10-21 00:3x `cli upload -v 2.4.8`，包 **728,596 B**）；本地树 `appInfo.js:457` 现读 `VERSION = '2.4.8'`＝**与架上同号，没有「改了没出包」的欠账**；⚠ **2.4.1～2.4.8 那七号的东西一件都不在线上**（新分享封面／「懒人记录神器」那句／配图长按拖动排序·第一张＝头图／卡片圆点横拖换模板／详情窗左右滑换前后篇·遇私密自动跳过／卡片外圈只往纸白走／首屏那枚 Share 胶囊）⇒ **对外材料里的「当前版本」只能写 2.4.0**；⚠ 10-21 凌晨那句「编辑笔记又不能拖动图片排序了」就是这么结案的：**不是回归，是他手机上跑的是线上那颗 2.4.0**。
-后端现网 **第五十一次部署**（10-20 18:53＝第三轮审计那批修复：后端 26 只文件＋云函数 `extract` 重传，双 unit 重启）｜**第五十次**（10-20 15:4x＝**配图拖动排序的后端那一半**上现网：`assets.sort_order` 那一列＋迁移＋`POST /api/notes/{id}/assets/reorder`＋四处读图口改吃同一份排序键，**小程序包一个字节没动**；那条口部署前 **405**→部署后 **401「无效的 Token」**；新探针 `docs/工具/探-现网配图拖动排序.py` 23 条红 0、回归 `assets_live_probe.py` 49/49；迁移头 `alembic current` = **`a4d7e2b91c58`**（由 `f0a3b9c6d172` 升上来；升完 `assets` 91 行 `sort_order` 全是 0、28 篇头图 `cover_file_id` 逐篇未变））｜卡片模板下发：现网 **11 行 live**，10-20 另两趟是**纯数据**改动（图文卡那一圈 3 宽灰描边撤＝配方 20 步减到 19 步；网点漫画补回 `onDark` 白字），不发版；`deploy.sh` 那道闸默认关，要 `POSTER_TEMPLATES=1`｜⚠ **分类译名那一格 10-21 没重读服务器**，仍是「列在库里、读它的代码没上」＝**待核，不许写成已上线**。
+后端现网 **第五十一次部署**（10-20 18:53＝第三轮审计那批修复：后端 26 只文件＋云函数 `extract` 重传，双 unit 重启）｜**第五十次**（10-20 15:4x＝**配图拖动排序的后端那一半**上现网：`assets.sort_order` 那一列＋迁移＋`POST /api/notes/{id}/assets/reorder`＋四处读图口改吃同一份排序键，**小程序包一个字节没动**；那条口部署前 **405**→部署后 **401「无效的 Token」**；新探针 `docs/工具/探-现网配图拖动排序.py` 23 条红 0、回归 `assets_live_probe.py` 49/49；迁移头 `alembic current` = **`a4d7e2b91c58`**（由 `f0a3b9c6d172` 升上来；升完 `assets` 91 行 `sort_order` 全是 0、28 篇头图 `cover_file_id` 逐篇未变））｜卡片模板下发：现网 **11 行 live**，10-20 另两趟是**纯数据**改动（图文卡那一圈 3 宽灰描边撤＝配方 20 步减到 19 步；网点漫画补回 `onDark` 白字），不发版；`deploy.sh` 那道闸默认关，要 `POSTER_TEMPLATES=1`｜✅ **分类译名那一格 10-21 01:3x 现读已翻正**：`categories.py` 里那两栏命中 6、`app/services/category_names.py` 在服务器上存在（mtime 10-19 14:55）＝与 §8.344 记的**第四十七次部署**（10-19 14:16）对上 ⇒ 旧判据「列在库里、代码没上」不成立；⚠ 但**屏上译名出没出仍无读数**（要一台手机）。
 iPhone：**1.2(34)**（`TumarkNote/ios/project.yml:224-225` 10-21 现读 `MARKETING_VERSION: "1.2"`／`CURRENT_PROJECT_VERSION: "34"`，树顶 `65c312c` 10-21 00:45，无远端）；它自己那套复刻清单正本 `ios/复刻清单-小程序2.2-20261016.md`（137,562 B，10-21 00:54 还在改）的锚点停在 **2.4.6**，而小程序这头已走到 **2.4.8** ⇒ **那一列凡是「照正本对齐」的结论都按 2.4.6 读的，2.4.7／2.4.8 那两号它还没跟**；它自己那份 `ios/出包前检查.md:1075` 现读**「能提审的仍然只有 `1.2(13)`；14~26 都只出过 Debug 包」**，且那边写明这仓库根本没有 remote；⚠ **真机那一头仍欠**（第十七到二十八刀的真机清单已落盘、装机卡在「手机锁着」）⇒ **iPhone 列写「有」的，多数只到模拟器断言级，不是真机级**，引用时带上这一句。
 ⚠ 两端对照口径禁令照旧：10-21 在那侧现读到的三格硬差异——**配图不能逐张删也不能拖动排序**（`Domain/ShotAttachmentStore.swift` 只有 `retain`／`urls`／`delete`／`sweepOrphans`／`discardAll` 五只口）、**没有私密分类**（`Views/NoteRowView.swift:19,25`、`Design/AppCopy.swift:166`、`Views/DetailView.swift:473` 三处都自己写明）、**没有转存这件事**（`Views/NoteRowView.swift:21,151`：列表来源栏第三档「转存人昵称」这边没有对应数据）；模板那一族是**十套写死在编译期**（`Domain/Card/CardTemplate.swift:5`），远程模板包目录 `agentsbin.cn/templates/manifest.json` 按它自己那份检查文档**还没部署** ⇒ 取不到就原地不动。小程序全免费、iPhone 六套要订阅（¥69.99 买断／¥19.99 月订）；小程序有账号与云备份、iPhone 本地优先无账户——**功能与商业口径都不许互推**；2.4.x 那一整窗口见后面「2.4 一夜八句」那张分表</t>
         </is>
@@ -785,7 +785,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>分类行文字下划线式；私密格自动备、有笔记删不掉；**10-17 起改成面板内管理**（`a2f0141`：＋新增／✕删带二次确认／长按拖动／点空白自动保存／四类默认／名称跟着界面语言自动翻译），⚠ **后端那一半（`5f0b801`）今天算「半上」：库到位了、代码没上**——10-19 01:0x 现读服务器：alembic 头已到 `f0a3b9c6d172`、`categories` 里 `name_zh`／`name_en` 两列**在**（那表 9 行），而 `app/api/routes/categories.py` 里 `name_zh|name_en` 命中 **0**、`app/services/category_names.py` 这只文件在服务器上**不存在** ⇒ 表在库里≠这条链上线</t>
+          <t>分类行文字下划线式；私密格自动备、有笔记删不掉；**10-17 起改成面板内管理**（`a2f0141`：＋新增／✕删带二次确认／长按拖动／点空白自动保存／四类默认／名称跟着界面语言自动翻译），⚠ **后端那一半 10-19 14:16 随第四十七次部署上现网了**（§8.344；10-21 01:3x 现读复证：`categories.py` 里那两栏命中 **6**、`app/services/category_names.py` 存在、mtime 10-19 14:55）——我 10-19 01:0x 那格写的「列在库里、代码没上」**已被这一次现读推翻**；但**屏上译名出没出仍没有读数**（那要一台手机），且 §8.344 自己那条「模型那一档在现网永远回不来」的探针结论还在 ⇒ 这一格只能报「代码已上、端到端未验」</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>样式不同；小程序有私密格保护规则；**「名称自动翻译」这一件在现网差的是读那两栏的代码**（列已在库里，屏上仍不出译名）</t>
+          <t>样式不同；小程序有私密格保护规则；**「名称自动翻译」差的那半现在只差真机读数、不缺服务器代码**</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-全量.xlsx
+++ b/docs/功能清单-全量.xlsx
@@ -521,8 +521,8 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全量功能清单 · 总览｜截至 **2026-10-21 01:0x**（版本号与发布位次已另立正本 **`docs/版本与发布现状.md`**——要位次读那一份，这张表只管功能对照；10-21 这趟只重读了小程序本地号与 iPhone 那一侧，服务器与后台没再进）
-小程序：线上 **2.4.0**（他 10-20 傍晚口述＋一条服务端日志佐证＝正式版 referer 档当天从 `/14/` 升到 `/15/`；后台最后一格**真截图**仍是 10-15 20:23＝那时线上 2.2.0，10-21 没进后台）／**审核中＝没有读数**（提审这一步 10-11 起定死归他本人，我不自动跑）／架上开发版本最新一枚 **2.4.8**（10-21 00:3x `cli upload -v 2.4.8`，包 **728,596 B**）；本地树 `appInfo.js:457` 现读 `VERSION = '2.4.8'`＝**与架上同号，没有「改了没出包」的欠账**；⚠ **2.4.1～2.4.8 那七号的东西一件都不在线上**（新分享封面／「懒人记录神器」那句／配图长按拖动排序·第一张＝头图／卡片圆点横拖换模板／详情窗左右滑换前后篇·遇私密自动跳过／卡片外圈只往纸白走／首屏那枚 Share 胶囊）⇒ **对外材料里的「当前版本」只能写 2.4.0**；⚠ 10-21 凌晨那句「编辑笔记又不能拖动图片排序了」就是这么结案的：**不是回归，是他手机上跑的是线上那颗 2.4.0**。
+          <t>全量功能清单 · 总览｜截至 **2026-10-21 12:2x**（版本号与发布位次已另立正本 **`docs/版本与发布现状.md`**——要位次读那一份，这张表只管功能对照；10-21 这趟只重读了小程序本地号、服务器日志那一档与 iPhone 那一侧，后台没进去）
+小程序：线上 **2.4.8**（他 10-21 12:1x 口述「2.4.8 已经发布」＋一条服务端旁证＝正式版 referer 档从 `/15/` 抬到 `/16/`，`/16/` 首次 12:12:14、一分钟内 103 次；后台那一格 10-21 全天零读数＝`请使用微信扫码`／`not login`，所以号是口述不是后台实读）／**审核中＝应已无在审单（推论，无读数）**（他 00:44:25 提的正是 2.4.8，既已发布那一单就走完了）／架上开发版本最新一枚 **2.4.8**（10-21 00:3x `cli upload -v 2.4.8`，包 **728,596 B**）；本地树 `appInfo.js:457` 现读 `VERSION = '2.4.8'`＝**与架上、与线上同号，没有「改了没出包」的欠账**；✅ **2.4.1～2.4.8 那七号的东西现在全在线上了**（新分享封面／「懒人记录神器」那句／配图长按拖动排序·第一张＝头图／卡片圆点横拖换模板／详情窗左右滑换前后篇·遇私密自动跳过／卡片外圈只往纸白走／首屏那枚 Share 胶囊）⇒ **对外材料里的「当前版本」写 2.4.8**；⚠ 唯一没跟着上线的是分享标题的**英文那一格**（2.4.2 起就没动过）。
 后端现网 **第五十一次部署**（10-20 18:53＝第三轮审计那批修复：后端 26 只文件＋云函数 `extract` 重传，双 unit 重启）｜**第五十次**（10-20 15:4x＝**配图拖动排序的后端那一半**上现网：`assets.sort_order` 那一列＋迁移＋`POST /api/notes/{id}/assets/reorder`＋四处读图口改吃同一份排序键，**小程序包一个字节没动**；那条口部署前 **405**→部署后 **401「无效的 Token」**；新探针 `docs/工具/探-现网配图拖动排序.py` 23 条红 0、回归 `assets_live_probe.py` 49/49；迁移头 `alembic current` = **`a4d7e2b91c58`**（由 `f0a3b9c6d172` 升上来；升完 `assets` 91 行 `sort_order` 全是 0、28 篇头图 `cover_file_id` 逐篇未变））｜卡片模板下发：现网 **11 行 live**，10-20 另两趟是**纯数据**改动（图文卡那一圈 3 宽灰描边撤＝配方 20 步减到 19 步；网点漫画补回 `onDark` 白字），不发版；`deploy.sh` 那道闸默认关，要 `POSTER_TEMPLATES=1`｜✅ **分类译名那一格 10-21 01:3x 现读已翻正**：`categories.py` 里那两栏命中 6、`app/services/category_names.py` 在服务器上存在（mtime 10-19 14:55）＝与 §8.344 记的**第四十七次部署**（10-19 14:16）对上 ⇒ 旧判据「列在库里、代码没上」不成立；⚠ 但**屏上译名出没出仍无读数**（要一台手机）。
 iPhone：**1.2(34)**（`TumarkNote/ios/project.yml:224-225` 10-21 现读 `MARKETING_VERSION: "1.2"`／`CURRENT_PROJECT_VERSION: "34"`，树顶 `65c312c` 10-21 00:45，无远端）；它自己那套复刻清单正本 `ios/复刻清单-小程序2.2-20261016.md`（137,562 B，10-21 00:54 还在改）的锚点停在 **2.4.6**，而小程序这头已走到 **2.4.8** ⇒ **那一列凡是「照正本对齐」的结论都按 2.4.6 读的，2.4.7／2.4.8 那两号它还没跟**；它自己那份 `ios/出包前检查.md:1075` 现读**「能提审的仍然只有 `1.2(13)`；14~26 都只出过 Debug 包」**，且那边写明这仓库根本没有 remote；⚠ **真机那一头仍欠**（第十七到二十八刀的真机清单已落盘、装机卡在「手机锁着」）⇒ **iPhone 列写「有」的，多数只到模拟器断言级，不是真机级**，引用时带上这一句。
 ⚠ 两端对照口径禁令照旧：10-21 在那侧现读到的三格硬差异——**配图不能逐张删也不能拖动排序**（`Domain/ShotAttachmentStore.swift` 只有 `retain`／`urls`／`delete`／`sweepOrphans`／`discardAll` 五只口）、**没有私密分类**（`Views/NoteRowView.swift:19,25`、`Design/AppCopy.swift:166`、`Views/DetailView.swift:473` 三处都自己写明）、**没有转存这件事**（`Views/NoteRowView.swift:21,151`：列表来源栏第三档「转存人昵称」这边没有对应数据）；模板那一族是**十套写死在编译期**（`Domain/Card/CardTemplate.swift:5`），远程模板包目录 `agentsbin.cn/templates/manifest.json` 按它自己那份检查文档**还没部署** ⇒ 取不到就原地不动。小程序全免费、iPhone 六套要订阅（¥69.99 买断／¥19.99 月订）；小程序有账号与云备份、iPhone 本地优先无账户——**功能与商业口径都不许互推**；2.4.x 那一整窗口见后面「2.4 一夜八句」那张分表</t>
@@ -2317,7 +2317,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2.4.0 ~ 2.4.8（10-19 15:0x 起 ~ 10-21 00:3x）｜**他 10-20 傍晚口述「2.4.0 已经发布」⇒ 线上＝2.4.0，而 2.4.1~2.4.8 那七号的东西一件都不在线上**
+          <t>2.4.0 ~ 2.4.8（10-19 15:0x 起 ~ 10-21 00:3x）｜**他 10-21 12:1x 口述「2.4.8 已经发布」⇒ 线上＝2.4.8，2.4.1~2.4.8 那七号的东西现在全在线上了**
 iPhone 同期：1.2(34)（树顶 `65c312c` 10-21 00:45），它那份复刻清单的锚点只重到正本 **2.4.6** ⇒ 本表凡是「2.4.7／2.4.8」的行，那侧连对标都没开始；那边真机仍欠（装机卡在「手机锁着」）</t>
         </is>
       </c>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>线上 **2.4.0**（口述＋一条服务端日志佐证：正式版 referer 档当天从 `/14/` 升到 `/15/`）；架上开发版最新 **2.4.8**（10-21 00:3x `cli upload -v 2.4.8`，**728,596 B**）；本地 `appInfo.js:457` 现读 `VERSION = '2.4.8'`＝与架上同号、没有「改了没出包」的欠账；**审核中＝没有读数**（提审归他本人，10-11 起定死）</t>
+          <t>线上 **2.4.8**（他 12:1x 口述＋一条服务端旁证：正式版 referer 档从 `/15/` 抬到 `/16/`，`/16/` 首次 12:12:14、一分钟 103 次；⚠ 那一档只证「换包」、不证包号）；架上开发版最新 **2.4.8**（10-21 00:3x `cli upload -v 2.4.8`，**728,596 B**）；本地 `appInfo.js:457` 现读 `VERSION = '2.4.8'`＝与架上、与线上三号对齐；**审核中＝应已无在审单（推论，无读数——后台 10-21 全天 not login）**</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>⚠ **对外材料里的「当前版本」只能写 2.4.0**；演示前先让他看「我的→关于」那一行念的是哪一号</t>
+          <t>⚠ **对外材料里的「当前版本」写 2.4.8**（此前那份写 2.4.0）；他掏手机演示时「我的→关于」应念 `v2.4.8`，若还念 2.4.0 是微信那头没换包</t>
         </is>
       </c>
     </row>
